--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRM_Dominus_Entrega\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43419089-DB6C-432F-A2FF-72E5ADBE651E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AA0724-5EF4-4AD9-9697-328003AA6425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="177">
   <si>
     <t>cidade</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>Tatiane</t>
+  </si>
+  <si>
+    <t>data_meta</t>
   </si>
 </sst>
 </file>
@@ -643,7 +646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -658,6 +661,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,10 +1024,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1273"/>
+  <dimension ref="A1:F1273"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1039,8 +1046,11 @@
       <c r="E1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
@@ -1056,8 +1066,11 @@
       <c r="E2" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="E3" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1090,8 +1106,11 @@
       <c r="E4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1107,8 +1126,11 @@
       <c r="E5" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1146,11 @@
       <c r="E6" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1166,11 @@
       <c r="E7" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1158,8 +1186,11 @@
       <c r="E8" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1175,8 +1206,11 @@
       <c r="E9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -1192,8 +1226,11 @@
       <c r="E10" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
@@ -1209,8 +1246,11 @@
       <c r="E11" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
@@ -1226,8 +1266,11 @@
       <c r="E12" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
@@ -1243,8 +1286,11 @@
       <c r="E13" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
@@ -1260,8 +1306,11 @@
       <c r="E14" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
@@ -1277,8 +1326,11 @@
       <c r="E15" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -1294,8 +1346,11 @@
       <c r="E16" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
@@ -1311,8 +1366,11 @@
       <c r="E17" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
@@ -1328,8 +1386,11 @@
       <c r="E18" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
@@ -1345,8 +1406,11 @@
       <c r="E19" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
@@ -1362,8 +1426,11 @@
       <c r="E20" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
@@ -1379,8 +1446,11 @@
       <c r="E21" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
@@ -1396,8 +1466,11 @@
       <c r="E22" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
@@ -1413,8 +1486,11 @@
       <c r="E23" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
@@ -1430,8 +1506,11 @@
       <c r="E24" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
@@ -1447,8 +1526,11 @@
       <c r="E25" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
@@ -1464,8 +1546,11 @@
       <c r="E26" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
@@ -1481,8 +1566,11 @@
       <c r="E27" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
@@ -1498,8 +1586,11 @@
       <c r="E28" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
@@ -1515,8 +1606,11 @@
       <c r="E29" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
@@ -1532,8 +1626,11 @@
       <c r="E30" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
@@ -1549,8 +1646,11 @@
       <c r="E31" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>34</v>
       </c>
@@ -1566,8 +1666,11 @@
       <c r="E32" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
@@ -1583,8 +1686,11 @@
       <c r="E33" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>36</v>
       </c>
@@ -1600,8 +1706,11 @@
       <c r="E34" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
@@ -1617,8 +1726,11 @@
       <c r="E35" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>38</v>
       </c>
@@ -1634,8 +1746,11 @@
       <c r="E36" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
@@ -1651,8 +1766,11 @@
       <c r="E37" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>40</v>
       </c>
@@ -1668,8 +1786,11 @@
       <c r="E38" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
@@ -1685,8 +1806,11 @@
       <c r="E39" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>42</v>
       </c>
@@ -1702,8 +1826,11 @@
       <c r="E40" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
@@ -1719,8 +1846,11 @@
       <c r="E41" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
@@ -1736,8 +1866,11 @@
       <c r="E42" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>45</v>
       </c>
@@ -1753,8 +1886,11 @@
       <c r="E43" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>46</v>
       </c>
@@ -1770,8 +1906,11 @@
       <c r="E44" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
@@ -1787,8 +1926,11 @@
       <c r="E45" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>48</v>
       </c>
@@ -1804,8 +1946,11 @@
       <c r="E46" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
@@ -1821,8 +1966,11 @@
       <c r="E47" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>50</v>
       </c>
@@ -1838,8 +1986,11 @@
       <c r="E48" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
@@ -1855,8 +2006,11 @@
       <c r="E49" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>52</v>
       </c>
@@ -1872,8 +2026,11 @@
       <c r="E50" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
@@ -1889,8 +2046,11 @@
       <c r="E51" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>54</v>
       </c>
@@ -1906,8 +2066,11 @@
       <c r="E52" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
@@ -1923,8 +2086,11 @@
       <c r="E53" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
@@ -1940,8 +2106,11 @@
       <c r="E54" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>57</v>
       </c>
@@ -1957,8 +2126,11 @@
       <c r="E55" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>58</v>
       </c>
@@ -1974,8 +2146,11 @@
       <c r="E56" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>59</v>
       </c>
@@ -1991,8 +2166,11 @@
       <c r="E57" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>60</v>
       </c>
@@ -2008,8 +2186,11 @@
       <c r="E58" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>61</v>
       </c>
@@ -2025,8 +2206,11 @@
       <c r="E59" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>62</v>
       </c>
@@ -2042,8 +2226,11 @@
       <c r="E60" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>63</v>
       </c>
@@ -2059,8 +2246,11 @@
       <c r="E61" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>64</v>
       </c>
@@ -2076,8 +2266,11 @@
       <c r="E62" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>65</v>
       </c>
@@ -2093,8 +2286,11 @@
       <c r="E63" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>66</v>
       </c>
@@ -2110,8 +2306,11 @@
       <c r="E64" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>67</v>
       </c>
@@ -2127,8 +2326,11 @@
       <c r="E65" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>68</v>
       </c>
@@ -2144,8 +2346,11 @@
       <c r="E66" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>69</v>
       </c>
@@ -2161,8 +2366,11 @@
       <c r="E67" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>70</v>
       </c>
@@ -2178,8 +2386,11 @@
       <c r="E68" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>71</v>
       </c>
@@ -2195,8 +2406,11 @@
       <c r="E69" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>72</v>
       </c>
@@ -2212,8 +2426,11 @@
       <c r="E70" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>73</v>
       </c>
@@ -2229,8 +2446,11 @@
       <c r="E71" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>74</v>
       </c>
@@ -2246,8 +2466,11 @@
       <c r="E72" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>75</v>
       </c>
@@ -2263,8 +2486,11 @@
       <c r="E73" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>76</v>
       </c>
@@ -2280,8 +2506,11 @@
       <c r="E74" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>77</v>
       </c>
@@ -2297,8 +2526,11 @@
       <c r="E75" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>78</v>
       </c>
@@ -2314,8 +2546,11 @@
       <c r="E76" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>79</v>
       </c>
@@ -2331,8 +2566,11 @@
       <c r="E77" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>80</v>
       </c>
@@ -2348,8 +2586,11 @@
       <c r="E78" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>81</v>
       </c>
@@ -2365,8 +2606,11 @@
       <c r="E79" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>82</v>
       </c>
@@ -2382,8 +2626,11 @@
       <c r="E80" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>83</v>
       </c>
@@ -2399,8 +2646,11 @@
       <c r="E81" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>84</v>
       </c>
@@ -2416,8 +2666,11 @@
       <c r="E82" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>85</v>
       </c>
@@ -2433,8 +2686,11 @@
       <c r="E83" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>86</v>
       </c>
@@ -2450,8 +2706,11 @@
       <c r="E84" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>87</v>
       </c>
@@ -2467,8 +2726,11 @@
       <c r="E85" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>88</v>
       </c>
@@ -2484,8 +2746,11 @@
       <c r="E86" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>89</v>
       </c>
@@ -2501,8 +2766,11 @@
       <c r="E87" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>90</v>
       </c>
@@ -2518,8 +2786,11 @@
       <c r="E88" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>91</v>
       </c>
@@ -2535,8 +2806,11 @@
       <c r="E89" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>92</v>
       </c>
@@ -2552,8 +2826,11 @@
       <c r="E90" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>93</v>
       </c>
@@ -2569,8 +2846,11 @@
       <c r="E91" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>94</v>
       </c>
@@ -2586,8 +2866,11 @@
       <c r="E92" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F92" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>95</v>
       </c>
@@ -2603,8 +2886,11 @@
       <c r="E93" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F93" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>96</v>
       </c>
@@ -2620,8 +2906,11 @@
       <c r="E94" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F94" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>97</v>
       </c>
@@ -2637,8 +2926,11 @@
       <c r="E95" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F95" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>98</v>
       </c>
@@ -2654,8 +2946,11 @@
       <c r="E96" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F96" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>99</v>
       </c>
@@ -2671,8 +2966,11 @@
       <c r="E97" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F97" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>100</v>
       </c>
@@ -2688,8 +2986,11 @@
       <c r="E98" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F98" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>101</v>
       </c>
@@ -2705,8 +3006,11 @@
       <c r="E99" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F99" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>102</v>
       </c>
@@ -2722,8 +3026,11 @@
       <c r="E100" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F100" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>103</v>
       </c>
@@ -2739,8 +3046,11 @@
       <c r="E101" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F101" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>104</v>
       </c>
@@ -2756,8 +3066,11 @@
       <c r="E102" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F102" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>105</v>
       </c>
@@ -2773,8 +3086,11 @@
       <c r="E103" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F103" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>106</v>
       </c>
@@ -2790,8 +3106,11 @@
       <c r="E104" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F104" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="4" t="s">
         <v>107</v>
       </c>
@@ -2807,8 +3126,11 @@
       <c r="E105" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F105" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="4" t="s">
         <v>108</v>
       </c>
@@ -2824,8 +3146,11 @@
       <c r="E106" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F106" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="4" t="s">
         <v>109</v>
       </c>
@@ -2841,8 +3166,11 @@
       <c r="E107" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F107" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="4" t="s">
         <v>110</v>
       </c>
@@ -2858,8 +3186,11 @@
       <c r="E108" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F108" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="4" t="s">
         <v>111</v>
       </c>
@@ -2875,8 +3206,11 @@
       <c r="E109" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F109" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="4" t="s">
         <v>112</v>
       </c>
@@ -2892,8 +3226,11 @@
       <c r="E110" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F110" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="4" t="s">
         <v>113</v>
       </c>
@@ -2909,8 +3246,11 @@
       <c r="E111" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F111" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="4" t="s">
         <v>114</v>
       </c>
@@ -2926,8 +3266,11 @@
       <c r="E112" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F112" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="4" t="s">
         <v>115</v>
       </c>
@@ -2943,8 +3286,11 @@
       <c r="E113" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F113" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="4" t="s">
         <v>116</v>
       </c>
@@ -2960,8 +3306,11 @@
       <c r="E114" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F114" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="4" t="s">
         <v>117</v>
       </c>
@@ -2977,8 +3326,11 @@
       <c r="E115" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F115" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="4" t="s">
         <v>118</v>
       </c>
@@ -2994,8 +3346,11 @@
       <c r="E116" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F116" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="4" t="s">
         <v>119</v>
       </c>
@@ -3011,8 +3366,11 @@
       <c r="E117" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F117" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="4" t="s">
         <v>120</v>
       </c>
@@ -3028,8 +3386,11 @@
       <c r="E118" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F118" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="4" t="s">
         <v>121</v>
       </c>
@@ -3045,8 +3406,11 @@
       <c r="E119" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F119" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="4" t="s">
         <v>122</v>
       </c>
@@ -3062,8 +3426,11 @@
       <c r="E120" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F120" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="4" t="s">
         <v>123</v>
       </c>
@@ -3079,8 +3446,11 @@
       <c r="E121" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F121" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="4" t="s">
         <v>124</v>
       </c>
@@ -3096,8 +3466,11 @@
       <c r="E122" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F122" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="4" t="s">
         <v>125</v>
       </c>
@@ -3113,8 +3486,11 @@
       <c r="E123" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F123" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="4" t="s">
         <v>126</v>
       </c>
@@ -3130,8 +3506,11 @@
       <c r="E124" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F124" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="4" t="s">
         <v>127</v>
       </c>
@@ -3147,8 +3526,11 @@
       <c r="E125" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F125" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="4" t="s">
         <v>128</v>
       </c>
@@ -3164,8 +3546,11 @@
       <c r="E126" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F126" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="4" t="s">
         <v>129</v>
       </c>
@@ -3181,8 +3566,11 @@
       <c r="E127" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F127" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="4" t="s">
         <v>130</v>
       </c>
@@ -3198,8 +3586,11 @@
       <c r="E128" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F128" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="4" t="s">
         <v>131</v>
       </c>
@@ -3215,8 +3606,11 @@
       <c r="E129" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F129" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="4" t="s">
         <v>132</v>
       </c>
@@ -3232,8 +3626,11 @@
       <c r="E130" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F130" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="4" t="s">
         <v>133</v>
       </c>
@@ -3249,8 +3646,11 @@
       <c r="E131" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F131" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="4" t="s">
         <v>134</v>
       </c>
@@ -3266,8 +3666,11 @@
       <c r="E132" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F132" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="4" t="s">
         <v>135</v>
       </c>
@@ -3283,8 +3686,11 @@
       <c r="E133" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F133" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="4" t="s">
         <v>136</v>
       </c>
@@ -3300,8 +3706,11 @@
       <c r="E134" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F134" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="4" t="s">
         <v>137</v>
       </c>
@@ -3317,8 +3726,11 @@
       <c r="E135" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F135" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="4" t="s">
         <v>138</v>
       </c>
@@ -3334,8 +3746,11 @@
       <c r="E136" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F136" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="4" t="s">
         <v>139</v>
       </c>
@@ -3351,8 +3766,11 @@
       <c r="E137" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F137" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="4" t="s">
         <v>140</v>
       </c>
@@ -3368,8 +3786,11 @@
       <c r="E138" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F138" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="4" t="s">
         <v>141</v>
       </c>
@@ -3385,8 +3806,11 @@
       <c r="E139" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F139" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="4" t="s">
         <v>142</v>
       </c>
@@ -3402,8 +3826,11 @@
       <c r="E140" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F140" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="4" t="s">
         <v>143</v>
       </c>
@@ -3419,8 +3846,11 @@
       <c r="E141" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F141" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="4" t="s">
         <v>144</v>
       </c>
@@ -3436,8 +3866,11 @@
       <c r="E142" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F142" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="4" t="s">
         <v>145</v>
       </c>
@@ -3453,8 +3886,11 @@
       <c r="E143" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F143" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="4" t="s">
         <v>146</v>
       </c>
@@ -3470,8 +3906,11 @@
       <c r="E144" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F144" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>147</v>
       </c>
@@ -3487,8 +3926,11 @@
       <c r="E145" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F145" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="4" t="s">
         <v>148</v>
       </c>
@@ -3504,8 +3946,11 @@
       <c r="E146" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F146" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="4" t="s">
         <v>149</v>
       </c>
@@ -3521,8 +3966,11 @@
       <c r="E147" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F147" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="4" t="s">
         <v>150</v>
       </c>
@@ -3538,8 +3986,11 @@
       <c r="E148" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F148" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="4" t="s">
         <v>151</v>
       </c>
@@ -3555,8 +4006,11 @@
       <c r="E149" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F149" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="4" t="s">
         <v>152</v>
       </c>
@@ -3572,8 +4026,11 @@
       <c r="E150" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F150" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="4" t="s">
         <v>153</v>
       </c>
@@ -3589,8 +4046,11 @@
       <c r="E151" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F151" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="4" t="s">
         <v>154</v>
       </c>
@@ -3606,8 +4066,11 @@
       <c r="E152" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F152" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="4" t="s">
         <v>155</v>
       </c>
@@ -3623,8 +4086,11 @@
       <c r="E153" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F153" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="4" t="s">
         <v>156</v>
       </c>
@@ -3640,8 +4106,11 @@
       <c r="E154" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F154" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="4" t="s">
         <v>157</v>
       </c>
@@ -3657,8 +4126,11 @@
       <c r="E155" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F155" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="4" t="s">
         <v>158</v>
       </c>
@@ -3674,8 +4146,11 @@
       <c r="E156" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F156" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>159</v>
       </c>
@@ -3691,8 +4166,11 @@
       <c r="E157" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F157" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="4" t="s">
         <v>160</v>
       </c>
@@ -3708,8 +4186,11 @@
       <c r="E158" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F158" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="4" t="s">
         <v>161</v>
       </c>
@@ -3725,8 +4206,11 @@
       <c r="E159" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F159" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="4" t="s">
         <v>162</v>
       </c>
@@ -3742,803 +4226,3191 @@
       <c r="E160" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="4"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="5"/>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="4"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="5"/>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="4"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="5"/>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="4"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="5"/>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="4"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="5"/>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="4"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="5"/>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="4"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="5"/>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="4"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="5"/>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="4"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="5"/>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="4"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="5"/>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="4"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="5"/>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="4"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="5"/>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="4"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="5"/>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="4"/>
-      <c r="B174" s="2"/>
-      <c r="C174" s="5"/>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="4"/>
-      <c r="B175" s="2"/>
-      <c r="C175" s="5"/>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="4"/>
-      <c r="B176" s="2"/>
-      <c r="C176" s="5"/>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="4"/>
-      <c r="B177" s="2"/>
-      <c r="C177" s="5"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="4"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="5"/>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="4"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="5"/>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="4"/>
-      <c r="B180" s="2"/>
-      <c r="C180" s="5"/>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="4"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="5"/>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="4"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="5"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" s="4"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="5"/>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="4"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="5"/>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="4"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="5"/>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" s="4"/>
-      <c r="B186" s="2"/>
-      <c r="C186" s="5"/>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="4"/>
-      <c r="B187" s="2"/>
-      <c r="C187" s="5"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="4"/>
-      <c r="B188" s="2"/>
-      <c r="C188" s="5"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="4"/>
-      <c r="B189" s="2"/>
-      <c r="C189" s="5"/>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="4"/>
-      <c r="B190" s="2"/>
-      <c r="C190" s="5"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="4"/>
-      <c r="B191" s="2"/>
-      <c r="C191" s="5"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="4"/>
-      <c r="B192" s="2"/>
-      <c r="C192" s="5"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="4"/>
-      <c r="B193" s="2"/>
-      <c r="C193" s="5"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="4"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="5"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="4"/>
-      <c r="B195" s="2"/>
-      <c r="C195" s="5"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="4"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="5"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="4"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="5"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="4"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="5"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="4"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="5"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" s="4"/>
-      <c r="B200" s="2"/>
-      <c r="C200" s="5"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" s="4"/>
-      <c r="B201" s="2"/>
-      <c r="C201" s="5"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" s="4"/>
-      <c r="B202" s="2"/>
-      <c r="C202" s="5"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" s="4"/>
-      <c r="B203" s="2"/>
-      <c r="C203" s="5"/>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" s="4"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="5"/>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" s="4"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="5"/>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" s="4"/>
-      <c r="B206" s="2"/>
-      <c r="C206" s="5"/>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" s="4"/>
-      <c r="B207" s="2"/>
-      <c r="C207" s="5"/>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" s="4"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="5"/>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" s="4"/>
-      <c r="B209" s="2"/>
-      <c r="C209" s="5"/>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" s="4"/>
-      <c r="B210" s="2"/>
-      <c r="C210" s="5"/>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="4"/>
-      <c r="B211" s="2"/>
-      <c r="C211" s="5"/>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" s="4"/>
-      <c r="B212" s="2"/>
-      <c r="C212" s="5"/>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="4"/>
-      <c r="B213" s="2"/>
-      <c r="C213" s="5"/>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214" s="4"/>
-      <c r="B214" s="2"/>
-      <c r="C214" s="5"/>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215" s="4"/>
-      <c r="B215" s="2"/>
-      <c r="C215" s="5"/>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A216" s="4"/>
-      <c r="B216" s="2"/>
-      <c r="C216" s="5"/>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A217" s="4"/>
-      <c r="B217" s="2"/>
-      <c r="C217" s="5"/>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A218" s="4"/>
-      <c r="B218" s="2"/>
-      <c r="C218" s="5"/>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A219" s="4"/>
-      <c r="B219" s="2"/>
-      <c r="C219" s="5"/>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A220" s="4"/>
-      <c r="B220" s="2"/>
-      <c r="C220" s="5"/>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A221" s="4"/>
-      <c r="B221" s="2"/>
-      <c r="C221" s="5"/>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A222" s="4"/>
-      <c r="B222" s="2"/>
-      <c r="C222" s="5"/>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A223" s="4"/>
-      <c r="B223" s="2"/>
-      <c r="C223" s="5"/>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A224" s="4"/>
-      <c r="B224" s="2"/>
-      <c r="C224" s="5"/>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A225" s="4"/>
-      <c r="B225" s="2"/>
-      <c r="C225" s="5"/>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A226" s="4"/>
-      <c r="B226" s="2"/>
-      <c r="C226" s="5"/>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" s="4"/>
-      <c r="B227" s="2"/>
-      <c r="C227" s="5"/>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" s="4"/>
-      <c r="B228" s="2"/>
-      <c r="C228" s="5"/>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" s="4"/>
-      <c r="B229" s="2"/>
-      <c r="C229" s="5"/>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" s="4"/>
-      <c r="B230" s="2"/>
-      <c r="C230" s="5"/>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" s="4"/>
-      <c r="B231" s="2"/>
-      <c r="C231" s="5"/>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" s="4"/>
-      <c r="B232" s="2"/>
-      <c r="C232" s="5"/>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233" s="4"/>
-      <c r="B233" s="2"/>
-      <c r="C233" s="5"/>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" s="4"/>
-      <c r="B234" s="2"/>
-      <c r="C234" s="5"/>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A235" s="4"/>
-      <c r="B235" s="2"/>
-      <c r="C235" s="5"/>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A236" s="4"/>
-      <c r="B236" s="2"/>
-      <c r="C236" s="5"/>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A237" s="4"/>
-      <c r="B237" s="2"/>
-      <c r="C237" s="5"/>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A238" s="4"/>
-      <c r="B238" s="2"/>
-      <c r="C238" s="5"/>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A239" s="4"/>
-      <c r="B239" s="2"/>
-      <c r="C239" s="5"/>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A240" s="4"/>
-      <c r="B240" s="2"/>
-      <c r="C240" s="5"/>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A241" s="4"/>
-      <c r="B241" s="2"/>
-      <c r="C241" s="5"/>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" s="4"/>
-      <c r="B242" s="2"/>
-      <c r="C242" s="5"/>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243" s="4"/>
-      <c r="B243" s="2"/>
-      <c r="C243" s="5"/>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244" s="4"/>
-      <c r="B244" s="2"/>
-      <c r="C244" s="5"/>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245" s="4"/>
-      <c r="B245" s="2"/>
-      <c r="C245" s="5"/>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="4"/>
-      <c r="B246" s="2"/>
-      <c r="C246" s="5"/>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="4"/>
-      <c r="B247" s="2"/>
-      <c r="C247" s="5"/>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="4"/>
-      <c r="B248" s="2"/>
-      <c r="C248" s="5"/>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="4"/>
-      <c r="B249" s="2"/>
-      <c r="C249" s="5"/>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A250" s="4"/>
-      <c r="B250" s="2"/>
-      <c r="C250" s="5"/>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="4"/>
-      <c r="B251" s="2"/>
-      <c r="C251" s="5"/>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="4"/>
-      <c r="B252" s="2"/>
-      <c r="C252" s="5"/>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253" s="4"/>
-      <c r="B253" s="2"/>
-      <c r="C253" s="5"/>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="4"/>
-      <c r="B254" s="2"/>
-      <c r="C254" s="5"/>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A255" s="4"/>
-      <c r="B255" s="2"/>
-      <c r="C255" s="5"/>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A256" s="4"/>
-      <c r="B256" s="2"/>
-      <c r="C256" s="5"/>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A257" s="4"/>
-      <c r="B257" s="2"/>
-      <c r="C257" s="5"/>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A258" s="4"/>
-      <c r="B258" s="2"/>
-      <c r="C258" s="5"/>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A259" s="4"/>
-      <c r="B259" s="2"/>
-      <c r="C259" s="5"/>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A260" s="4"/>
-      <c r="B260" s="2"/>
-      <c r="C260" s="5"/>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A261" s="4"/>
-      <c r="B261" s="2"/>
-      <c r="C261" s="5"/>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A262" s="4"/>
-      <c r="B262" s="2"/>
-      <c r="C262" s="5"/>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A263" s="4"/>
-      <c r="B263" s="2"/>
-      <c r="C263" s="5"/>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A264" s="4"/>
-      <c r="B264" s="2"/>
-      <c r="C264" s="5"/>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A265" s="4"/>
-      <c r="B265" s="2"/>
-      <c r="C265" s="5"/>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266" s="4"/>
-      <c r="B266" s="2"/>
-      <c r="C266" s="5"/>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A267" s="4"/>
-      <c r="B267" s="2"/>
-      <c r="C267" s="5"/>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268" s="4"/>
-      <c r="B268" s="2"/>
-      <c r="C268" s="5"/>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269" s="4"/>
-      <c r="B269" s="2"/>
-      <c r="C269" s="5"/>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" s="4"/>
-      <c r="B270" s="2"/>
-      <c r="C270" s="5"/>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" s="4"/>
-      <c r="B271" s="2"/>
-      <c r="C271" s="5"/>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" s="4"/>
-      <c r="B272" s="2"/>
-      <c r="C272" s="5"/>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" s="4"/>
-      <c r="B273" s="2"/>
-      <c r="C273" s="5"/>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" s="4"/>
-      <c r="B274" s="2"/>
-      <c r="C274" s="5"/>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" s="4"/>
-      <c r="B275" s="2"/>
-      <c r="C275" s="5"/>
-    </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A276" s="4"/>
-      <c r="B276" s="2"/>
-      <c r="C276" s="5"/>
-    </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A277" s="4"/>
-      <c r="B277" s="2"/>
-      <c r="C277" s="5"/>
-    </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A278" s="4"/>
-      <c r="B278" s="2"/>
-      <c r="C278" s="5"/>
-    </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A279" s="4"/>
-      <c r="B279" s="2"/>
-      <c r="C279" s="5"/>
-    </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A280" s="4"/>
-      <c r="B280" s="2"/>
-      <c r="C280" s="5"/>
-    </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A281" s="4"/>
-      <c r="B281" s="2"/>
-      <c r="C281" s="5"/>
-    </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A282" s="4"/>
-      <c r="B282" s="2"/>
-      <c r="C282" s="5"/>
-    </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A283" s="4"/>
-      <c r="B283" s="2"/>
-      <c r="C283" s="5"/>
-    </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A284" s="4"/>
-      <c r="B284" s="2"/>
-      <c r="C284" s="5"/>
-    </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A285" s="4"/>
-      <c r="B285" s="2"/>
-      <c r="C285" s="5"/>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" s="4"/>
-      <c r="B286" s="2"/>
-      <c r="C286" s="5"/>
-    </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A287" s="4"/>
-      <c r="B287" s="2"/>
-      <c r="C287" s="5"/>
-    </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A288" s="4"/>
-      <c r="B288" s="2"/>
-      <c r="C288" s="5"/>
-    </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A289" s="4"/>
-      <c r="B289" s="2"/>
-      <c r="C289" s="5"/>
-    </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A290" s="4"/>
-      <c r="B290" s="2"/>
-      <c r="C290" s="5"/>
-    </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A291" s="4"/>
-      <c r="B291" s="2"/>
-      <c r="C291" s="5"/>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" s="4"/>
-      <c r="B292" s="2"/>
-      <c r="C292" s="5"/>
-    </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A293" s="4"/>
-      <c r="B293" s="2"/>
-      <c r="C293" s="5"/>
-    </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A294" s="4"/>
-      <c r="B294" s="2"/>
-      <c r="C294" s="5"/>
-    </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A295" s="4"/>
-      <c r="B295" s="2"/>
-      <c r="C295" s="5"/>
-    </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A296" s="4"/>
-      <c r="B296" s="2"/>
-      <c r="C296" s="5"/>
-    </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A297" s="4"/>
-      <c r="B297" s="2"/>
-      <c r="C297" s="5"/>
-    </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A298" s="4"/>
-      <c r="B298" s="2"/>
-      <c r="C298" s="5"/>
-    </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A299" s="4"/>
-      <c r="B299" s="2"/>
-      <c r="C299" s="5"/>
-    </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A300" s="4"/>
-      <c r="B300" s="2"/>
-      <c r="C300" s="5"/>
-    </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A301" s="4"/>
-      <c r="B301" s="2"/>
-      <c r="C301" s="5"/>
-    </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A302" s="4"/>
-      <c r="B302" s="2"/>
-      <c r="C302" s="5"/>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A303" s="4"/>
-      <c r="B303" s="2"/>
-      <c r="C303" s="5"/>
-    </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A304" s="4"/>
-      <c r="B304" s="2"/>
-      <c r="C304" s="5"/>
-    </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A305" s="4"/>
-      <c r="B305" s="2"/>
-      <c r="C305" s="5"/>
-    </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A306" s="4"/>
-      <c r="B306" s="2"/>
-      <c r="C306" s="5"/>
-    </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A307" s="4"/>
-      <c r="B307" s="2"/>
-      <c r="C307" s="5"/>
-    </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A308" s="4"/>
-      <c r="B308" s="2"/>
-      <c r="C308" s="5"/>
-    </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A309" s="4"/>
-      <c r="B309" s="2"/>
-      <c r="C309" s="5"/>
-    </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A310" s="4"/>
-      <c r="B310" s="2"/>
-      <c r="C310" s="5"/>
-    </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A311" s="4"/>
-      <c r="B311" s="2"/>
-      <c r="C311" s="5"/>
-    </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A312" s="4"/>
-      <c r="B312" s="2"/>
-      <c r="C312" s="5"/>
-    </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A313" s="4"/>
-      <c r="B313" s="2"/>
-      <c r="C313" s="5"/>
-    </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A314" s="4"/>
-      <c r="B314" s="2"/>
-      <c r="C314" s="5"/>
-    </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A315" s="4"/>
-      <c r="B315" s="2"/>
-      <c r="C315" s="5"/>
-    </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A316" s="4"/>
-      <c r="B316" s="2"/>
-      <c r="C316" s="5"/>
-    </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A317" s="4"/>
-      <c r="B317" s="2"/>
-      <c r="C317" s="5"/>
-    </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A318" s="4"/>
-      <c r="B318" s="2"/>
-      <c r="C318" s="5"/>
-    </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A319" s="4"/>
-      <c r="B319" s="2"/>
-      <c r="C319" s="5"/>
-    </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="F160" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="5">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>165</v>
+      </c>
+      <c r="E161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F161" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="5">
+        <v>15</v>
+      </c>
+      <c r="D162" t="s">
+        <v>165</v>
+      </c>
+      <c r="E162" t="s">
+        <v>166</v>
+      </c>
+      <c r="F162" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="5">
+        <v>3</v>
+      </c>
+      <c r="D163" t="s">
+        <v>165</v>
+      </c>
+      <c r="E163" t="s">
+        <v>166</v>
+      </c>
+      <c r="F163" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="5">
+        <v>4</v>
+      </c>
+      <c r="D164" t="s">
+        <v>167</v>
+      </c>
+      <c r="E164" t="s">
+        <v>166</v>
+      </c>
+      <c r="F164" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="5">
+        <v>0</v>
+      </c>
+      <c r="D165" t="s">
+        <v>165</v>
+      </c>
+      <c r="E165" t="s">
+        <v>166</v>
+      </c>
+      <c r="F165" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="5">
+        <v>153</v>
+      </c>
+      <c r="D166" t="s">
+        <v>168</v>
+      </c>
+      <c r="E166" t="s">
+        <v>166</v>
+      </c>
+      <c r="F166" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="5">
+        <v>9</v>
+      </c>
+      <c r="D167" t="s">
+        <v>169</v>
+      </c>
+      <c r="E167" t="s">
+        <v>170</v>
+      </c>
+      <c r="F167" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="5">
+        <v>1</v>
+      </c>
+      <c r="D168" t="s">
+        <v>169</v>
+      </c>
+      <c r="E168" t="s">
+        <v>170</v>
+      </c>
+      <c r="F168" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="5">
+        <v>0</v>
+      </c>
+      <c r="D169" t="s">
+        <v>171</v>
+      </c>
+      <c r="E169" t="s">
+        <v>166</v>
+      </c>
+      <c r="F169" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="5">
+        <v>0</v>
+      </c>
+      <c r="D170" t="s">
+        <v>169</v>
+      </c>
+      <c r="E170" t="s">
+        <v>172</v>
+      </c>
+      <c r="F170" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="5">
+        <v>11</v>
+      </c>
+      <c r="D171" t="s">
+        <v>169</v>
+      </c>
+      <c r="E171" t="s">
+        <v>173</v>
+      </c>
+      <c r="F171" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="5">
+        <v>111</v>
+      </c>
+      <c r="D172" t="s">
+        <v>168</v>
+      </c>
+      <c r="E172" t="s">
+        <v>166</v>
+      </c>
+      <c r="F172" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="5">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>171</v>
+      </c>
+      <c r="E173" t="s">
+        <v>166</v>
+      </c>
+      <c r="F173" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="5">
+        <v>1</v>
+      </c>
+      <c r="D174" t="s">
+        <v>165</v>
+      </c>
+      <c r="E174" t="s">
+        <v>166</v>
+      </c>
+      <c r="F174" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="5">
+        <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>165</v>
+      </c>
+      <c r="E175" t="s">
+        <v>166</v>
+      </c>
+      <c r="F175" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="5">
+        <v>10</v>
+      </c>
+      <c r="D176" t="s">
+        <v>167</v>
+      </c>
+      <c r="E176" t="s">
+        <v>166</v>
+      </c>
+      <c r="F176" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="5">
+        <v>84</v>
+      </c>
+      <c r="D177" t="s">
+        <v>168</v>
+      </c>
+      <c r="E177" t="s">
+        <v>166</v>
+      </c>
+      <c r="F177" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="5">
+        <v>15</v>
+      </c>
+      <c r="D178" t="s">
+        <v>165</v>
+      </c>
+      <c r="E178" t="s">
+        <v>166</v>
+      </c>
+      <c r="F178" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="5">
+        <v>2</v>
+      </c>
+      <c r="D179" t="s">
+        <v>169</v>
+      </c>
+      <c r="E179" t="s">
+        <v>170</v>
+      </c>
+      <c r="F179" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="5">
+        <v>4</v>
+      </c>
+      <c r="D180" t="s">
+        <v>165</v>
+      </c>
+      <c r="E180" t="s">
+        <v>166</v>
+      </c>
+      <c r="F180" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A181" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="5">
+        <v>116</v>
+      </c>
+      <c r="D181" t="s">
+        <v>168</v>
+      </c>
+      <c r="E181" t="s">
+        <v>166</v>
+      </c>
+      <c r="F181" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A182" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="5">
+        <v>51</v>
+      </c>
+      <c r="D182" t="s">
+        <v>167</v>
+      </c>
+      <c r="E182" t="s">
+        <v>166</v>
+      </c>
+      <c r="F182" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="5">
+        <v>33</v>
+      </c>
+      <c r="D183" t="s">
+        <v>168</v>
+      </c>
+      <c r="E183" t="s">
+        <v>166</v>
+      </c>
+      <c r="F183" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A184" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="5">
+        <v>32</v>
+      </c>
+      <c r="D184" t="s">
+        <v>169</v>
+      </c>
+      <c r="E184" t="s">
+        <v>172</v>
+      </c>
+      <c r="F184" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A185" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="5">
+        <v>3</v>
+      </c>
+      <c r="D185" t="s">
+        <v>168</v>
+      </c>
+      <c r="E185" t="s">
+        <v>166</v>
+      </c>
+      <c r="F185" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="5">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>169</v>
+      </c>
+      <c r="E186" t="s">
+        <v>170</v>
+      </c>
+      <c r="F186" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A187" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="5">
+        <v>76</v>
+      </c>
+      <c r="D187" t="s">
+        <v>174</v>
+      </c>
+      <c r="E187" t="s">
+        <v>166</v>
+      </c>
+      <c r="F187" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A188" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="5">
+        <v>45</v>
+      </c>
+      <c r="D188" t="s">
+        <v>167</v>
+      </c>
+      <c r="E188" t="s">
+        <v>166</v>
+      </c>
+      <c r="F188" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="5">
+        <v>121</v>
+      </c>
+      <c r="D189" t="s">
+        <v>168</v>
+      </c>
+      <c r="E189" t="s">
+        <v>166</v>
+      </c>
+      <c r="F189" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A190" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="5">
+        <v>2</v>
+      </c>
+      <c r="D190" t="s">
+        <v>169</v>
+      </c>
+      <c r="E190" t="s">
+        <v>170</v>
+      </c>
+      <c r="F190" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="5">
+        <v>517</v>
+      </c>
+      <c r="D191" t="s">
+        <v>165</v>
+      </c>
+      <c r="E191" t="s">
+        <v>166</v>
+      </c>
+      <c r="F191" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="5">
+        <v>1</v>
+      </c>
+      <c r="D192" t="s">
+        <v>169</v>
+      </c>
+      <c r="E192" t="s">
+        <v>173</v>
+      </c>
+      <c r="F192" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="5">
+        <v>37</v>
+      </c>
+      <c r="D193" t="s">
+        <v>165</v>
+      </c>
+      <c r="E193" t="s">
+        <v>166</v>
+      </c>
+      <c r="F193" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="5">
+        <v>54</v>
+      </c>
+      <c r="D194" t="s">
+        <v>165</v>
+      </c>
+      <c r="E194" t="s">
+        <v>166</v>
+      </c>
+      <c r="F194" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="5">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>165</v>
+      </c>
+      <c r="E195" t="s">
+        <v>166</v>
+      </c>
+      <c r="F195" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="5">
+        <v>11</v>
+      </c>
+      <c r="D196" t="s">
+        <v>171</v>
+      </c>
+      <c r="E196" t="s">
+        <v>166</v>
+      </c>
+      <c r="F196" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="5">
+        <v>36</v>
+      </c>
+      <c r="D197" t="s">
+        <v>171</v>
+      </c>
+      <c r="E197" t="s">
+        <v>166</v>
+      </c>
+      <c r="F197" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="5">
+        <v>1</v>
+      </c>
+      <c r="D198" t="s">
+        <v>169</v>
+      </c>
+      <c r="E198" t="s">
+        <v>170</v>
+      </c>
+      <c r="F198" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="5">
+        <v>45</v>
+      </c>
+      <c r="D199" t="s">
+        <v>174</v>
+      </c>
+      <c r="E199" t="s">
+        <v>166</v>
+      </c>
+      <c r="F199" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="5">
+        <v>18</v>
+      </c>
+      <c r="D200" t="s">
+        <v>165</v>
+      </c>
+      <c r="E200" t="s">
+        <v>166</v>
+      </c>
+      <c r="F200" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="5">
+        <v>3</v>
+      </c>
+      <c r="D201" t="s">
+        <v>165</v>
+      </c>
+      <c r="E201" t="s">
+        <v>166</v>
+      </c>
+      <c r="F201" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="5">
+        <v>136</v>
+      </c>
+      <c r="D202" t="s">
+        <v>174</v>
+      </c>
+      <c r="E202" t="s">
+        <v>166</v>
+      </c>
+      <c r="F202" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="5">
+        <v>2</v>
+      </c>
+      <c r="D203" t="s">
+        <v>169</v>
+      </c>
+      <c r="E203" t="s">
+        <v>170</v>
+      </c>
+      <c r="F203" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="5">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>165</v>
+      </c>
+      <c r="E204" t="s">
+        <v>166</v>
+      </c>
+      <c r="F204" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="5">
+        <v>2</v>
+      </c>
+      <c r="D205" t="s">
+        <v>169</v>
+      </c>
+      <c r="E205" t="s">
+        <v>173</v>
+      </c>
+      <c r="F205" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="5">
+        <v>178</v>
+      </c>
+      <c r="D206" t="s">
+        <v>169</v>
+      </c>
+      <c r="E206" t="s">
+        <v>170</v>
+      </c>
+      <c r="F206" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="5">
+        <v>2</v>
+      </c>
+      <c r="D207" t="s">
+        <v>169</v>
+      </c>
+      <c r="E207" t="s">
+        <v>170</v>
+      </c>
+      <c r="F207" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="5">
+        <v>2</v>
+      </c>
+      <c r="D208" t="s">
+        <v>169</v>
+      </c>
+      <c r="E208" t="s">
+        <v>173</v>
+      </c>
+      <c r="F208" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="5">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
+        <v>168</v>
+      </c>
+      <c r="E209" t="s">
+        <v>166</v>
+      </c>
+      <c r="F209" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="5">
+        <v>73</v>
+      </c>
+      <c r="D210" t="s">
+        <v>168</v>
+      </c>
+      <c r="E210" t="s">
+        <v>166</v>
+      </c>
+      <c r="F210" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="5">
+        <v>3</v>
+      </c>
+      <c r="D211" t="s">
+        <v>165</v>
+      </c>
+      <c r="E211" t="s">
+        <v>166</v>
+      </c>
+      <c r="F211" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="5">
+        <v>65</v>
+      </c>
+      <c r="D212" t="s">
+        <v>171</v>
+      </c>
+      <c r="E212" t="s">
+        <v>166</v>
+      </c>
+      <c r="F212" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5">
+        <v>2</v>
+      </c>
+      <c r="D213" t="s">
+        <v>165</v>
+      </c>
+      <c r="E213" t="s">
+        <v>166</v>
+      </c>
+      <c r="F213" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="5">
+        <v>5</v>
+      </c>
+      <c r="D214" t="s">
+        <v>168</v>
+      </c>
+      <c r="E214" t="s">
+        <v>166</v>
+      </c>
+      <c r="F214" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="5">
+        <v>6</v>
+      </c>
+      <c r="D215" t="s">
+        <v>169</v>
+      </c>
+      <c r="E215" t="s">
+        <v>170</v>
+      </c>
+      <c r="F215" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="5">
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>169</v>
+      </c>
+      <c r="E216" t="s">
+        <v>173</v>
+      </c>
+      <c r="F216" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="5">
+        <v>7</v>
+      </c>
+      <c r="D217" t="s">
+        <v>174</v>
+      </c>
+      <c r="E217" t="s">
+        <v>166</v>
+      </c>
+      <c r="F217" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="5">
+        <v>332</v>
+      </c>
+      <c r="D218" t="s">
+        <v>168</v>
+      </c>
+      <c r="E218" t="s">
+        <v>166</v>
+      </c>
+      <c r="F218" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5">
+        <v>356</v>
+      </c>
+      <c r="D219" t="s">
+        <v>167</v>
+      </c>
+      <c r="E219" t="s">
+        <v>166</v>
+      </c>
+      <c r="F219" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" s="5">
+        <v>19</v>
+      </c>
+      <c r="D220" t="s">
+        <v>165</v>
+      </c>
+      <c r="E220" t="s">
+        <v>166</v>
+      </c>
+      <c r="F220" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="5">
+        <v>3</v>
+      </c>
+      <c r="D221" t="s">
+        <v>169</v>
+      </c>
+      <c r="E221" t="s">
+        <v>175</v>
+      </c>
+      <c r="F221" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="5">
+        <v>11</v>
+      </c>
+      <c r="D222" t="s">
+        <v>171</v>
+      </c>
+      <c r="E222" t="s">
+        <v>166</v>
+      </c>
+      <c r="F222" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="5">
+        <v>3</v>
+      </c>
+      <c r="D223" t="s">
+        <v>165</v>
+      </c>
+      <c r="E223" t="s">
+        <v>166</v>
+      </c>
+      <c r="F223" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="5">
+        <v>1</v>
+      </c>
+      <c r="D224" t="s">
+        <v>169</v>
+      </c>
+      <c r="E224" t="s">
+        <v>173</v>
+      </c>
+      <c r="F224" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="5">
+        <v>2</v>
+      </c>
+      <c r="D225" t="s">
+        <v>165</v>
+      </c>
+      <c r="E225" t="s">
+        <v>166</v>
+      </c>
+      <c r="F225" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="5">
+        <v>8</v>
+      </c>
+      <c r="D226" t="s">
+        <v>165</v>
+      </c>
+      <c r="E226" t="s">
+        <v>166</v>
+      </c>
+      <c r="F226" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="5">
+        <v>11</v>
+      </c>
+      <c r="D227" t="s">
+        <v>165</v>
+      </c>
+      <c r="E227" t="s">
+        <v>166</v>
+      </c>
+      <c r="F227" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="5">
+        <v>51</v>
+      </c>
+      <c r="D228" t="s">
+        <v>167</v>
+      </c>
+      <c r="E228" t="s">
+        <v>166</v>
+      </c>
+      <c r="F228" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="5">
+        <v>0</v>
+      </c>
+      <c r="D229" t="s">
+        <v>165</v>
+      </c>
+      <c r="E229" t="s">
+        <v>166</v>
+      </c>
+      <c r="F229" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="5">
+        <v>53</v>
+      </c>
+      <c r="D230" t="s">
+        <v>171</v>
+      </c>
+      <c r="E230" t="s">
+        <v>166</v>
+      </c>
+      <c r="F230" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="5">
+        <v>91</v>
+      </c>
+      <c r="D231" t="s">
+        <v>167</v>
+      </c>
+      <c r="E231" t="s">
+        <v>166</v>
+      </c>
+      <c r="F231" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="5">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>169</v>
+      </c>
+      <c r="E232" t="s">
+        <v>170</v>
+      </c>
+      <c r="F232" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="5">
+        <v>3</v>
+      </c>
+      <c r="D233" t="s">
+        <v>169</v>
+      </c>
+      <c r="E233" t="s">
+        <v>170</v>
+      </c>
+      <c r="F233" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="5">
+        <v>32</v>
+      </c>
+      <c r="D234" t="s">
+        <v>165</v>
+      </c>
+      <c r="E234" t="s">
+        <v>166</v>
+      </c>
+      <c r="F234" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="5">
+        <v>0</v>
+      </c>
+      <c r="D235" t="s">
+        <v>165</v>
+      </c>
+      <c r="E235" t="s">
+        <v>166</v>
+      </c>
+      <c r="F235" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="5">
+        <v>184</v>
+      </c>
+      <c r="D236" t="s">
+        <v>171</v>
+      </c>
+      <c r="E236" t="s">
+        <v>166</v>
+      </c>
+      <c r="F236" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="5">
+        <v>32</v>
+      </c>
+      <c r="D237" t="s">
+        <v>169</v>
+      </c>
+      <c r="E237" t="s">
+        <v>175</v>
+      </c>
+      <c r="F237" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="5">
+        <v>2</v>
+      </c>
+      <c r="D238" t="s">
+        <v>165</v>
+      </c>
+      <c r="E238" t="s">
+        <v>166</v>
+      </c>
+      <c r="F238" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="5">
+        <v>69</v>
+      </c>
+      <c r="D239" t="s">
+        <v>168</v>
+      </c>
+      <c r="E239" t="s">
+        <v>166</v>
+      </c>
+      <c r="F239" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="5">
+        <v>65</v>
+      </c>
+      <c r="D240" t="s">
+        <v>165</v>
+      </c>
+      <c r="E240" t="s">
+        <v>166</v>
+      </c>
+      <c r="F240" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="5">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>169</v>
+      </c>
+      <c r="E241" t="s">
+        <v>170</v>
+      </c>
+      <c r="F241" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="5">
+        <v>2</v>
+      </c>
+      <c r="D242" t="s">
+        <v>174</v>
+      </c>
+      <c r="E242" t="s">
+        <v>166</v>
+      </c>
+      <c r="F242" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C243" s="5">
+        <v>5</v>
+      </c>
+      <c r="D243" t="s">
+        <v>165</v>
+      </c>
+      <c r="E243" t="s">
+        <v>166</v>
+      </c>
+      <c r="F243" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="5">
+        <v>6</v>
+      </c>
+      <c r="D244" t="s">
+        <v>174</v>
+      </c>
+      <c r="E244" t="s">
+        <v>166</v>
+      </c>
+      <c r="F244" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="5">
+        <v>1</v>
+      </c>
+      <c r="D245" t="s">
+        <v>169</v>
+      </c>
+      <c r="E245" t="s">
+        <v>170</v>
+      </c>
+      <c r="F245" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="5">
+        <v>8</v>
+      </c>
+      <c r="D246" t="s">
+        <v>174</v>
+      </c>
+      <c r="E246" t="s">
+        <v>166</v>
+      </c>
+      <c r="F246" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" s="5">
+        <v>7</v>
+      </c>
+      <c r="D247" t="s">
+        <v>165</v>
+      </c>
+      <c r="E247" t="s">
+        <v>166</v>
+      </c>
+      <c r="F247" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="5">
+        <v>0</v>
+      </c>
+      <c r="D248" t="s">
+        <v>165</v>
+      </c>
+      <c r="E248" t="s">
+        <v>166</v>
+      </c>
+      <c r="F248" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="5">
+        <v>11</v>
+      </c>
+      <c r="D249" t="s">
+        <v>171</v>
+      </c>
+      <c r="E249" t="s">
+        <v>166</v>
+      </c>
+      <c r="F249" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C250" s="5">
+        <v>15</v>
+      </c>
+      <c r="D250" t="s">
+        <v>174</v>
+      </c>
+      <c r="E250" t="s">
+        <v>166</v>
+      </c>
+      <c r="F250" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C251" s="5">
+        <v>24</v>
+      </c>
+      <c r="D251" t="s">
+        <v>169</v>
+      </c>
+      <c r="E251" t="s">
+        <v>172</v>
+      </c>
+      <c r="F251" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="5">
+        <v>7</v>
+      </c>
+      <c r="D252" t="s">
+        <v>165</v>
+      </c>
+      <c r="E252" t="s">
+        <v>166</v>
+      </c>
+      <c r="F252" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="5">
+        <v>3</v>
+      </c>
+      <c r="D253" t="s">
+        <v>165</v>
+      </c>
+      <c r="E253" t="s">
+        <v>166</v>
+      </c>
+      <c r="F253" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C254" s="5">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>174</v>
+      </c>
+      <c r="E254" t="s">
+        <v>166</v>
+      </c>
+      <c r="F254" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C255" s="5">
+        <v>9</v>
+      </c>
+      <c r="D255" t="s">
+        <v>168</v>
+      </c>
+      <c r="E255" t="s">
+        <v>166</v>
+      </c>
+      <c r="F255" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="5">
+        <v>6</v>
+      </c>
+      <c r="D256" t="s">
+        <v>174</v>
+      </c>
+      <c r="E256" t="s">
+        <v>166</v>
+      </c>
+      <c r="F256" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="5">
+        <v>2</v>
+      </c>
+      <c r="D257" t="s">
+        <v>165</v>
+      </c>
+      <c r="E257" t="s">
+        <v>166</v>
+      </c>
+      <c r="F257" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" s="5">
+        <v>1</v>
+      </c>
+      <c r="D258" t="s">
+        <v>169</v>
+      </c>
+      <c r="E258" t="s">
+        <v>170</v>
+      </c>
+      <c r="F258" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="5">
+        <v>9</v>
+      </c>
+      <c r="D259" t="s">
+        <v>171</v>
+      </c>
+      <c r="E259" t="s">
+        <v>166</v>
+      </c>
+      <c r="F259" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="5">
+        <v>52</v>
+      </c>
+      <c r="D260" t="s">
+        <v>165</v>
+      </c>
+      <c r="E260" t="s">
+        <v>166</v>
+      </c>
+      <c r="F260" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="5">
+        <v>202</v>
+      </c>
+      <c r="D261" t="s">
+        <v>169</v>
+      </c>
+      <c r="E261" t="s">
+        <v>173</v>
+      </c>
+      <c r="F261" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C262" s="5">
+        <v>1</v>
+      </c>
+      <c r="D262" t="s">
+        <v>165</v>
+      </c>
+      <c r="E262" t="s">
+        <v>166</v>
+      </c>
+      <c r="F262" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="5">
+        <v>62</v>
+      </c>
+      <c r="D263" t="s">
+        <v>165</v>
+      </c>
+      <c r="E263" t="s">
+        <v>166</v>
+      </c>
+      <c r="F263" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C264" s="5">
+        <v>1</v>
+      </c>
+      <c r="D264" t="s">
+        <v>169</v>
+      </c>
+      <c r="E264" t="s">
+        <v>170</v>
+      </c>
+      <c r="F264" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C265" s="5">
+        <v>9</v>
+      </c>
+      <c r="D265" t="s">
+        <v>174</v>
+      </c>
+      <c r="E265" t="s">
+        <v>166</v>
+      </c>
+      <c r="F265" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A266" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="5">
+        <v>3</v>
+      </c>
+      <c r="D266" t="s">
+        <v>174</v>
+      </c>
+      <c r="E266" t="s">
+        <v>166</v>
+      </c>
+      <c r="F266" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A267" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C267" s="5">
+        <v>43</v>
+      </c>
+      <c r="D267" t="s">
+        <v>165</v>
+      </c>
+      <c r="E267" t="s">
+        <v>166</v>
+      </c>
+      <c r="F267" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A268" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" s="5">
+        <v>14</v>
+      </c>
+      <c r="D268" t="s">
+        <v>165</v>
+      </c>
+      <c r="E268" t="s">
+        <v>166</v>
+      </c>
+      <c r="F268" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A269" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="5">
+        <v>251</v>
+      </c>
+      <c r="D269" t="s">
+        <v>167</v>
+      </c>
+      <c r="E269" t="s">
+        <v>166</v>
+      </c>
+      <c r="F269" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A270" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="5">
+        <v>0</v>
+      </c>
+      <c r="D270" t="s">
+        <v>169</v>
+      </c>
+      <c r="E270" t="s">
+        <v>170</v>
+      </c>
+      <c r="F270" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A271" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C271" s="5">
+        <v>13</v>
+      </c>
+      <c r="D271" t="s">
+        <v>165</v>
+      </c>
+      <c r="E271" t="s">
+        <v>166</v>
+      </c>
+      <c r="F271" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A272" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C272" s="5">
+        <v>12</v>
+      </c>
+      <c r="D272" t="s">
+        <v>167</v>
+      </c>
+      <c r="E272" t="s">
+        <v>166</v>
+      </c>
+      <c r="F272" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A273" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="5">
+        <v>3</v>
+      </c>
+      <c r="D273" t="s">
+        <v>169</v>
+      </c>
+      <c r="E273" t="s">
+        <v>173</v>
+      </c>
+      <c r="F273" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A274" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C274" s="5">
+        <v>14</v>
+      </c>
+      <c r="D274" t="s">
+        <v>167</v>
+      </c>
+      <c r="E274" t="s">
+        <v>166</v>
+      </c>
+      <c r="F274" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A275" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="5">
+        <v>3</v>
+      </c>
+      <c r="D275" t="s">
+        <v>167</v>
+      </c>
+      <c r="E275" t="s">
+        <v>166</v>
+      </c>
+      <c r="F275" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A276" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C276" s="5">
+        <v>9</v>
+      </c>
+      <c r="D276" t="s">
+        <v>165</v>
+      </c>
+      <c r="E276" t="s">
+        <v>166</v>
+      </c>
+      <c r="F276" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C277" s="5">
+        <v>3</v>
+      </c>
+      <c r="D277" t="s">
+        <v>165</v>
+      </c>
+      <c r="E277" t="s">
+        <v>166</v>
+      </c>
+      <c r="F277" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A278" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="5">
+        <v>1</v>
+      </c>
+      <c r="D278" t="s">
+        <v>169</v>
+      </c>
+      <c r="E278" t="s">
+        <v>172</v>
+      </c>
+      <c r="F278" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A279" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C279" s="5">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>165</v>
+      </c>
+      <c r="E279" t="s">
+        <v>166</v>
+      </c>
+      <c r="F279" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A280" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C280" s="5">
+        <v>20</v>
+      </c>
+      <c r="D280" t="s">
+        <v>169</v>
+      </c>
+      <c r="E280" t="s">
+        <v>175</v>
+      </c>
+      <c r="F280" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="5">
+        <v>11</v>
+      </c>
+      <c r="D281" t="s">
+        <v>169</v>
+      </c>
+      <c r="E281" t="s">
+        <v>172</v>
+      </c>
+      <c r="F281" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A282" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C282" s="5">
+        <v>128</v>
+      </c>
+      <c r="D282" t="s">
+        <v>168</v>
+      </c>
+      <c r="E282" t="s">
+        <v>166</v>
+      </c>
+      <c r="F282" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A283" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C283" s="5">
+        <v>174</v>
+      </c>
+      <c r="D283" t="s">
+        <v>168</v>
+      </c>
+      <c r="E283" t="s">
+        <v>166</v>
+      </c>
+      <c r="F283" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A284" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C284" s="5">
+        <v>4</v>
+      </c>
+      <c r="D284" t="s">
+        <v>165</v>
+      </c>
+      <c r="E284" t="s">
+        <v>166</v>
+      </c>
+      <c r="F284" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C285" s="5">
+        <v>27</v>
+      </c>
+      <c r="D285" t="s">
+        <v>165</v>
+      </c>
+      <c r="E285" t="s">
+        <v>166</v>
+      </c>
+      <c r="F285" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A286" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="5">
+        <v>4</v>
+      </c>
+      <c r="D286" t="s">
+        <v>169</v>
+      </c>
+      <c r="E286" t="s">
+        <v>175</v>
+      </c>
+      <c r="F286" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A287" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="5">
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>174</v>
+      </c>
+      <c r="E287" t="s">
+        <v>166</v>
+      </c>
+      <c r="F287" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A288" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="5">
+        <v>60</v>
+      </c>
+      <c r="D288" t="s">
+        <v>171</v>
+      </c>
+      <c r="E288" t="s">
+        <v>166</v>
+      </c>
+      <c r="F288" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A289" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="5">
+        <v>23</v>
+      </c>
+      <c r="D289" t="s">
+        <v>167</v>
+      </c>
+      <c r="E289" t="s">
+        <v>166</v>
+      </c>
+      <c r="F289" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A290" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="5">
+        <v>27</v>
+      </c>
+      <c r="D290" t="s">
+        <v>167</v>
+      </c>
+      <c r="E290" t="s">
+        <v>166</v>
+      </c>
+      <c r="F290" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A291" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="5">
+        <v>2</v>
+      </c>
+      <c r="D291" t="s">
+        <v>165</v>
+      </c>
+      <c r="E291" t="s">
+        <v>166</v>
+      </c>
+      <c r="F291" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C292" s="5">
+        <v>1</v>
+      </c>
+      <c r="D292" t="s">
+        <v>174</v>
+      </c>
+      <c r="E292" t="s">
+        <v>166</v>
+      </c>
+      <c r="F292" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C293" s="5">
+        <v>13</v>
+      </c>
+      <c r="D293" t="s">
+        <v>169</v>
+      </c>
+      <c r="E293" t="s">
+        <v>172</v>
+      </c>
+      <c r="F293" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C294" s="5">
+        <v>12</v>
+      </c>
+      <c r="D294" t="s">
+        <v>165</v>
+      </c>
+      <c r="E294" t="s">
+        <v>166</v>
+      </c>
+      <c r="F294" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A295" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="5">
+        <v>13</v>
+      </c>
+      <c r="D295" t="s">
+        <v>165</v>
+      </c>
+      <c r="E295" t="s">
+        <v>166</v>
+      </c>
+      <c r="F295" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A296" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="5">
+        <v>6</v>
+      </c>
+      <c r="D296" t="s">
+        <v>165</v>
+      </c>
+      <c r="E296" t="s">
+        <v>166</v>
+      </c>
+      <c r="F296" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A297" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="5">
+        <v>3</v>
+      </c>
+      <c r="D297" t="s">
+        <v>169</v>
+      </c>
+      <c r="E297" t="s">
+        <v>173</v>
+      </c>
+      <c r="F297" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A298" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C298" s="5">
+        <v>3</v>
+      </c>
+      <c r="D298" t="s">
+        <v>169</v>
+      </c>
+      <c r="E298" t="s">
+        <v>170</v>
+      </c>
+      <c r="F298" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A299" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C299" s="5">
+        <v>46</v>
+      </c>
+      <c r="D299" t="s">
+        <v>169</v>
+      </c>
+      <c r="E299" t="s">
+        <v>173</v>
+      </c>
+      <c r="F299" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A300" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="5">
+        <v>68</v>
+      </c>
+      <c r="D300" t="s">
+        <v>167</v>
+      </c>
+      <c r="E300" t="s">
+        <v>166</v>
+      </c>
+      <c r="F300" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A301" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="5">
+        <v>1</v>
+      </c>
+      <c r="D301" t="s">
+        <v>165</v>
+      </c>
+      <c r="E301" t="s">
+        <v>166</v>
+      </c>
+      <c r="F301" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A302" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C302" s="5">
+        <v>25</v>
+      </c>
+      <c r="D302" t="s">
+        <v>174</v>
+      </c>
+      <c r="E302" t="s">
+        <v>166</v>
+      </c>
+      <c r="F302" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A303" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="5">
+        <v>110</v>
+      </c>
+      <c r="D303" t="s">
+        <v>167</v>
+      </c>
+      <c r="E303" t="s">
+        <v>166</v>
+      </c>
+      <c r="F303" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A304" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="5">
+        <v>6</v>
+      </c>
+      <c r="D304" t="s">
+        <v>165</v>
+      </c>
+      <c r="E304" t="s">
+        <v>166</v>
+      </c>
+      <c r="F304" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A305" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="5">
+        <v>68</v>
+      </c>
+      <c r="D305" t="s">
+        <v>174</v>
+      </c>
+      <c r="E305" t="s">
+        <v>166</v>
+      </c>
+      <c r="F305" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A306" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="5">
+        <v>2</v>
+      </c>
+      <c r="D306" t="s">
+        <v>169</v>
+      </c>
+      <c r="E306" t="s">
+        <v>170</v>
+      </c>
+      <c r="F306" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A307" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="5">
+        <v>4</v>
+      </c>
+      <c r="D307" t="s">
+        <v>169</v>
+      </c>
+      <c r="E307" t="s">
+        <v>172</v>
+      </c>
+      <c r="F307" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A308" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="5">
+        <v>8</v>
+      </c>
+      <c r="D308" t="s">
+        <v>174</v>
+      </c>
+      <c r="E308" t="s">
+        <v>166</v>
+      </c>
+      <c r="F308" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A309" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C309" s="5">
+        <v>5</v>
+      </c>
+      <c r="D309" t="s">
+        <v>167</v>
+      </c>
+      <c r="E309" t="s">
+        <v>166</v>
+      </c>
+      <c r="F309" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A310" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="5">
+        <v>303</v>
+      </c>
+      <c r="D310" t="s">
+        <v>174</v>
+      </c>
+      <c r="E310" t="s">
+        <v>166</v>
+      </c>
+      <c r="F310" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A311" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="5">
+        <v>127</v>
+      </c>
+      <c r="D311" t="s">
+        <v>169</v>
+      </c>
+      <c r="E311" t="s">
+        <v>175</v>
+      </c>
+      <c r="F311" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A312" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="5">
+        <v>41</v>
+      </c>
+      <c r="D312" t="s">
+        <v>168</v>
+      </c>
+      <c r="E312" t="s">
+        <v>166</v>
+      </c>
+      <c r="F312" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A313" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="5">
+        <v>4</v>
+      </c>
+      <c r="D313" t="s">
+        <v>169</v>
+      </c>
+      <c r="E313" t="s">
+        <v>170</v>
+      </c>
+      <c r="F313" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A314" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="5">
+        <v>13</v>
+      </c>
+      <c r="D314" t="s">
+        <v>167</v>
+      </c>
+      <c r="E314" t="s">
+        <v>166</v>
+      </c>
+      <c r="F314" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A315" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="5">
+        <v>0</v>
+      </c>
+      <c r="D315" t="s">
+        <v>174</v>
+      </c>
+      <c r="E315" t="s">
+        <v>166</v>
+      </c>
+      <c r="F315" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A316" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="5">
+        <v>52</v>
+      </c>
+      <c r="D316" t="s">
+        <v>165</v>
+      </c>
+      <c r="E316" t="s">
+        <v>166</v>
+      </c>
+      <c r="F316" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A317" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="5">
+        <v>2</v>
+      </c>
+      <c r="D317" t="s">
+        <v>165</v>
+      </c>
+      <c r="E317" t="s">
+        <v>166</v>
+      </c>
+      <c r="F317" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A318" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="5">
+        <v>20</v>
+      </c>
+      <c r="D318" t="s">
+        <v>165</v>
+      </c>
+      <c r="E318" t="s">
+        <v>166</v>
+      </c>
+      <c r="F318" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A319" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="5">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>168</v>
+      </c>
+      <c r="E319" t="s">
+        <v>166</v>
+      </c>
+      <c r="F319" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A320" s="4"/>
       <c r="B320" s="2"/>
       <c r="C320" s="5"/>

--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CRM_Dominus_Entrega\crm_dominus\apps\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AA0724-5EF4-4AD9-9697-328003AA6425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716E2EFA-0601-4DEC-8E8A-8ADF1CFD1C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -528,9 +528,6 @@
     <t>coordenador</t>
   </si>
   <si>
-    <t>Maycon</t>
-  </si>
-  <si>
     <t>Demais coordenadores</t>
   </si>
   <si>
@@ -562,6 +559,9 @@
   </si>
   <si>
     <t>data_meta</t>
+  </si>
+  <si>
+    <t>Josiane</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -641,12 +641,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -662,6 +671,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1047,24 +1059,24 @@
         <v>164</v>
       </c>
       <c r="F1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
         <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F2" s="6">
         <v>45802</v>
@@ -1074,17 +1086,17 @@
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="B3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E3" t="s">
-        <v>166</v>
+      <c r="D3" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F3" s="6">
         <v>45802</v>
@@ -1094,17 +1106,17 @@
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" t="s">
-        <v>166</v>
+      <c r="D4" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F4" s="6">
         <v>45802</v>
@@ -1114,17 +1126,17 @@
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="B5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>167</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F5" s="6">
         <v>45802</v>
@@ -1134,17 +1146,17 @@
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E6" t="s">
-        <v>166</v>
+      <c r="D6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F6" s="6">
         <v>45802</v>
@@ -1154,37 +1166,37 @@
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4">
         <v>143</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E7" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="6">
-        <v>45802</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="5">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="E8" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E8" t="s">
-        <v>170</v>
       </c>
       <c r="F8" s="6">
         <v>45802</v>
@@ -1194,17 +1206,17 @@
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5">
+      <c r="B9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E9" t="s">
-        <v>170</v>
       </c>
       <c r="F9" s="6">
         <v>45802</v>
@@ -1214,17 +1226,17 @@
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
         <v>0</v>
       </c>
-      <c r="D10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E10" t="s">
-        <v>166</v>
+      <c r="D10" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F10" s="6">
         <v>45802</v>
@@ -1234,17 +1246,17 @@
       <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="5">
+      <c r="B11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
         <v>1</v>
       </c>
-      <c r="D11" t="s">
-        <v>169</v>
-      </c>
-      <c r="E11" t="s">
-        <v>172</v>
+      <c r="D11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F11" s="6">
         <v>45802</v>
@@ -1254,17 +1266,17 @@
       <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E12" t="s">
-        <v>173</v>
+      <c r="D12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F12" s="6">
         <v>45802</v>
@@ -1274,17 +1286,17 @@
       <c r="A13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="5">
+      <c r="B13" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="4">
         <v>119</v>
       </c>
-      <c r="D13" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" t="s">
-        <v>166</v>
+      <c r="D13" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F13" s="6">
         <v>45802</v>
@@ -1294,17 +1306,17 @@
       <c r="A14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
         <v>2</v>
       </c>
-      <c r="D14" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" t="s">
-        <v>166</v>
+      <c r="D14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F14" s="6">
         <v>45802</v>
@@ -1314,17 +1326,17 @@
       <c r="A15" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="4">
         <v>1</v>
       </c>
-      <c r="D15" t="s">
-        <v>165</v>
-      </c>
-      <c r="E15" t="s">
-        <v>166</v>
+      <c r="D15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F15" s="6">
         <v>45802</v>
@@ -1334,17 +1346,17 @@
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="B16" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4">
         <v>1</v>
       </c>
-      <c r="D16" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" t="s">
-        <v>166</v>
+      <c r="D16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F16" s="6">
         <v>45802</v>
@@ -1354,17 +1366,17 @@
       <c r="A17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="5">
+      <c r="B17" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="4">
         <v>11</v>
       </c>
-      <c r="D17" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F17" s="6">
         <v>45802</v>
@@ -1374,17 +1386,17 @@
       <c r="A18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="B18" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="4">
         <v>76</v>
       </c>
-      <c r="D18" t="s">
-        <v>168</v>
-      </c>
-      <c r="E18" t="s">
-        <v>166</v>
+      <c r="D18" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F18" s="6">
         <v>45802</v>
@@ -1394,17 +1406,17 @@
       <c r="A19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="5">
+      <c r="B19" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4">
         <v>16</v>
       </c>
-      <c r="D19" t="s">
-        <v>165</v>
-      </c>
-      <c r="E19" t="s">
-        <v>166</v>
+      <c r="D19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F19" s="6">
         <v>45802</v>
@@ -1414,17 +1426,17 @@
       <c r="A20" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4">
         <v>2</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E20" t="s">
-        <v>170</v>
       </c>
       <c r="F20" s="6">
         <v>45802</v>
@@ -1434,17 +1446,17 @@
       <c r="A21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="5">
+      <c r="B21" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="4">
         <v>5</v>
       </c>
-      <c r="D21" t="s">
-        <v>165</v>
-      </c>
-      <c r="E21" t="s">
-        <v>166</v>
+      <c r="D21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F21" s="6">
         <v>45802</v>
@@ -1454,17 +1466,17 @@
       <c r="A22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="5">
+      <c r="B22" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="4">
         <v>108</v>
       </c>
-      <c r="D22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E22" t="s">
-        <v>166</v>
+      <c r="D22" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F22" s="6">
         <v>45802</v>
@@ -1474,17 +1486,17 @@
       <c r="A23" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="5">
+      <c r="B23" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4">
         <v>55</v>
       </c>
-      <c r="D23" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="D23" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F23" s="6">
         <v>45802</v>
@@ -1494,17 +1506,17 @@
       <c r="A24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B24" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="4">
         <v>28</v>
       </c>
-      <c r="D24" t="s">
-        <v>168</v>
-      </c>
-      <c r="E24" t="s">
-        <v>166</v>
+      <c r="D24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F24" s="6">
         <v>45802</v>
@@ -1514,17 +1526,17 @@
       <c r="A25" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="B25" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="4">
         <v>33</v>
       </c>
-      <c r="D25" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" t="s">
-        <v>172</v>
+      <c r="D25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F25" s="6">
         <v>45802</v>
@@ -1534,17 +1546,17 @@
       <c r="A26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="5">
-        <v>3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>168</v>
-      </c>
-      <c r="E26" t="s">
-        <v>166</v>
+      <c r="B26" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="4">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F26" s="6">
         <v>45802</v>
@@ -1554,17 +1566,17 @@
       <c r="A27" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="5">
+      <c r="B27" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="4">
         <v>1</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E27" t="s">
-        <v>170</v>
       </c>
       <c r="F27" s="6">
         <v>45802</v>
@@ -1574,17 +1586,17 @@
       <c r="A28" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="5">
+      <c r="B28" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="4">
         <v>82</v>
       </c>
-      <c r="D28" t="s">
-        <v>174</v>
-      </c>
-      <c r="E28" t="s">
-        <v>166</v>
+      <c r="D28" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F28" s="6">
         <v>45802</v>
@@ -1594,17 +1606,17 @@
       <c r="A29" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C29" s="5">
+      <c r="B29" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C29" s="4">
         <v>46</v>
       </c>
-      <c r="D29" t="s">
-        <v>167</v>
-      </c>
-      <c r="E29" t="s">
+      <c r="D29" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F29" s="6">
         <v>45802</v>
@@ -1614,17 +1626,17 @@
       <c r="A30" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="4">
         <v>121</v>
       </c>
-      <c r="D30" t="s">
-        <v>168</v>
-      </c>
-      <c r="E30" t="s">
-        <v>166</v>
+      <c r="D30" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F30" s="6">
         <v>45802</v>
@@ -1634,17 +1646,17 @@
       <c r="A31" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="5">
+      <c r="B31" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="4">
         <v>2</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E31" t="s">
-        <v>170</v>
       </c>
       <c r="F31" s="6">
         <v>45802</v>
@@ -1654,17 +1666,17 @@
       <c r="A32" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="5">
+      <c r="B32" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4">
         <v>521</v>
       </c>
-      <c r="D32" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" t="s">
-        <v>166</v>
+      <c r="D32" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F32" s="6">
         <v>45802</v>
@@ -1674,17 +1686,17 @@
       <c r="A33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C33" s="5">
+      <c r="B33" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="4">
         <v>1</v>
       </c>
-      <c r="D33" t="s">
-        <v>169</v>
-      </c>
-      <c r="E33" t="s">
-        <v>173</v>
+      <c r="D33" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F33" s="6">
         <v>45802</v>
@@ -1694,17 +1706,17 @@
       <c r="A34" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="B34" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4">
         <v>45</v>
       </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>166</v>
+      <c r="D34" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F34" s="6">
         <v>45802</v>
@@ -1714,17 +1726,17 @@
       <c r="A35" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C35" s="5">
+      <c r="B35" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C35" s="4">
         <v>56</v>
       </c>
-      <c r="D35" t="s">
-        <v>165</v>
-      </c>
-      <c r="E35" t="s">
-        <v>166</v>
+      <c r="D35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F35" s="6">
         <v>45802</v>
@@ -1734,17 +1746,17 @@
       <c r="A36" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="B36" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="4">
         <v>2</v>
       </c>
-      <c r="D36" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" t="s">
-        <v>166</v>
+      <c r="D36" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F36" s="6">
         <v>45802</v>
@@ -1754,17 +1766,17 @@
       <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C37" s="5">
+      <c r="B37" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="4">
         <v>14</v>
       </c>
-      <c r="D37" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" t="s">
-        <v>166</v>
+      <c r="D37" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F37" s="6">
         <v>45802</v>
@@ -1774,17 +1786,17 @@
       <c r="A38" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="5">
+      <c r="B38" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4">
         <v>41</v>
       </c>
-      <c r="D38" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" t="s">
-        <v>166</v>
+      <c r="D38" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F38" s="6">
         <v>45802</v>
@@ -1794,17 +1806,17 @@
       <c r="A39" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C39" s="5">
+      <c r="B39" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39" s="4">
         <v>1</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E39" t="s">
-        <v>170</v>
       </c>
       <c r="F39" s="6">
         <v>45802</v>
@@ -1814,17 +1826,17 @@
       <c r="A40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="5">
+      <c r="B40" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4">
         <v>55</v>
       </c>
-      <c r="D40" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" t="s">
-        <v>166</v>
+      <c r="D40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F40" s="6">
         <v>45802</v>
@@ -1834,37 +1846,37 @@
       <c r="A41" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="5">
+      <c r="B41" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="4">
         <v>21</v>
       </c>
-      <c r="D41" t="s">
-        <v>165</v>
-      </c>
-      <c r="E41" t="s">
-        <v>166</v>
+      <c r="D41" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F41" s="6">
         <v>45802</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5">
-        <v>3</v>
-      </c>
-      <c r="D42" t="s">
-        <v>165</v>
-      </c>
-      <c r="E42" t="s">
-        <v>166</v>
+      <c r="B42" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F42" s="6">
         <v>45802</v>
@@ -1874,17 +1886,17 @@
       <c r="A43" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C43" s="5">
+      <c r="B43" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C43" s="4">
         <v>125</v>
       </c>
-      <c r="D43" t="s">
-        <v>174</v>
-      </c>
-      <c r="E43" t="s">
-        <v>166</v>
+      <c r="D43" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F43" s="6">
         <v>45802</v>
@@ -1894,17 +1906,17 @@
       <c r="A44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="5">
-        <v>3</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="B44" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4">
+        <v>3</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E44" t="s">
-        <v>170</v>
       </c>
       <c r="F44" s="6">
         <v>45802</v>
@@ -1914,17 +1926,17 @@
       <c r="A45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45" s="5">
+      <c r="B45" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="4">
         <v>1</v>
       </c>
-      <c r="D45" t="s">
-        <v>165</v>
-      </c>
-      <c r="E45" t="s">
-        <v>166</v>
+      <c r="D45" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F45" s="6">
         <v>45802</v>
@@ -1934,17 +1946,17 @@
       <c r="A46" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="5">
-        <v>3</v>
-      </c>
-      <c r="D46" t="s">
-        <v>169</v>
-      </c>
-      <c r="E46" t="s">
-        <v>173</v>
+      <c r="B46" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="4">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F46" s="6">
         <v>45802</v>
@@ -1954,17 +1966,17 @@
       <c r="A47" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="5">
+      <c r="B47" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="4">
         <v>199</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E47" t="s">
-        <v>170</v>
       </c>
       <c r="F47" s="6">
         <v>45802</v>
@@ -1974,17 +1986,17 @@
       <c r="A48" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C48" s="5">
-        <v>3</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="B48" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C48" s="4">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E48" t="s">
-        <v>170</v>
       </c>
       <c r="F48" s="6">
         <v>45802</v>
@@ -1994,17 +2006,17 @@
       <c r="A49" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="5">
+      <c r="B49" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="4">
         <v>2</v>
       </c>
-      <c r="D49" t="s">
-        <v>169</v>
-      </c>
-      <c r="E49" t="s">
-        <v>173</v>
+      <c r="D49" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F49" s="6">
         <v>45802</v>
@@ -2014,17 +2026,17 @@
       <c r="A50" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="5">
+      <c r="B50" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="4">
         <v>8</v>
       </c>
-      <c r="D50" t="s">
-        <v>168</v>
-      </c>
-      <c r="E50" t="s">
-        <v>166</v>
+      <c r="D50" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F50" s="6">
         <v>45802</v>
@@ -2034,17 +2046,17 @@
       <c r="A51" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C51" s="5">
+      <c r="B51" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="4">
         <v>68</v>
       </c>
-      <c r="D51" t="s">
-        <v>168</v>
-      </c>
-      <c r="E51" t="s">
-        <v>166</v>
+      <c r="D51" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F51" s="6">
         <v>45802</v>
@@ -2054,17 +2066,17 @@
       <c r="A52" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="5">
+      <c r="B52" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="4">
         <v>4</v>
       </c>
-      <c r="D52" t="s">
-        <v>165</v>
-      </c>
-      <c r="E52" t="s">
-        <v>166</v>
+      <c r="D52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F52" s="6">
         <v>45802</v>
@@ -2074,17 +2086,17 @@
       <c r="A53" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="5">
+      <c r="B53" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="4">
         <v>85</v>
       </c>
-      <c r="D53" t="s">
-        <v>171</v>
-      </c>
-      <c r="E53" t="s">
-        <v>166</v>
+      <c r="D53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F53" s="6">
         <v>45802</v>
@@ -2094,17 +2106,17 @@
       <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="5">
+      <c r="B54" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="4">
         <v>2</v>
       </c>
-      <c r="D54" t="s">
-        <v>165</v>
-      </c>
-      <c r="E54" t="s">
-        <v>166</v>
+      <c r="D54" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F54" s="6">
         <v>45802</v>
@@ -2114,17 +2126,17 @@
       <c r="A55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C55" s="5">
+      <c r="B55" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="4">
         <v>6</v>
       </c>
-      <c r="D55" t="s">
-        <v>168</v>
-      </c>
-      <c r="E55" t="s">
-        <v>166</v>
+      <c r="D55" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F55" s="6">
         <v>45802</v>
@@ -2134,17 +2146,17 @@
       <c r="A56" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C56" s="5">
+      <c r="B56" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="4">
         <v>8</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D56" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E56" t="s">
-        <v>170</v>
       </c>
       <c r="F56" s="6">
         <v>45802</v>
@@ -2154,17 +2166,17 @@
       <c r="A57" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="5">
+      <c r="B57" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="4">
         <v>15</v>
       </c>
-      <c r="D57" t="s">
-        <v>169</v>
-      </c>
-      <c r="E57" t="s">
-        <v>173</v>
+      <c r="D57" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F57" s="6">
         <v>45802</v>
@@ -2174,17 +2186,17 @@
       <c r="A58" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="5">
+      <c r="B58" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="4">
         <v>9</v>
       </c>
-      <c r="D58" t="s">
-        <v>174</v>
-      </c>
-      <c r="E58" t="s">
-        <v>166</v>
+      <c r="D58" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F58" s="6">
         <v>45802</v>
@@ -2194,17 +2206,17 @@
       <c r="A59" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C59" s="5">
+      <c r="B59" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="4">
         <v>303</v>
       </c>
-      <c r="D59" t="s">
-        <v>168</v>
-      </c>
-      <c r="E59" t="s">
-        <v>166</v>
+      <c r="D59" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F59" s="6">
         <v>45802</v>
@@ -2214,17 +2226,17 @@
       <c r="A60" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C60" s="5">
+      <c r="B60" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="4">
         <v>355</v>
       </c>
-      <c r="D60" t="s">
-        <v>167</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="D60" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F60" s="6">
         <v>45802</v>
@@ -2234,17 +2246,17 @@
       <c r="A61" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="5">
+      <c r="B61" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="4">
         <v>19</v>
       </c>
-      <c r="D61" t="s">
-        <v>165</v>
-      </c>
-      <c r="E61" t="s">
-        <v>166</v>
+      <c r="D61" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F61" s="6">
         <v>45802</v>
@@ -2254,17 +2266,17 @@
       <c r="A62" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C62" s="5">
+      <c r="B62" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="4">
         <v>4</v>
       </c>
-      <c r="D62" t="s">
-        <v>169</v>
-      </c>
-      <c r="E62" t="s">
-        <v>175</v>
+      <c r="D62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F62" s="6">
         <v>45802</v>
@@ -2274,17 +2286,17 @@
       <c r="A63" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C63" s="5">
+      <c r="B63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="4">
         <v>11</v>
       </c>
-      <c r="D63" t="s">
-        <v>171</v>
-      </c>
-      <c r="E63" t="s">
-        <v>166</v>
+      <c r="D63" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F63" s="6">
         <v>45802</v>
@@ -2294,17 +2306,17 @@
       <c r="A64" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C64" s="5">
-        <v>3</v>
-      </c>
-      <c r="D64" t="s">
-        <v>165</v>
-      </c>
-      <c r="E64" t="s">
-        <v>166</v>
+      <c r="B64" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C64" s="4">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F64" s="6">
         <v>45802</v>
@@ -2314,17 +2326,17 @@
       <c r="A65" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C65" s="5">
+      <c r="B65" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" s="4">
         <v>1</v>
       </c>
-      <c r="D65" t="s">
-        <v>169</v>
-      </c>
-      <c r="E65" t="s">
-        <v>173</v>
+      <c r="D65" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F65" s="6">
         <v>45802</v>
@@ -2334,17 +2346,17 @@
       <c r="A66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C66" s="5">
+      <c r="B66" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C66" s="4">
         <v>2</v>
       </c>
-      <c r="D66" t="s">
-        <v>165</v>
-      </c>
-      <c r="E66" t="s">
-        <v>166</v>
+      <c r="D66" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F66" s="6">
         <v>45802</v>
@@ -2354,17 +2366,17 @@
       <c r="A67" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C67" s="5">
+      <c r="B67" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="4">
         <v>10</v>
       </c>
-      <c r="D67" t="s">
-        <v>165</v>
-      </c>
-      <c r="E67" t="s">
-        <v>166</v>
+      <c r="D67" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F67" s="6">
         <v>45802</v>
@@ -2374,17 +2386,17 @@
       <c r="A68" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C68" s="5">
+      <c r="B68" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="4">
         <v>15</v>
       </c>
-      <c r="D68" t="s">
-        <v>165</v>
-      </c>
-      <c r="E68" t="s">
-        <v>166</v>
+      <c r="D68" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F68" s="6">
         <v>45802</v>
@@ -2394,17 +2406,17 @@
       <c r="A69" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C69" s="5">
+      <c r="B69" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" s="4">
         <v>51</v>
       </c>
-      <c r="D69" t="s">
-        <v>167</v>
-      </c>
-      <c r="E69" t="s">
+      <c r="D69" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F69" s="6">
         <v>45802</v>
@@ -2414,17 +2426,17 @@
       <c r="A70" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="5">
+      <c r="B70" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="4">
         <v>1</v>
       </c>
-      <c r="D70" t="s">
-        <v>165</v>
-      </c>
-      <c r="E70" t="s">
-        <v>166</v>
+      <c r="D70" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F70" s="6">
         <v>45802</v>
@@ -2434,17 +2446,17 @@
       <c r="A71" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C71" s="5">
+      <c r="B71" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="4">
         <v>40</v>
       </c>
-      <c r="D71" t="s">
-        <v>171</v>
-      </c>
-      <c r="E71" t="s">
-        <v>166</v>
+      <c r="D71" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F71" s="6">
         <v>45802</v>
@@ -2454,17 +2466,17 @@
       <c r="A72" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="5">
+      <c r="B72" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="4">
         <v>95</v>
       </c>
-      <c r="D72" t="s">
-        <v>167</v>
-      </c>
-      <c r="E72" t="s">
+      <c r="D72" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F72" s="6">
         <v>45802</v>
@@ -2474,17 +2486,17 @@
       <c r="A73" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C73" s="5">
+      <c r="B73" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" s="4">
         <v>1</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D73" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E73" t="s">
-        <v>170</v>
       </c>
       <c r="F73" s="6">
         <v>45802</v>
@@ -2494,17 +2506,17 @@
       <c r="A74" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C74" s="5">
-        <v>3</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="B74" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="4">
+        <v>3</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E74" t="s">
-        <v>170</v>
       </c>
       <c r="F74" s="6">
         <v>45802</v>
@@ -2514,17 +2526,17 @@
       <c r="A75" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="5">
+      <c r="B75" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C75" s="4">
         <v>43</v>
       </c>
-      <c r="D75" t="s">
-        <v>165</v>
-      </c>
-      <c r="E75" t="s">
-        <v>166</v>
+      <c r="D75" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F75" s="6">
         <v>45802</v>
@@ -2534,17 +2546,17 @@
       <c r="A76" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="5">
+      <c r="B76" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="4">
         <v>0</v>
       </c>
-      <c r="D76" t="s">
-        <v>165</v>
-      </c>
-      <c r="E76" t="s">
-        <v>166</v>
+      <c r="D76" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F76" s="6">
         <v>45802</v>
@@ -2554,17 +2566,17 @@
       <c r="A77" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C77" s="5">
+      <c r="B77" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C77" s="4">
         <v>224</v>
       </c>
-      <c r="D77" t="s">
-        <v>171</v>
-      </c>
-      <c r="E77" t="s">
-        <v>166</v>
+      <c r="D77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F77" s="6">
         <v>45802</v>
@@ -2574,17 +2586,17 @@
       <c r="A78" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" s="5">
+      <c r="B78" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="4">
         <v>27</v>
       </c>
-      <c r="D78" t="s">
-        <v>169</v>
-      </c>
-      <c r="E78" t="s">
-        <v>175</v>
+      <c r="D78" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F78" s="6">
         <v>45802</v>
@@ -2594,17 +2606,17 @@
       <c r="A79" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C79" s="5">
-        <v>3</v>
-      </c>
-      <c r="D79" t="s">
-        <v>165</v>
-      </c>
-      <c r="E79" t="s">
-        <v>166</v>
+      <c r="B79" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="4">
+        <v>3</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F79" s="6">
         <v>45802</v>
@@ -2614,17 +2626,17 @@
       <c r="A80" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="5">
+      <c r="B80" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="4">
         <v>79</v>
       </c>
-      <c r="D80" t="s">
-        <v>168</v>
-      </c>
-      <c r="E80" t="s">
-        <v>166</v>
+      <c r="D80" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F80" s="6">
         <v>45802</v>
@@ -2634,17 +2646,17 @@
       <c r="A81" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C81" s="5">
+      <c r="B81" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C81" s="4">
         <v>69</v>
       </c>
-      <c r="D81" t="s">
-        <v>165</v>
-      </c>
-      <c r="E81" t="s">
-        <v>166</v>
+      <c r="D81" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F81" s="6">
         <v>45802</v>
@@ -2654,17 +2666,17 @@
       <c r="A82" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C82" s="5">
+      <c r="B82" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C82" s="4">
         <v>9</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D82" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E82" t="s">
-        <v>170</v>
       </c>
       <c r="F82" s="6">
         <v>45802</v>
@@ -2674,17 +2686,17 @@
       <c r="A83" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C83" s="5">
+      <c r="B83" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C83" s="4">
         <v>4</v>
       </c>
-      <c r="D83" t="s">
-        <v>174</v>
-      </c>
-      <c r="E83" t="s">
-        <v>166</v>
+      <c r="D83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F83" s="6">
         <v>45802</v>
@@ -2694,17 +2706,17 @@
       <c r="A84" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C84" s="5">
+      <c r="B84" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C84" s="4">
         <v>5</v>
       </c>
-      <c r="D84" t="s">
-        <v>165</v>
-      </c>
-      <c r="E84" t="s">
-        <v>166</v>
+      <c r="D84" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F84" s="6">
         <v>45802</v>
@@ -2714,17 +2726,17 @@
       <c r="A85" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C85" s="5">
+      <c r="B85" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C85" s="4">
         <v>6</v>
       </c>
-      <c r="D85" t="s">
-        <v>174</v>
-      </c>
-      <c r="E85" t="s">
-        <v>166</v>
+      <c r="D85" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F85" s="6">
         <v>45802</v>
@@ -2734,17 +2746,17 @@
       <c r="A86" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C86" s="5">
+      <c r="B86" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="4">
         <v>1</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D86" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E86" t="s">
-        <v>170</v>
       </c>
       <c r="F86" s="6">
         <v>45802</v>
@@ -2754,17 +2766,17 @@
       <c r="A87" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C87" s="5">
+      <c r="B87" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C87" s="4">
         <v>10</v>
       </c>
-      <c r="D87" t="s">
-        <v>174</v>
-      </c>
-      <c r="E87" t="s">
-        <v>166</v>
+      <c r="D87" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F87" s="6">
         <v>45802</v>
@@ -2774,17 +2786,17 @@
       <c r="A88" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C88" s="5">
+      <c r="B88" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C88" s="4">
         <v>9</v>
       </c>
-      <c r="D88" t="s">
-        <v>165</v>
-      </c>
-      <c r="E88" t="s">
-        <v>166</v>
+      <c r="D88" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F88" s="6">
         <v>45802</v>
@@ -2794,17 +2806,17 @@
       <c r="A89" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C89" s="5">
+      <c r="B89" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="4">
         <v>1</v>
       </c>
-      <c r="D89" t="s">
-        <v>165</v>
-      </c>
-      <c r="E89" t="s">
-        <v>166</v>
+      <c r="D89" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F89" s="6">
         <v>45802</v>
@@ -2814,17 +2826,17 @@
       <c r="A90" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C90" s="5">
+      <c r="B90" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C90" s="4">
         <v>13</v>
       </c>
-      <c r="D90" t="s">
-        <v>171</v>
-      </c>
-      <c r="E90" t="s">
-        <v>166</v>
+      <c r="D90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F90" s="6">
         <v>45802</v>
@@ -2834,17 +2846,17 @@
       <c r="A91" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C91" s="5">
+      <c r="B91" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C91" s="4">
         <v>12</v>
       </c>
-      <c r="D91" t="s">
-        <v>174</v>
-      </c>
-      <c r="E91" t="s">
-        <v>166</v>
+      <c r="D91" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F91" s="6">
         <v>45802</v>
@@ -2854,17 +2866,17 @@
       <c r="A92" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C92" s="5">
+      <c r="B92" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C92" s="4">
         <v>28</v>
       </c>
-      <c r="D92" t="s">
-        <v>169</v>
-      </c>
-      <c r="E92" t="s">
-        <v>172</v>
+      <c r="D92" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F92" s="6">
         <v>45802</v>
@@ -2874,17 +2886,17 @@
       <c r="A93" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C93" s="5">
+      <c r="B93" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C93" s="4">
         <v>9</v>
       </c>
-      <c r="D93" t="s">
-        <v>165</v>
-      </c>
-      <c r="E93" t="s">
-        <v>166</v>
+      <c r="D93" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F93" s="6">
         <v>45802</v>
@@ -2894,17 +2906,17 @@
       <c r="A94" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C94" s="5">
+      <c r="B94" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C94" s="4">
         <v>5</v>
       </c>
-      <c r="D94" t="s">
-        <v>165</v>
-      </c>
-      <c r="E94" t="s">
-        <v>166</v>
+      <c r="D94" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F94" s="6">
         <v>45802</v>
@@ -2914,37 +2926,37 @@
       <c r="A95" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C95" s="5">
+      <c r="B95" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C95" s="4">
         <v>6</v>
       </c>
-      <c r="D95" t="s">
-        <v>174</v>
-      </c>
-      <c r="E95" t="s">
-        <v>166</v>
+      <c r="D95" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F95" s="6">
         <v>45802</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C96" s="5">
+      <c r="B96" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C96" s="4">
         <v>10</v>
       </c>
-      <c r="D96" t="s">
-        <v>168</v>
-      </c>
-      <c r="E96" t="s">
-        <v>166</v>
+      <c r="D96" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F96" s="6">
         <v>45802</v>
@@ -2954,17 +2966,17 @@
       <c r="A97" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C97" s="5">
+      <c r="B97" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C97" s="4">
         <v>7</v>
       </c>
-      <c r="D97" t="s">
-        <v>174</v>
-      </c>
-      <c r="E97" t="s">
-        <v>166</v>
+      <c r="D97" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F97" s="6">
         <v>45802</v>
@@ -2974,17 +2986,17 @@
       <c r="A98" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C98" s="5">
-        <v>3</v>
-      </c>
-      <c r="D98" t="s">
-        <v>165</v>
-      </c>
-      <c r="E98" t="s">
-        <v>166</v>
+      <c r="B98" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C98" s="4">
+        <v>3</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F98" s="6">
         <v>45802</v>
@@ -2994,37 +3006,37 @@
       <c r="A99" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C99" s="5">
+      <c r="B99" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C99" s="4">
         <v>1</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" s="6">
+        <v>45802</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="4">
+        <v>12</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F99" s="6">
-        <v>45802</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="5">
-        <v>12</v>
-      </c>
-      <c r="D100" t="s">
-        <v>171</v>
-      </c>
-      <c r="E100" t="s">
-        <v>166</v>
+      <c r="E100" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F100" s="6">
         <v>45802</v>
@@ -3034,17 +3046,17 @@
       <c r="A101" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C101" s="5">
+      <c r="B101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="4">
         <v>64</v>
       </c>
-      <c r="D101" t="s">
-        <v>165</v>
-      </c>
-      <c r="E101" t="s">
-        <v>166</v>
+      <c r="D101" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F101" s="6">
         <v>45802</v>
@@ -3054,17 +3066,17 @@
       <c r="A102" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="5">
+      <c r="B102" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="4">
         <v>222</v>
       </c>
-      <c r="D102" t="s">
-        <v>169</v>
-      </c>
-      <c r="E102" t="s">
-        <v>173</v>
+      <c r="D102" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F102" s="6">
         <v>45802</v>
@@ -3074,17 +3086,17 @@
       <c r="A103" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C103" s="5">
+      <c r="B103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C103" s="4">
         <v>2</v>
       </c>
-      <c r="D103" t="s">
-        <v>165</v>
-      </c>
-      <c r="E103" t="s">
-        <v>166</v>
+      <c r="D103" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F103" s="6">
         <v>45802</v>
@@ -3094,17 +3106,17 @@
       <c r="A104" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="5">
+      <c r="B104" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="4">
         <v>70</v>
       </c>
-      <c r="D104" t="s">
-        <v>165</v>
-      </c>
-      <c r="E104" t="s">
-        <v>166</v>
+      <c r="D104" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F104" s="6">
         <v>45802</v>
@@ -3114,17 +3126,17 @@
       <c r="A105" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C105" s="5">
+      <c r="B105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C105" s="4">
         <v>1</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D105" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E105" t="s">
-        <v>170</v>
       </c>
       <c r="F105" s="6">
         <v>45802</v>
@@ -3134,17 +3146,17 @@
       <c r="A106" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="5">
+      <c r="B106" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="4">
         <v>9</v>
       </c>
-      <c r="D106" t="s">
-        <v>174</v>
-      </c>
-      <c r="E106" t="s">
-        <v>166</v>
+      <c r="D106" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F106" s="6">
         <v>45802</v>
@@ -3154,17 +3166,17 @@
       <c r="A107" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C107" s="5">
-        <v>3</v>
-      </c>
-      <c r="D107" t="s">
-        <v>174</v>
-      </c>
-      <c r="E107" t="s">
-        <v>166</v>
+      <c r="B107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C107" s="4">
+        <v>3</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F107" s="6">
         <v>45802</v>
@@ -3174,17 +3186,17 @@
       <c r="A108" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C108" s="5">
+      <c r="B108" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C108" s="4">
         <v>52</v>
       </c>
-      <c r="D108" t="s">
-        <v>165</v>
-      </c>
-      <c r="E108" t="s">
-        <v>166</v>
+      <c r="D108" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F108" s="6">
         <v>45802</v>
@@ -3194,17 +3206,17 @@
       <c r="A109" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C109" s="5">
+      <c r="B109" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C109" s="4">
         <v>17</v>
       </c>
-      <c r="D109" t="s">
-        <v>165</v>
-      </c>
-      <c r="E109" t="s">
-        <v>166</v>
+      <c r="D109" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F109" s="6">
         <v>45802</v>
@@ -3214,17 +3226,17 @@
       <c r="A110" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="5">
+      <c r="B110" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="4">
         <v>302</v>
       </c>
-      <c r="D110" t="s">
-        <v>167</v>
-      </c>
-      <c r="E110" t="s">
+      <c r="D110" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F110" s="6">
         <v>45802</v>
@@ -3234,17 +3246,17 @@
       <c r="A111" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C111" s="5">
+      <c r="B111" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C111" s="4">
         <v>1</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D111" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E111" t="s">
-        <v>170</v>
       </c>
       <c r="F111" s="6">
         <v>45802</v>
@@ -3254,17 +3266,17 @@
       <c r="A112" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C112" s="5">
+      <c r="B112" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C112" s="4">
         <v>14</v>
       </c>
-      <c r="D112" t="s">
-        <v>165</v>
-      </c>
-      <c r="E112" t="s">
-        <v>166</v>
+      <c r="D112" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F112" s="6">
         <v>45802</v>
@@ -3274,17 +3286,17 @@
       <c r="A113" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C113" s="5">
+      <c r="B113" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C113" s="4">
         <v>12</v>
       </c>
-      <c r="D113" t="s">
-        <v>167</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="D113" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F113" s="6">
         <v>45802</v>
@@ -3294,17 +3306,17 @@
       <c r="A114" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="5">
+      <c r="B114" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="4">
         <v>4</v>
       </c>
-      <c r="D114" t="s">
-        <v>169</v>
-      </c>
-      <c r="E114" t="s">
-        <v>173</v>
+      <c r="D114" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F114" s="6">
         <v>45802</v>
@@ -3314,17 +3326,17 @@
       <c r="A115" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C115" s="5">
+      <c r="B115" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C115" s="4">
         <v>14</v>
       </c>
-      <c r="D115" t="s">
-        <v>167</v>
-      </c>
-      <c r="E115" t="s">
+      <c r="D115" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F115" s="6">
         <v>45802</v>
@@ -3334,17 +3346,17 @@
       <c r="A116" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C116" s="5">
+      <c r="B116" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C116" s="4">
         <v>4</v>
       </c>
-      <c r="D116" t="s">
-        <v>167</v>
-      </c>
-      <c r="E116" t="s">
+      <c r="D116" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F116" s="6">
         <v>45802</v>
@@ -3354,17 +3366,17 @@
       <c r="A117" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C117" s="5">
+      <c r="B117" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C117" s="4">
         <v>6</v>
       </c>
-      <c r="D117" t="s">
-        <v>165</v>
-      </c>
-      <c r="E117" t="s">
-        <v>166</v>
+      <c r="D117" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F117" s="6">
         <v>45802</v>
@@ -3374,17 +3386,17 @@
       <c r="A118" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C118" s="5">
-        <v>3</v>
-      </c>
-      <c r="D118" t="s">
-        <v>165</v>
-      </c>
-      <c r="E118" t="s">
-        <v>166</v>
+      <c r="B118" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="4">
+        <v>3</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F118" s="6">
         <v>45802</v>
@@ -3394,17 +3406,17 @@
       <c r="A119" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C119" s="5">
+      <c r="B119" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C119" s="4">
         <v>1</v>
       </c>
-      <c r="D119" t="s">
-        <v>169</v>
-      </c>
-      <c r="E119" t="s">
-        <v>172</v>
+      <c r="D119" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F119" s="6">
         <v>45802</v>
@@ -3414,17 +3426,17 @@
       <c r="A120" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C120" s="5">
+      <c r="B120" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C120" s="4">
         <v>8</v>
       </c>
-      <c r="D120" t="s">
-        <v>165</v>
-      </c>
-      <c r="E120" t="s">
-        <v>166</v>
+      <c r="D120" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F120" s="6">
         <v>45802</v>
@@ -3434,17 +3446,17 @@
       <c r="A121" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C121" s="5">
+      <c r="B121" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C121" s="4">
         <v>17</v>
       </c>
-      <c r="D121" t="s">
-        <v>169</v>
-      </c>
-      <c r="E121" t="s">
-        <v>175</v>
+      <c r="D121" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F121" s="6">
         <v>45802</v>
@@ -3454,17 +3466,17 @@
       <c r="A122" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C122" s="5">
+      <c r="B122" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="4">
         <v>9</v>
       </c>
-      <c r="D122" t="s">
-        <v>169</v>
-      </c>
-      <c r="E122" t="s">
-        <v>172</v>
+      <c r="D122" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F122" s="6">
         <v>45802</v>
@@ -3474,17 +3486,17 @@
       <c r="A123" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C123" s="5">
+      <c r="B123" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C123" s="4">
         <v>152</v>
       </c>
-      <c r="D123" t="s">
-        <v>168</v>
-      </c>
-      <c r="E123" t="s">
-        <v>166</v>
+      <c r="D123" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F123" s="6">
         <v>45802</v>
@@ -3494,17 +3506,17 @@
       <c r="A124" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="5">
+      <c r="B124" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="4">
         <v>185</v>
       </c>
-      <c r="D124" t="s">
-        <v>168</v>
-      </c>
-      <c r="E124" t="s">
-        <v>166</v>
+      <c r="D124" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F124" s="6">
         <v>45802</v>
@@ -3514,17 +3526,17 @@
       <c r="A125" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C125" s="5">
+      <c r="B125" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C125" s="4">
         <v>5</v>
       </c>
-      <c r="D125" t="s">
-        <v>165</v>
-      </c>
-      <c r="E125" t="s">
-        <v>166</v>
+      <c r="D125" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F125" s="6">
         <v>45802</v>
@@ -3534,17 +3546,17 @@
       <c r="A126" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="5">
+      <c r="B126" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="4">
         <v>10</v>
       </c>
-      <c r="D126" t="s">
-        <v>165</v>
-      </c>
-      <c r="E126" t="s">
-        <v>166</v>
+      <c r="D126" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F126" s="6">
         <v>45802</v>
@@ -3554,17 +3566,17 @@
       <c r="A127" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C127" s="5">
-        <v>3</v>
-      </c>
-      <c r="D127" t="s">
-        <v>169</v>
-      </c>
-      <c r="E127" t="s">
-        <v>175</v>
+      <c r="B127" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C127" s="4">
+        <v>3</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F127" s="6">
         <v>45802</v>
@@ -3574,17 +3586,17 @@
       <c r="A128" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C128" s="5">
+      <c r="B128" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="4">
         <v>1</v>
       </c>
-      <c r="D128" t="s">
-        <v>174</v>
-      </c>
-      <c r="E128" t="s">
-        <v>166</v>
+      <c r="D128" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F128" s="6">
         <v>45802</v>
@@ -3594,17 +3606,17 @@
       <c r="A129" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C129" s="5">
+      <c r="B129" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C129" s="4">
         <v>49</v>
       </c>
-      <c r="D129" t="s">
-        <v>171</v>
-      </c>
-      <c r="E129" t="s">
-        <v>166</v>
+      <c r="D129" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F129" s="6">
         <v>45802</v>
@@ -3614,17 +3626,17 @@
       <c r="A130" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C130" s="5">
+      <c r="B130" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="4">
         <v>23</v>
       </c>
-      <c r="D130" t="s">
-        <v>167</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="D130" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F130" s="6">
         <v>45802</v>
@@ -3634,17 +3646,17 @@
       <c r="A131" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C131" s="5">
+      <c r="B131" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C131" s="4">
         <v>32</v>
       </c>
-      <c r="D131" t="s">
-        <v>167</v>
-      </c>
-      <c r="E131" t="s">
+      <c r="D131" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F131" s="6">
         <v>45802</v>
@@ -3654,17 +3666,17 @@
       <c r="A132" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C132" s="5">
-        <v>3</v>
-      </c>
-      <c r="D132" t="s">
-        <v>165</v>
-      </c>
-      <c r="E132" t="s">
-        <v>166</v>
+      <c r="B132" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="4">
+        <v>3</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F132" s="6">
         <v>45802</v>
@@ -3674,17 +3686,17 @@
       <c r="A133" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C133" s="5">
+      <c r="B133" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C133" s="4">
         <v>1</v>
       </c>
-      <c r="D133" t="s">
-        <v>174</v>
-      </c>
-      <c r="E133" t="s">
-        <v>166</v>
+      <c r="D133" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F133" s="6">
         <v>45802</v>
@@ -3694,17 +3706,17 @@
       <c r="A134" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="5">
+      <c r="B134" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="4">
         <v>14</v>
       </c>
-      <c r="D134" t="s">
-        <v>169</v>
-      </c>
-      <c r="E134" t="s">
-        <v>172</v>
+      <c r="D134" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F134" s="6">
         <v>45802</v>
@@ -3714,17 +3726,17 @@
       <c r="A135" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C135" s="5">
+      <c r="B135" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C135" s="4">
         <v>17</v>
       </c>
-      <c r="D135" t="s">
-        <v>165</v>
-      </c>
-      <c r="E135" t="s">
-        <v>166</v>
+      <c r="D135" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F135" s="6">
         <v>45802</v>
@@ -3734,17 +3746,17 @@
       <c r="A136" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C136" s="5">
+      <c r="B136" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="4">
         <v>16</v>
       </c>
-      <c r="D136" t="s">
-        <v>165</v>
-      </c>
-      <c r="E136" t="s">
-        <v>166</v>
+      <c r="D136" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F136" s="6">
         <v>45802</v>
@@ -3754,17 +3766,17 @@
       <c r="A137" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C137" s="5">
+      <c r="B137" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C137" s="4">
         <v>7</v>
       </c>
-      <c r="D137" t="s">
-        <v>165</v>
-      </c>
-      <c r="E137" t="s">
-        <v>166</v>
+      <c r="D137" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F137" s="6">
         <v>45802</v>
@@ -3774,17 +3786,17 @@
       <c r="A138" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C138" s="5">
-        <v>3</v>
-      </c>
-      <c r="D138" t="s">
-        <v>169</v>
-      </c>
-      <c r="E138" t="s">
-        <v>173</v>
+      <c r="B138" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="4">
+        <v>3</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F138" s="6">
         <v>45802</v>
@@ -3794,17 +3806,17 @@
       <c r="A139" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C139" s="5">
+      <c r="B139" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C139" s="4">
         <v>4</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D139" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E139" t="s">
-        <v>170</v>
       </c>
       <c r="F139" s="6">
         <v>45802</v>
@@ -3814,17 +3826,17 @@
       <c r="A140" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C140" s="5">
+      <c r="B140" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="4">
         <v>50</v>
       </c>
-      <c r="D140" t="s">
-        <v>169</v>
-      </c>
-      <c r="E140" t="s">
-        <v>173</v>
+      <c r="D140" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F140" s="6">
         <v>45802</v>
@@ -3834,17 +3846,17 @@
       <c r="A141" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C141" s="5">
+      <c r="B141" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C141" s="4">
         <v>58</v>
       </c>
-      <c r="D141" t="s">
-        <v>167</v>
-      </c>
-      <c r="E141" t="s">
+      <c r="D141" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F141" s="6">
         <v>45802</v>
@@ -3854,17 +3866,17 @@
       <c r="A142" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C142" s="5">
+      <c r="B142" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C142" s="4">
         <v>1</v>
       </c>
-      <c r="D142" t="s">
-        <v>165</v>
-      </c>
-      <c r="E142" t="s">
-        <v>166</v>
+      <c r="D142" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F142" s="6">
         <v>45802</v>
@@ -3874,17 +3886,17 @@
       <c r="A143" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C143" s="5">
+      <c r="B143" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C143" s="4">
         <v>23</v>
       </c>
-      <c r="D143" t="s">
-        <v>174</v>
-      </c>
-      <c r="E143" t="s">
-        <v>166</v>
+      <c r="D143" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F143" s="6">
         <v>45802</v>
@@ -3894,17 +3906,17 @@
       <c r="A144" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C144" s="5">
+      <c r="B144" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="4">
         <v>95</v>
       </c>
-      <c r="D144" t="s">
-        <v>167</v>
-      </c>
-      <c r="E144" t="s">
+      <c r="D144" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F144" s="6">
         <v>45802</v>
@@ -3914,17 +3926,17 @@
       <c r="A145" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C145" s="5">
+      <c r="B145" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C145" s="4">
         <v>6</v>
       </c>
-      <c r="D145" t="s">
-        <v>165</v>
-      </c>
-      <c r="E145" t="s">
-        <v>166</v>
+      <c r="D145" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F145" s="6">
         <v>45802</v>
@@ -3934,17 +3946,17 @@
       <c r="A146" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C146" s="5">
+      <c r="B146" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="4">
         <v>78</v>
       </c>
-      <c r="D146" t="s">
-        <v>174</v>
-      </c>
-      <c r="E146" t="s">
-        <v>166</v>
+      <c r="D146" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F146" s="6">
         <v>45802</v>
@@ -3954,17 +3966,17 @@
       <c r="A147" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C147" s="5">
-        <v>3</v>
-      </c>
-      <c r="D147" t="s">
+      <c r="B147" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C147" s="4">
+        <v>3</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E147" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E147" t="s">
-        <v>170</v>
       </c>
       <c r="F147" s="6">
         <v>45802</v>
@@ -3974,17 +3986,17 @@
       <c r="A148" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C148" s="5">
+      <c r="B148" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="4">
         <v>4</v>
       </c>
-      <c r="D148" t="s">
-        <v>169</v>
-      </c>
-      <c r="E148" t="s">
-        <v>172</v>
+      <c r="D148" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F148" s="6">
         <v>45802</v>
@@ -3994,17 +4006,17 @@
       <c r="A149" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C149" s="5">
+      <c r="B149" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C149" s="4">
         <v>8</v>
       </c>
-      <c r="D149" t="s">
-        <v>174</v>
-      </c>
-      <c r="E149" t="s">
-        <v>166</v>
+      <c r="D149" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F149" s="6">
         <v>45802</v>
@@ -4014,17 +4026,17 @@
       <c r="A150" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C150" s="5">
+      <c r="B150" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="4">
         <v>5</v>
       </c>
-      <c r="D150" t="s">
-        <v>167</v>
-      </c>
-      <c r="E150" t="s">
+      <c r="D150" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F150" s="6">
         <v>45802</v>
@@ -4034,17 +4046,17 @@
       <c r="A151" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C151" s="5">
+      <c r="B151" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C151" s="4">
         <v>308</v>
       </c>
-      <c r="D151" t="s">
-        <v>174</v>
-      </c>
-      <c r="E151" t="s">
-        <v>166</v>
+      <c r="D151" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F151" s="6">
         <v>45802</v>
@@ -4054,17 +4066,17 @@
       <c r="A152" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C152" s="5">
+      <c r="B152" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="4">
         <v>141</v>
       </c>
-      <c r="D152" t="s">
-        <v>169</v>
-      </c>
-      <c r="E152" t="s">
-        <v>175</v>
+      <c r="D152" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F152" s="6">
         <v>45802</v>
@@ -4074,17 +4086,17 @@
       <c r="A153" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C153" s="5">
+      <c r="B153" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C153" s="4">
         <v>39</v>
       </c>
-      <c r="D153" t="s">
-        <v>168</v>
-      </c>
-      <c r="E153" t="s">
-        <v>166</v>
+      <c r="D153" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F153" s="6">
         <v>45802</v>
@@ -4094,17 +4106,17 @@
       <c r="A154" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C154" s="5">
+      <c r="B154" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="4">
         <v>4</v>
       </c>
-      <c r="D154" t="s">
+      <c r="D154" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E154" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E154" t="s">
-        <v>170</v>
       </c>
       <c r="F154" s="6">
         <v>45802</v>
@@ -4114,17 +4126,17 @@
       <c r="A155" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C155" s="5">
+      <c r="B155" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C155" s="4">
         <v>13</v>
       </c>
-      <c r="D155" t="s">
-        <v>167</v>
-      </c>
-      <c r="E155" t="s">
+      <c r="D155" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F155" s="6">
         <v>45802</v>
@@ -4134,17 +4146,17 @@
       <c r="A156" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C156" s="5">
+      <c r="B156" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="4">
         <v>0</v>
       </c>
-      <c r="D156" t="s">
-        <v>174</v>
-      </c>
-      <c r="E156" t="s">
-        <v>166</v>
+      <c r="D156" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F156" s="6">
         <v>45802</v>
@@ -4154,17 +4166,17 @@
       <c r="A157" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C157" s="5">
+      <c r="B157" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C157" s="4">
         <v>55</v>
       </c>
-      <c r="D157" t="s">
-        <v>165</v>
-      </c>
-      <c r="E157" t="s">
-        <v>166</v>
+      <c r="D157" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F157" s="6">
         <v>45802</v>
@@ -4174,17 +4186,17 @@
       <c r="A158" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C158" s="5">
+      <c r="B158" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="4">
         <v>2</v>
       </c>
-      <c r="D158" t="s">
-        <v>165</v>
-      </c>
-      <c r="E158" t="s">
-        <v>166</v>
+      <c r="D158" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F158" s="6">
         <v>45802</v>
@@ -4194,17 +4206,17 @@
       <c r="A159" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C159" s="5">
+      <c r="B159" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C159" s="4">
         <v>14</v>
       </c>
-      <c r="D159" t="s">
-        <v>165</v>
-      </c>
-      <c r="E159" t="s">
-        <v>166</v>
+      <c r="D159" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F159" s="6">
         <v>45802</v>
@@ -4214,17 +4226,17 @@
       <c r="A160" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C160" s="5">
+      <c r="B160" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="4">
         <v>1</v>
       </c>
-      <c r="D160" t="s">
-        <v>168</v>
-      </c>
-      <c r="E160" t="s">
-        <v>166</v>
+      <c r="D160" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F160" s="6">
         <v>45802</v>
@@ -4234,17 +4246,17 @@
       <c r="A161" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C161" s="5">
+      <c r="B161" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C161" s="4">
         <v>17</v>
       </c>
-      <c r="D161" t="s">
-        <v>165</v>
-      </c>
-      <c r="E161" t="s">
-        <v>166</v>
+      <c r="D161" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F161" s="6">
         <v>45833</v>
@@ -4254,17 +4266,17 @@
       <c r="A162" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C162" s="5">
+      <c r="B162" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="4">
         <v>15</v>
       </c>
-      <c r="D162" t="s">
-        <v>165</v>
-      </c>
-      <c r="E162" t="s">
-        <v>166</v>
+      <c r="D162" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F162" s="6">
         <v>45833</v>
@@ -4274,17 +4286,17 @@
       <c r="A163" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C163" s="5">
-        <v>3</v>
-      </c>
-      <c r="D163" t="s">
-        <v>165</v>
-      </c>
-      <c r="E163" t="s">
-        <v>166</v>
+      <c r="B163" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C163" s="4">
+        <v>3</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F163" s="6">
         <v>45833</v>
@@ -4294,17 +4306,17 @@
       <c r="A164" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C164" s="5">
+      <c r="B164" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="4">
         <v>4</v>
       </c>
-      <c r="D164" t="s">
-        <v>167</v>
-      </c>
-      <c r="E164" t="s">
+      <c r="D164" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F164" s="6">
         <v>45833</v>
@@ -4314,17 +4326,17 @@
       <c r="A165" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C165" s="5">
+      <c r="B165" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="4">
         <v>0</v>
       </c>
-      <c r="D165" t="s">
-        <v>165</v>
-      </c>
-      <c r="E165" t="s">
-        <v>166</v>
+      <c r="D165" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F165" s="6">
         <v>45833</v>
@@ -4334,37 +4346,37 @@
       <c r="A166" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C166" s="5">
+      <c r="B166" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C166" s="4">
         <v>153</v>
       </c>
-      <c r="D166" t="s">
+      <c r="D166" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F166" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C167" s="4">
+        <v>9</v>
+      </c>
+      <c r="D167" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E166" t="s">
-        <v>166</v>
-      </c>
-      <c r="F166" s="6">
-        <v>45833</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C167" s="5">
-        <v>9</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="E167" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E167" t="s">
-        <v>170</v>
       </c>
       <c r="F167" s="6">
         <v>45833</v>
@@ -4374,17 +4386,17 @@
       <c r="A168" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C168" s="5">
+      <c r="B168" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C168" s="4">
         <v>1</v>
       </c>
-      <c r="D168" t="s">
+      <c r="D168" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E168" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E168" t="s">
-        <v>170</v>
       </c>
       <c r="F168" s="6">
         <v>45833</v>
@@ -4394,17 +4406,17 @@
       <c r="A169" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C169" s="5">
+      <c r="B169" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C169" s="4">
         <v>0</v>
       </c>
-      <c r="D169" t="s">
-        <v>171</v>
-      </c>
-      <c r="E169" t="s">
-        <v>166</v>
+      <c r="D169" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F169" s="6">
         <v>45833</v>
@@ -4414,17 +4426,17 @@
       <c r="A170" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C170" s="5">
+      <c r="B170" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="4">
         <v>0</v>
       </c>
-      <c r="D170" t="s">
-        <v>169</v>
-      </c>
-      <c r="E170" t="s">
-        <v>172</v>
+      <c r="D170" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F170" s="6">
         <v>45833</v>
@@ -4434,17 +4446,17 @@
       <c r="A171" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C171" s="5">
+      <c r="B171" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C171" s="4">
         <v>11</v>
       </c>
-      <c r="D171" t="s">
-        <v>169</v>
-      </c>
-      <c r="E171" t="s">
-        <v>173</v>
+      <c r="D171" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F171" s="6">
         <v>45833</v>
@@ -4454,17 +4466,17 @@
       <c r="A172" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C172" s="5">
+      <c r="B172" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C172" s="4">
         <v>111</v>
       </c>
-      <c r="D172" t="s">
-        <v>168</v>
-      </c>
-      <c r="E172" t="s">
-        <v>166</v>
+      <c r="D172" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F172" s="6">
         <v>45833</v>
@@ -4474,17 +4486,17 @@
       <c r="A173" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C173" s="5">
+      <c r="B173" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C173" s="4">
         <v>1</v>
       </c>
-      <c r="D173" t="s">
-        <v>171</v>
-      </c>
-      <c r="E173" t="s">
-        <v>166</v>
+      <c r="D173" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F173" s="6">
         <v>45833</v>
@@ -4494,17 +4506,17 @@
       <c r="A174" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C174" s="5">
+      <c r="B174" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" s="4">
         <v>1</v>
       </c>
-      <c r="D174" t="s">
-        <v>165</v>
-      </c>
-      <c r="E174" t="s">
-        <v>166</v>
+      <c r="D174" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F174" s="6">
         <v>45833</v>
@@ -4514,17 +4526,17 @@
       <c r="A175" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C175" s="5">
+      <c r="B175" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C175" s="4">
         <v>1</v>
       </c>
-      <c r="D175" t="s">
-        <v>165</v>
-      </c>
-      <c r="E175" t="s">
-        <v>166</v>
+      <c r="D175" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F175" s="6">
         <v>45833</v>
@@ -4534,17 +4546,17 @@
       <c r="A176" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C176" s="5">
+      <c r="B176" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C176" s="4">
         <v>10</v>
       </c>
-      <c r="D176" t="s">
-        <v>167</v>
-      </c>
-      <c r="E176" t="s">
+      <c r="D176" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F176" s="6">
         <v>45833</v>
@@ -4554,17 +4566,17 @@
       <c r="A177" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C177" s="5">
+      <c r="B177" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C177" s="4">
         <v>84</v>
       </c>
-      <c r="D177" t="s">
-        <v>168</v>
-      </c>
-      <c r="E177" t="s">
-        <v>166</v>
+      <c r="D177" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F177" s="6">
         <v>45833</v>
@@ -4574,17 +4586,17 @@
       <c r="A178" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C178" s="5">
+      <c r="B178" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="4">
         <v>15</v>
       </c>
-      <c r="D178" t="s">
-        <v>165</v>
-      </c>
-      <c r="E178" t="s">
-        <v>166</v>
+      <c r="D178" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F178" s="6">
         <v>45833</v>
@@ -4594,17 +4606,17 @@
       <c r="A179" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C179" s="5">
+      <c r="B179" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C179" s="4">
         <v>2</v>
       </c>
-      <c r="D179" t="s">
+      <c r="D179" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E179" t="s">
-        <v>170</v>
       </c>
       <c r="F179" s="6">
         <v>45833</v>
@@ -4614,17 +4626,17 @@
       <c r="A180" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C180" s="5">
+      <c r="B180" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C180" s="4">
         <v>4</v>
       </c>
-      <c r="D180" t="s">
-        <v>165</v>
-      </c>
-      <c r="E180" t="s">
-        <v>166</v>
+      <c r="D180" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F180" s="6">
         <v>45833</v>
@@ -4634,17 +4646,17 @@
       <c r="A181" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C181" s="5">
+      <c r="B181" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C181" s="4">
         <v>116</v>
       </c>
-      <c r="D181" t="s">
-        <v>168</v>
-      </c>
-      <c r="E181" t="s">
-        <v>166</v>
+      <c r="D181" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F181" s="6">
         <v>45833</v>
@@ -4654,17 +4666,17 @@
       <c r="A182" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C182" s="5">
+      <c r="B182" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C182" s="4">
         <v>51</v>
       </c>
-      <c r="D182" t="s">
-        <v>167</v>
-      </c>
-      <c r="E182" t="s">
+      <c r="D182" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F182" s="6">
         <v>45833</v>
@@ -4674,17 +4686,17 @@
       <c r="A183" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C183" s="5">
+      <c r="B183" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C183" s="4">
         <v>33</v>
       </c>
-      <c r="D183" t="s">
-        <v>168</v>
-      </c>
-      <c r="E183" t="s">
-        <v>166</v>
+      <c r="D183" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F183" s="6">
         <v>45833</v>
@@ -4694,17 +4706,17 @@
       <c r="A184" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C184" s="5">
+      <c r="B184" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C184" s="4">
         <v>32</v>
       </c>
-      <c r="D184" t="s">
-        <v>169</v>
-      </c>
-      <c r="E184" t="s">
-        <v>172</v>
+      <c r="D184" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F184" s="6">
         <v>45833</v>
@@ -4714,17 +4726,17 @@
       <c r="A185" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C185" s="5">
-        <v>3</v>
-      </c>
-      <c r="D185" t="s">
-        <v>168</v>
-      </c>
-      <c r="E185" t="s">
-        <v>166</v>
+      <c r="B185" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C185" s="4">
+        <v>3</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F185" s="6">
         <v>45833</v>
@@ -4734,17 +4746,17 @@
       <c r="A186" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C186" s="5">
+      <c r="B186" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C186" s="4">
         <v>0</v>
       </c>
-      <c r="D186" t="s">
+      <c r="D186" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E186" t="s">
-        <v>170</v>
       </c>
       <c r="F186" s="6">
         <v>45833</v>
@@ -4754,17 +4766,17 @@
       <c r="A187" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C187" s="5">
+      <c r="B187" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C187" s="4">
         <v>76</v>
       </c>
-      <c r="D187" t="s">
-        <v>174</v>
-      </c>
-      <c r="E187" t="s">
-        <v>166</v>
+      <c r="D187" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F187" s="6">
         <v>45833</v>
@@ -4774,17 +4786,17 @@
       <c r="A188" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C188" s="5">
+      <c r="B188" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C188" s="4">
         <v>45</v>
       </c>
-      <c r="D188" t="s">
-        <v>167</v>
-      </c>
-      <c r="E188" t="s">
+      <c r="D188" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F188" s="6">
         <v>45833</v>
@@ -4794,17 +4806,17 @@
       <c r="A189" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C189" s="5">
+      <c r="B189" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C189" s="4">
         <v>121</v>
       </c>
-      <c r="D189" t="s">
-        <v>168</v>
-      </c>
-      <c r="E189" t="s">
-        <v>166</v>
+      <c r="D189" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F189" s="6">
         <v>45833</v>
@@ -4814,17 +4826,17 @@
       <c r="A190" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C190" s="5">
+      <c r="B190" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C190" s="4">
         <v>2</v>
       </c>
-      <c r="D190" t="s">
+      <c r="D190" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E190" t="s">
-        <v>170</v>
       </c>
       <c r="F190" s="6">
         <v>45833</v>
@@ -4834,17 +4846,17 @@
       <c r="A191" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C191" s="5">
+      <c r="B191" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C191" s="4">
         <v>517</v>
       </c>
-      <c r="D191" t="s">
-        <v>165</v>
-      </c>
-      <c r="E191" t="s">
-        <v>166</v>
+      <c r="D191" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F191" s="6">
         <v>45833</v>
@@ -4854,17 +4866,17 @@
       <c r="A192" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C192" s="5">
+      <c r="B192" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C192" s="4">
         <v>1</v>
       </c>
-      <c r="D192" t="s">
-        <v>169</v>
-      </c>
-      <c r="E192" t="s">
-        <v>173</v>
+      <c r="D192" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F192" s="6">
         <v>45833</v>
@@ -4874,17 +4886,17 @@
       <c r="A193" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C193" s="5">
+      <c r="B193" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C193" s="4">
         <v>37</v>
       </c>
-      <c r="D193" t="s">
-        <v>165</v>
-      </c>
-      <c r="E193" t="s">
-        <v>166</v>
+      <c r="D193" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F193" s="6">
         <v>45833</v>
@@ -4894,17 +4906,17 @@
       <c r="A194" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C194" s="5">
+      <c r="B194" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C194" s="4">
         <v>54</v>
       </c>
-      <c r="D194" t="s">
-        <v>165</v>
-      </c>
-      <c r="E194" t="s">
-        <v>166</v>
+      <c r="D194" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F194" s="6">
         <v>45833</v>
@@ -4914,17 +4926,17 @@
       <c r="A195" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C195" s="5">
+      <c r="B195" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C195" s="4">
         <v>2</v>
       </c>
-      <c r="D195" t="s">
-        <v>165</v>
-      </c>
-      <c r="E195" t="s">
-        <v>166</v>
+      <c r="D195" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F195" s="6">
         <v>45833</v>
@@ -4934,17 +4946,17 @@
       <c r="A196" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C196" s="5">
+      <c r="B196" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C196" s="4">
         <v>11</v>
       </c>
-      <c r="D196" t="s">
-        <v>171</v>
-      </c>
-      <c r="E196" t="s">
-        <v>166</v>
+      <c r="D196" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F196" s="6">
         <v>45833</v>
@@ -4954,17 +4966,17 @@
       <c r="A197" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C197" s="5">
+      <c r="B197" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C197" s="4">
         <v>36</v>
       </c>
-      <c r="D197" t="s">
-        <v>171</v>
-      </c>
-      <c r="E197" t="s">
-        <v>166</v>
+      <c r="D197" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F197" s="6">
         <v>45833</v>
@@ -4974,17 +4986,17 @@
       <c r="A198" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C198" s="5">
+      <c r="B198" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C198" s="4">
         <v>1</v>
       </c>
-      <c r="D198" t="s">
+      <c r="D198" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E198" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E198" t="s">
-        <v>170</v>
       </c>
       <c r="F198" s="6">
         <v>45833</v>
@@ -4994,17 +5006,17 @@
       <c r="A199" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C199" s="5">
+      <c r="B199" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C199" s="4">
         <v>45</v>
       </c>
-      <c r="D199" t="s">
-        <v>174</v>
-      </c>
-      <c r="E199" t="s">
-        <v>166</v>
+      <c r="D199" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F199" s="6">
         <v>45833</v>
@@ -5014,17 +5026,17 @@
       <c r="A200" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5">
+      <c r="B200" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="4">
         <v>18</v>
       </c>
-      <c r="D200" t="s">
-        <v>165</v>
-      </c>
-      <c r="E200" t="s">
-        <v>166</v>
+      <c r="D200" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F200" s="6">
         <v>45833</v>
@@ -5034,17 +5046,17 @@
       <c r="A201" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C201" s="5">
-        <v>3</v>
-      </c>
-      <c r="D201" t="s">
-        <v>165</v>
-      </c>
-      <c r="E201" t="s">
-        <v>166</v>
+      <c r="B201" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C201" s="4">
+        <v>3</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F201" s="6">
         <v>45833</v>
@@ -5054,17 +5066,17 @@
       <c r="A202" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C202" s="5">
+      <c r="B202" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C202" s="4">
         <v>136</v>
       </c>
-      <c r="D202" t="s">
-        <v>174</v>
-      </c>
-      <c r="E202" t="s">
-        <v>166</v>
+      <c r="D202" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F202" s="6">
         <v>45833</v>
@@ -5074,17 +5086,17 @@
       <c r="A203" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C203" s="5">
+      <c r="B203" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C203" s="4">
         <v>2</v>
       </c>
-      <c r="D203" t="s">
+      <c r="D203" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E203" t="s">
-        <v>170</v>
       </c>
       <c r="F203" s="6">
         <v>45833</v>
@@ -5094,17 +5106,17 @@
       <c r="A204" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C204" s="5">
+      <c r="B204" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C204" s="4">
         <v>1</v>
       </c>
-      <c r="D204" t="s">
-        <v>165</v>
-      </c>
-      <c r="E204" t="s">
-        <v>166</v>
+      <c r="D204" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F204" s="6">
         <v>45833</v>
@@ -5114,17 +5126,17 @@
       <c r="A205" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C205" s="5">
+      <c r="B205" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C205" s="4">
         <v>2</v>
       </c>
-      <c r="D205" t="s">
-        <v>169</v>
-      </c>
-      <c r="E205" t="s">
-        <v>173</v>
+      <c r="D205" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F205" s="6">
         <v>45833</v>
@@ -5134,17 +5146,17 @@
       <c r="A206" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C206" s="5">
+      <c r="B206" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C206" s="4">
         <v>178</v>
       </c>
-      <c r="D206" t="s">
+      <c r="D206" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E206" t="s">
-        <v>170</v>
       </c>
       <c r="F206" s="6">
         <v>45833</v>
@@ -5154,17 +5166,17 @@
       <c r="A207" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C207" s="5">
+      <c r="B207" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C207" s="4">
         <v>2</v>
       </c>
-      <c r="D207" t="s">
+      <c r="D207" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E207" t="s">
-        <v>170</v>
       </c>
       <c r="F207" s="6">
         <v>45833</v>
@@ -5174,17 +5186,17 @@
       <c r="A208" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C208" s="5">
+      <c r="B208" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C208" s="4">
         <v>2</v>
       </c>
-      <c r="D208" t="s">
-        <v>169</v>
-      </c>
-      <c r="E208" t="s">
-        <v>173</v>
+      <c r="D208" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F208" s="6">
         <v>45833</v>
@@ -5194,17 +5206,17 @@
       <c r="A209" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C209" s="5">
+      <c r="B209" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C209" s="4">
         <v>6</v>
       </c>
-      <c r="D209" t="s">
-        <v>168</v>
-      </c>
-      <c r="E209" t="s">
-        <v>166</v>
+      <c r="D209" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F209" s="6">
         <v>45833</v>
@@ -5214,17 +5226,17 @@
       <c r="A210" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B210" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C210" s="5">
+      <c r="B210" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C210" s="4">
         <v>73</v>
       </c>
-      <c r="D210" t="s">
-        <v>168</v>
-      </c>
-      <c r="E210" t="s">
-        <v>166</v>
+      <c r="D210" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F210" s="6">
         <v>45833</v>
@@ -5234,17 +5246,17 @@
       <c r="A211" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C211" s="5">
-        <v>3</v>
-      </c>
-      <c r="D211" t="s">
-        <v>165</v>
-      </c>
-      <c r="E211" t="s">
-        <v>166</v>
+      <c r="B211" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C211" s="4">
+        <v>3</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F211" s="6">
         <v>45833</v>
@@ -5254,17 +5266,17 @@
       <c r="A212" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C212" s="5">
+      <c r="B212" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C212" s="4">
         <v>65</v>
       </c>
-      <c r="D212" t="s">
-        <v>171</v>
-      </c>
-      <c r="E212" t="s">
-        <v>166</v>
+      <c r="D212" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F212" s="6">
         <v>45833</v>
@@ -5274,17 +5286,17 @@
       <c r="A213" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C213" s="5">
+      <c r="B213" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="4">
         <v>2</v>
       </c>
-      <c r="D213" t="s">
-        <v>165</v>
-      </c>
-      <c r="E213" t="s">
-        <v>166</v>
+      <c r="D213" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F213" s="6">
         <v>45833</v>
@@ -5294,17 +5306,17 @@
       <c r="A214" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C214" s="5">
+      <c r="B214" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C214" s="4">
         <v>5</v>
       </c>
-      <c r="D214" t="s">
-        <v>168</v>
-      </c>
-      <c r="E214" t="s">
-        <v>166</v>
+      <c r="D214" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F214" s="6">
         <v>45833</v>
@@ -5314,17 +5326,17 @@
       <c r="A215" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C215" s="5">
+      <c r="B215" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C215" s="4">
         <v>6</v>
       </c>
-      <c r="D215" t="s">
+      <c r="D215" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E215" t="s">
-        <v>170</v>
       </c>
       <c r="F215" s="6">
         <v>45833</v>
@@ -5334,17 +5346,17 @@
       <c r="A216" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C216" s="5">
+      <c r="B216" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C216" s="4">
         <v>17</v>
       </c>
-      <c r="D216" t="s">
-        <v>169</v>
-      </c>
-      <c r="E216" t="s">
-        <v>173</v>
+      <c r="D216" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F216" s="6">
         <v>45833</v>
@@ -5354,17 +5366,17 @@
       <c r="A217" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C217" s="5">
+      <c r="B217" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C217" s="4">
         <v>7</v>
       </c>
-      <c r="D217" t="s">
-        <v>174</v>
-      </c>
-      <c r="E217" t="s">
-        <v>166</v>
+      <c r="D217" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F217" s="6">
         <v>45833</v>
@@ -5374,17 +5386,17 @@
       <c r="A218" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C218" s="5">
+      <c r="B218" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C218" s="4">
         <v>332</v>
       </c>
-      <c r="D218" t="s">
-        <v>168</v>
-      </c>
-      <c r="E218" t="s">
-        <v>166</v>
+      <c r="D218" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F218" s="6">
         <v>45833</v>
@@ -5394,17 +5406,17 @@
       <c r="A219" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C219" s="5">
+      <c r="B219" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="4">
         <v>356</v>
       </c>
-      <c r="D219" t="s">
-        <v>167</v>
-      </c>
-      <c r="E219" t="s">
+      <c r="D219" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F219" s="6">
         <v>45833</v>
@@ -5414,17 +5426,17 @@
       <c r="A220" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C220" s="5">
+      <c r="B220" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C220" s="4">
         <v>19</v>
       </c>
-      <c r="D220" t="s">
-        <v>165</v>
-      </c>
-      <c r="E220" t="s">
-        <v>166</v>
+      <c r="D220" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F220" s="6">
         <v>45833</v>
@@ -5434,17 +5446,17 @@
       <c r="A221" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C221" s="5">
-        <v>3</v>
-      </c>
-      <c r="D221" t="s">
-        <v>169</v>
-      </c>
-      <c r="E221" t="s">
-        <v>175</v>
+      <c r="B221" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C221" s="4">
+        <v>3</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F221" s="6">
         <v>45833</v>
@@ -5454,17 +5466,17 @@
       <c r="A222" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C222" s="5">
+      <c r="B222" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C222" s="4">
         <v>11</v>
       </c>
-      <c r="D222" t="s">
-        <v>171</v>
-      </c>
-      <c r="E222" t="s">
-        <v>166</v>
+      <c r="D222" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F222" s="6">
         <v>45833</v>
@@ -5474,17 +5486,17 @@
       <c r="A223" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C223" s="5">
-        <v>3</v>
-      </c>
-      <c r="D223" t="s">
-        <v>165</v>
-      </c>
-      <c r="E223" t="s">
-        <v>166</v>
+      <c r="B223" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C223" s="4">
+        <v>3</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F223" s="6">
         <v>45833</v>
@@ -5494,17 +5506,17 @@
       <c r="A224" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C224" s="5">
+      <c r="B224" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C224" s="4">
         <v>1</v>
       </c>
-      <c r="D224" t="s">
-        <v>169</v>
-      </c>
-      <c r="E224" t="s">
-        <v>173</v>
+      <c r="D224" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F224" s="6">
         <v>45833</v>
@@ -5514,17 +5526,17 @@
       <c r="A225" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C225" s="5">
+      <c r="B225" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C225" s="4">
         <v>2</v>
       </c>
-      <c r="D225" t="s">
-        <v>165</v>
-      </c>
-      <c r="E225" t="s">
-        <v>166</v>
+      <c r="D225" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F225" s="6">
         <v>45833</v>
@@ -5534,17 +5546,17 @@
       <c r="A226" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C226" s="5">
+      <c r="B226" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C226" s="4">
         <v>8</v>
       </c>
-      <c r="D226" t="s">
-        <v>165</v>
-      </c>
-      <c r="E226" t="s">
-        <v>166</v>
+      <c r="D226" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F226" s="6">
         <v>45833</v>
@@ -5554,17 +5566,17 @@
       <c r="A227" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C227" s="5">
+      <c r="B227" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C227" s="4">
         <v>11</v>
       </c>
-      <c r="D227" t="s">
-        <v>165</v>
-      </c>
-      <c r="E227" t="s">
-        <v>166</v>
+      <c r="D227" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F227" s="6">
         <v>45833</v>
@@ -5574,17 +5586,17 @@
       <c r="A228" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C228" s="5">
+      <c r="B228" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C228" s="4">
         <v>51</v>
       </c>
-      <c r="D228" t="s">
-        <v>167</v>
-      </c>
-      <c r="E228" t="s">
+      <c r="D228" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F228" s="6">
         <v>45833</v>
@@ -5594,17 +5606,17 @@
       <c r="A229" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C229" s="5">
+      <c r="B229" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C229" s="4">
         <v>0</v>
       </c>
-      <c r="D229" t="s">
-        <v>165</v>
-      </c>
-      <c r="E229" t="s">
-        <v>166</v>
+      <c r="D229" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F229" s="6">
         <v>45833</v>
@@ -5614,17 +5626,17 @@
       <c r="A230" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C230" s="5">
+      <c r="B230" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C230" s="4">
         <v>53</v>
       </c>
-      <c r="D230" t="s">
-        <v>171</v>
-      </c>
-      <c r="E230" t="s">
-        <v>166</v>
+      <c r="D230" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F230" s="6">
         <v>45833</v>
@@ -5634,17 +5646,17 @@
       <c r="A231" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C231" s="5">
+      <c r="B231" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C231" s="4">
         <v>91</v>
       </c>
-      <c r="D231" t="s">
-        <v>167</v>
-      </c>
-      <c r="E231" t="s">
+      <c r="D231" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F231" s="6">
         <v>45833</v>
@@ -5654,17 +5666,17 @@
       <c r="A232" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C232" s="5">
+      <c r="B232" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C232" s="4">
         <v>1</v>
       </c>
-      <c r="D232" t="s">
+      <c r="D232" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E232" t="s">
-        <v>170</v>
       </c>
       <c r="F232" s="6">
         <v>45833</v>
@@ -5674,17 +5686,17 @@
       <c r="A233" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C233" s="5">
-        <v>3</v>
-      </c>
-      <c r="D233" t="s">
+      <c r="B233" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C233" s="4">
+        <v>3</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E233" t="s">
-        <v>170</v>
       </c>
       <c r="F233" s="6">
         <v>45833</v>
@@ -5694,17 +5706,17 @@
       <c r="A234" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C234" s="5">
+      <c r="B234" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C234" s="4">
         <v>32</v>
       </c>
-      <c r="D234" t="s">
-        <v>165</v>
-      </c>
-      <c r="E234" t="s">
-        <v>166</v>
+      <c r="D234" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F234" s="6">
         <v>45833</v>
@@ -5714,17 +5726,17 @@
       <c r="A235" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C235" s="5">
+      <c r="B235" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C235" s="4">
         <v>0</v>
       </c>
-      <c r="D235" t="s">
-        <v>165</v>
-      </c>
-      <c r="E235" t="s">
-        <v>166</v>
+      <c r="D235" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F235" s="6">
         <v>45833</v>
@@ -5734,17 +5746,17 @@
       <c r="A236" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C236" s="5">
+      <c r="B236" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C236" s="4">
         <v>184</v>
       </c>
-      <c r="D236" t="s">
-        <v>171</v>
-      </c>
-      <c r="E236" t="s">
-        <v>166</v>
+      <c r="D236" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F236" s="6">
         <v>45833</v>
@@ -5754,17 +5766,17 @@
       <c r="A237" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C237" s="5">
+      <c r="B237" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C237" s="4">
         <v>32</v>
       </c>
-      <c r="D237" t="s">
-        <v>169</v>
-      </c>
-      <c r="E237" t="s">
-        <v>175</v>
+      <c r="D237" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F237" s="6">
         <v>45833</v>
@@ -5774,17 +5786,17 @@
       <c r="A238" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C238" s="5">
+      <c r="B238" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C238" s="4">
         <v>2</v>
       </c>
-      <c r="D238" t="s">
-        <v>165</v>
-      </c>
-      <c r="E238" t="s">
-        <v>166</v>
+      <c r="D238" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F238" s="6">
         <v>45833</v>
@@ -5794,17 +5806,17 @@
       <c r="A239" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C239" s="5">
+      <c r="B239" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C239" s="4">
         <v>69</v>
       </c>
-      <c r="D239" t="s">
-        <v>168</v>
-      </c>
-      <c r="E239" t="s">
-        <v>166</v>
+      <c r="D239" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F239" s="6">
         <v>45833</v>
@@ -5814,17 +5826,17 @@
       <c r="A240" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C240" s="5">
+      <c r="B240" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C240" s="4">
         <v>65</v>
       </c>
-      <c r="D240" t="s">
-        <v>165</v>
-      </c>
-      <c r="E240" t="s">
-        <v>166</v>
+      <c r="D240" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F240" s="6">
         <v>45833</v>
@@ -5834,17 +5846,17 @@
       <c r="A241" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C241" s="5">
+      <c r="B241" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C241" s="4">
         <v>5</v>
       </c>
-      <c r="D241" t="s">
+      <c r="D241" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E241" t="s">
-        <v>170</v>
       </c>
       <c r="F241" s="6">
         <v>45833</v>
@@ -5854,17 +5866,17 @@
       <c r="A242" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C242" s="5">
+      <c r="B242" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C242" s="4">
         <v>2</v>
       </c>
-      <c r="D242" t="s">
-        <v>174</v>
-      </c>
-      <c r="E242" t="s">
-        <v>166</v>
+      <c r="D242" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F242" s="6">
         <v>45833</v>
@@ -5874,17 +5886,17 @@
       <c r="A243" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C243" s="5">
+      <c r="B243" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C243" s="4">
         <v>5</v>
       </c>
-      <c r="D243" t="s">
-        <v>165</v>
-      </c>
-      <c r="E243" t="s">
-        <v>166</v>
+      <c r="D243" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F243" s="6">
         <v>45833</v>
@@ -5894,17 +5906,17 @@
       <c r="A244" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C244" s="5">
+      <c r="B244" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C244" s="4">
         <v>6</v>
       </c>
-      <c r="D244" t="s">
-        <v>174</v>
-      </c>
-      <c r="E244" t="s">
-        <v>166</v>
+      <c r="D244" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F244" s="6">
         <v>45833</v>
@@ -5914,17 +5926,17 @@
       <c r="A245" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C245" s="5">
+      <c r="B245" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C245" s="4">
         <v>1</v>
       </c>
-      <c r="D245" t="s">
+      <c r="D245" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E245" t="s">
-        <v>170</v>
       </c>
       <c r="F245" s="6">
         <v>45833</v>
@@ -5934,17 +5946,17 @@
       <c r="A246" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C246" s="5">
+      <c r="B246" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C246" s="4">
         <v>8</v>
       </c>
-      <c r="D246" t="s">
-        <v>174</v>
-      </c>
-      <c r="E246" t="s">
-        <v>166</v>
+      <c r="D246" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F246" s="6">
         <v>45833</v>
@@ -5954,17 +5966,17 @@
       <c r="A247" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C247" s="5">
+      <c r="B247" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C247" s="4">
         <v>7</v>
       </c>
-      <c r="D247" t="s">
-        <v>165</v>
-      </c>
-      <c r="E247" t="s">
-        <v>166</v>
+      <c r="D247" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F247" s="6">
         <v>45833</v>
@@ -5974,17 +5986,17 @@
       <c r="A248" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C248" s="5">
+      <c r="B248" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C248" s="4">
         <v>0</v>
       </c>
-      <c r="D248" t="s">
-        <v>165</v>
-      </c>
-      <c r="E248" t="s">
-        <v>166</v>
+      <c r="D248" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F248" s="6">
         <v>45833</v>
@@ -5994,17 +6006,17 @@
       <c r="A249" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C249" s="5">
+      <c r="B249" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C249" s="4">
         <v>11</v>
       </c>
-      <c r="D249" t="s">
-        <v>171</v>
-      </c>
-      <c r="E249" t="s">
-        <v>166</v>
+      <c r="D249" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F249" s="6">
         <v>45833</v>
@@ -6014,17 +6026,17 @@
       <c r="A250" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C250" s="5">
+      <c r="B250" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C250" s="4">
         <v>15</v>
       </c>
-      <c r="D250" t="s">
-        <v>174</v>
-      </c>
-      <c r="E250" t="s">
-        <v>166</v>
+      <c r="D250" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F250" s="6">
         <v>45833</v>
@@ -6034,17 +6046,17 @@
       <c r="A251" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C251" s="5">
+      <c r="B251" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C251" s="4">
         <v>24</v>
       </c>
-      <c r="D251" t="s">
-        <v>169</v>
-      </c>
-      <c r="E251" t="s">
-        <v>172</v>
+      <c r="D251" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F251" s="6">
         <v>45833</v>
@@ -6054,17 +6066,17 @@
       <c r="A252" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B252" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C252" s="5">
+      <c r="B252" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C252" s="4">
         <v>7</v>
       </c>
-      <c r="D252" t="s">
-        <v>165</v>
-      </c>
-      <c r="E252" t="s">
-        <v>166</v>
+      <c r="D252" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F252" s="6">
         <v>45833</v>
@@ -6074,17 +6086,17 @@
       <c r="A253" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C253" s="5">
-        <v>3</v>
-      </c>
-      <c r="D253" t="s">
-        <v>165</v>
-      </c>
-      <c r="E253" t="s">
-        <v>166</v>
+      <c r="B253" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C253" s="4">
+        <v>3</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F253" s="6">
         <v>45833</v>
@@ -6094,37 +6106,37 @@
       <c r="A254" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C254" s="5">
+      <c r="B254" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C254" s="4">
         <v>5</v>
       </c>
-      <c r="D254" t="s">
-        <v>174</v>
-      </c>
-      <c r="E254" t="s">
-        <v>166</v>
+      <c r="D254" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F254" s="6">
         <v>45833</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="4" t="s">
+      <c r="A255" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C255" s="5">
+      <c r="B255" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C255" s="4">
         <v>9</v>
       </c>
-      <c r="D255" t="s">
-        <v>168</v>
-      </c>
-      <c r="E255" t="s">
-        <v>166</v>
+      <c r="D255" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F255" s="6">
         <v>45833</v>
@@ -6134,17 +6146,17 @@
       <c r="A256" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C256" s="5">
+      <c r="B256" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C256" s="4">
         <v>6</v>
       </c>
-      <c r="D256" t="s">
-        <v>174</v>
-      </c>
-      <c r="E256" t="s">
-        <v>166</v>
+      <c r="D256" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F256" s="6">
         <v>45833</v>
@@ -6154,17 +6166,17 @@
       <c r="A257" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C257" s="5">
+      <c r="B257" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C257" s="4">
         <v>2</v>
       </c>
-      <c r="D257" t="s">
-        <v>165</v>
-      </c>
-      <c r="E257" t="s">
-        <v>166</v>
+      <c r="D257" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F257" s="6">
         <v>45833</v>
@@ -6174,37 +6186,37 @@
       <c r="A258" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C258" s="5">
+      <c r="B258" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C258" s="4">
         <v>1</v>
       </c>
-      <c r="D258" t="s">
+      <c r="D258" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E258" t="s">
+      <c r="F258" s="6">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C259" s="4">
+        <v>9</v>
+      </c>
+      <c r="D259" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F258" s="6">
-        <v>45833</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A259" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C259" s="5">
-        <v>9</v>
-      </c>
-      <c r="D259" t="s">
-        <v>171</v>
-      </c>
-      <c r="E259" t="s">
-        <v>166</v>
+      <c r="E259" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F259" s="6">
         <v>45833</v>
@@ -6214,17 +6226,17 @@
       <c r="A260" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C260" s="5">
+      <c r="B260" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C260" s="4">
         <v>52</v>
       </c>
-      <c r="D260" t="s">
-        <v>165</v>
-      </c>
-      <c r="E260" t="s">
-        <v>166</v>
+      <c r="D260" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F260" s="6">
         <v>45833</v>
@@ -6234,17 +6246,17 @@
       <c r="A261" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C261" s="5">
+      <c r="B261" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C261" s="4">
         <v>202</v>
       </c>
-      <c r="D261" t="s">
-        <v>169</v>
-      </c>
-      <c r="E261" t="s">
-        <v>173</v>
+      <c r="D261" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F261" s="6">
         <v>45833</v>
@@ -6254,17 +6266,17 @@
       <c r="A262" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C262" s="5">
+      <c r="B262" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C262" s="4">
         <v>1</v>
       </c>
-      <c r="D262" t="s">
-        <v>165</v>
-      </c>
-      <c r="E262" t="s">
-        <v>166</v>
+      <c r="D262" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F262" s="6">
         <v>45833</v>
@@ -6274,17 +6286,17 @@
       <c r="A263" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C263" s="5">
+      <c r="B263" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C263" s="4">
         <v>62</v>
       </c>
-      <c r="D263" t="s">
-        <v>165</v>
-      </c>
-      <c r="E263" t="s">
-        <v>166</v>
+      <c r="D263" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F263" s="6">
         <v>45833</v>
@@ -6294,17 +6306,17 @@
       <c r="A264" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C264" s="5">
+      <c r="B264" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C264" s="4">
         <v>1</v>
       </c>
-      <c r="D264" t="s">
+      <c r="D264" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E264" t="s">
-        <v>170</v>
       </c>
       <c r="F264" s="6">
         <v>45833</v>
@@ -6314,17 +6326,17 @@
       <c r="A265" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C265" s="5">
+      <c r="B265" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C265" s="4">
         <v>9</v>
       </c>
-      <c r="D265" t="s">
-        <v>174</v>
-      </c>
-      <c r="E265" t="s">
-        <v>166</v>
+      <c r="D265" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F265" s="6">
         <v>45833</v>
@@ -6334,17 +6346,17 @@
       <c r="A266" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C266" s="5">
-        <v>3</v>
-      </c>
-      <c r="D266" t="s">
-        <v>174</v>
-      </c>
-      <c r="E266" t="s">
-        <v>166</v>
+      <c r="B266" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C266" s="4">
+        <v>3</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F266" s="6">
         <v>45833</v>
@@ -6354,17 +6366,17 @@
       <c r="A267" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C267" s="5">
+      <c r="B267" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C267" s="4">
         <v>43</v>
       </c>
-      <c r="D267" t="s">
-        <v>165</v>
-      </c>
-      <c r="E267" t="s">
-        <v>166</v>
+      <c r="D267" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F267" s="6">
         <v>45833</v>
@@ -6374,17 +6386,17 @@
       <c r="A268" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C268" s="5">
+      <c r="B268" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C268" s="4">
         <v>14</v>
       </c>
-      <c r="D268" t="s">
-        <v>165</v>
-      </c>
-      <c r="E268" t="s">
-        <v>166</v>
+      <c r="D268" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F268" s="6">
         <v>45833</v>
@@ -6394,17 +6406,17 @@
       <c r="A269" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C269" s="5">
+      <c r="B269" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C269" s="4">
         <v>251</v>
       </c>
-      <c r="D269" t="s">
-        <v>167</v>
-      </c>
-      <c r="E269" t="s">
+      <c r="D269" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F269" s="6">
         <v>45833</v>
@@ -6414,17 +6426,17 @@
       <c r="A270" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C270" s="5">
+      <c r="B270" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C270" s="4">
         <v>0</v>
       </c>
-      <c r="D270" t="s">
+      <c r="D270" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E270" t="s">
-        <v>170</v>
       </c>
       <c r="F270" s="6">
         <v>45833</v>
@@ -6434,17 +6446,17 @@
       <c r="A271" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C271" s="5">
+      <c r="B271" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C271" s="4">
         <v>13</v>
       </c>
-      <c r="D271" t="s">
-        <v>165</v>
-      </c>
-      <c r="E271" t="s">
-        <v>166</v>
+      <c r="D271" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F271" s="6">
         <v>45833</v>
@@ -6454,17 +6466,17 @@
       <c r="A272" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C272" s="5">
+      <c r="B272" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C272" s="4">
         <v>12</v>
       </c>
-      <c r="D272" t="s">
-        <v>167</v>
-      </c>
-      <c r="E272" t="s">
+      <c r="D272" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F272" s="6">
         <v>45833</v>
@@ -6474,17 +6486,17 @@
       <c r="A273" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B273" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C273" s="5">
-        <v>3</v>
-      </c>
-      <c r="D273" t="s">
-        <v>169</v>
-      </c>
-      <c r="E273" t="s">
-        <v>173</v>
+      <c r="B273" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C273" s="4">
+        <v>3</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F273" s="6">
         <v>45833</v>
@@ -6494,17 +6506,17 @@
       <c r="A274" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="B274" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C274" s="5">
+      <c r="B274" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C274" s="4">
         <v>14</v>
       </c>
-      <c r="D274" t="s">
-        <v>167</v>
-      </c>
-      <c r="E274" t="s">
+      <c r="D274" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F274" s="6">
         <v>45833</v>
@@ -6514,17 +6526,17 @@
       <c r="A275" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C275" s="5">
-        <v>3</v>
-      </c>
-      <c r="D275" t="s">
-        <v>167</v>
-      </c>
-      <c r="E275" t="s">
+      <c r="B275" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C275" s="4">
+        <v>3</v>
+      </c>
+      <c r="D275" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F275" s="6">
         <v>45833</v>
@@ -6534,17 +6546,17 @@
       <c r="A276" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C276" s="5">
+      <c r="B276" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C276" s="4">
         <v>9</v>
       </c>
-      <c r="D276" t="s">
-        <v>165</v>
-      </c>
-      <c r="E276" t="s">
-        <v>166</v>
+      <c r="D276" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F276" s="6">
         <v>45833</v>
@@ -6554,17 +6566,17 @@
       <c r="A277" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C277" s="5">
-        <v>3</v>
-      </c>
-      <c r="D277" t="s">
-        <v>165</v>
-      </c>
-      <c r="E277" t="s">
-        <v>166</v>
+      <c r="B277" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C277" s="4">
+        <v>3</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F277" s="6">
         <v>45833</v>
@@ -6574,17 +6586,17 @@
       <c r="A278" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B278" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C278" s="5">
+      <c r="B278" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C278" s="4">
         <v>1</v>
       </c>
-      <c r="D278" t="s">
-        <v>169</v>
-      </c>
-      <c r="E278" t="s">
-        <v>172</v>
+      <c r="D278" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F278" s="6">
         <v>45833</v>
@@ -6594,17 +6606,17 @@
       <c r="A279" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C279" s="5">
+      <c r="B279" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C279" s="4">
         <v>7</v>
       </c>
-      <c r="D279" t="s">
-        <v>165</v>
-      </c>
-      <c r="E279" t="s">
-        <v>166</v>
+      <c r="D279" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F279" s="6">
         <v>45833</v>
@@ -6614,17 +6626,17 @@
       <c r="A280" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C280" s="5">
+      <c r="B280" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C280" s="4">
         <v>20</v>
       </c>
-      <c r="D280" t="s">
-        <v>169</v>
-      </c>
-      <c r="E280" t="s">
-        <v>175</v>
+      <c r="D280" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F280" s="6">
         <v>45833</v>
@@ -6634,17 +6646,17 @@
       <c r="A281" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C281" s="5">
+      <c r="B281" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C281" s="4">
         <v>11</v>
       </c>
-      <c r="D281" t="s">
-        <v>169</v>
-      </c>
-      <c r="E281" t="s">
-        <v>172</v>
+      <c r="D281" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F281" s="6">
         <v>45833</v>
@@ -6654,17 +6666,17 @@
       <c r="A282" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C282" s="5">
+      <c r="B282" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C282" s="4">
         <v>128</v>
       </c>
-      <c r="D282" t="s">
-        <v>168</v>
-      </c>
-      <c r="E282" t="s">
-        <v>166</v>
+      <c r="D282" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F282" s="6">
         <v>45833</v>
@@ -6674,17 +6686,17 @@
       <c r="A283" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C283" s="5">
+      <c r="B283" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C283" s="4">
         <v>174</v>
       </c>
-      <c r="D283" t="s">
-        <v>168</v>
-      </c>
-      <c r="E283" t="s">
-        <v>166</v>
+      <c r="D283" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F283" s="6">
         <v>45833</v>
@@ -6694,17 +6706,17 @@
       <c r="A284" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B284" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C284" s="5">
+      <c r="B284" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C284" s="4">
         <v>4</v>
       </c>
-      <c r="D284" t="s">
-        <v>165</v>
-      </c>
-      <c r="E284" t="s">
-        <v>166</v>
+      <c r="D284" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F284" s="6">
         <v>45833</v>
@@ -6714,17 +6726,17 @@
       <c r="A285" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C285" s="5">
+      <c r="B285" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C285" s="4">
         <v>27</v>
       </c>
-      <c r="D285" t="s">
-        <v>165</v>
-      </c>
-      <c r="E285" t="s">
-        <v>166</v>
+      <c r="D285" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F285" s="6">
         <v>45833</v>
@@ -6734,17 +6746,17 @@
       <c r="A286" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C286" s="5">
+      <c r="B286" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C286" s="4">
         <v>4</v>
       </c>
-      <c r="D286" t="s">
-        <v>169</v>
-      </c>
-      <c r="E286" t="s">
-        <v>175</v>
+      <c r="D286" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F286" s="6">
         <v>45833</v>
@@ -6754,17 +6766,17 @@
       <c r="A287" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C287" s="5">
+      <c r="B287" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C287" s="4">
         <v>1</v>
       </c>
-      <c r="D287" t="s">
-        <v>174</v>
-      </c>
-      <c r="E287" t="s">
-        <v>166</v>
+      <c r="D287" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F287" s="6">
         <v>45833</v>
@@ -6774,17 +6786,17 @@
       <c r="A288" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B288" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C288" s="5">
+      <c r="B288" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C288" s="4">
         <v>60</v>
       </c>
-      <c r="D288" t="s">
-        <v>171</v>
-      </c>
-      <c r="E288" t="s">
-        <v>166</v>
+      <c r="D288" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F288" s="6">
         <v>45833</v>
@@ -6794,17 +6806,17 @@
       <c r="A289" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C289" s="5">
+      <c r="B289" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="4">
         <v>23</v>
       </c>
-      <c r="D289" t="s">
-        <v>167</v>
-      </c>
-      <c r="E289" t="s">
+      <c r="D289" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F289" s="6">
         <v>45833</v>
@@ -6814,17 +6826,17 @@
       <c r="A290" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C290" s="5">
+      <c r="B290" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C290" s="4">
         <v>27</v>
       </c>
-      <c r="D290" t="s">
-        <v>167</v>
-      </c>
-      <c r="E290" t="s">
+      <c r="D290" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F290" s="6">
         <v>45833</v>
@@ -6834,17 +6846,17 @@
       <c r="A291" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C291" s="5">
+      <c r="B291" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C291" s="4">
         <v>2</v>
       </c>
-      <c r="D291" t="s">
-        <v>165</v>
-      </c>
-      <c r="E291" t="s">
-        <v>166</v>
+      <c r="D291" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F291" s="6">
         <v>45833</v>
@@ -6854,17 +6866,17 @@
       <c r="A292" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C292" s="5">
+      <c r="B292" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C292" s="4">
         <v>1</v>
       </c>
-      <c r="D292" t="s">
-        <v>174</v>
-      </c>
-      <c r="E292" t="s">
-        <v>166</v>
+      <c r="D292" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F292" s="6">
         <v>45833</v>
@@ -6874,17 +6886,17 @@
       <c r="A293" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C293" s="5">
+      <c r="B293" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C293" s="4">
         <v>13</v>
       </c>
-      <c r="D293" t="s">
-        <v>169</v>
-      </c>
-      <c r="E293" t="s">
-        <v>172</v>
+      <c r="D293" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F293" s="6">
         <v>45833</v>
@@ -6894,17 +6906,17 @@
       <c r="A294" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C294" s="5">
+      <c r="B294" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C294" s="4">
         <v>12</v>
       </c>
-      <c r="D294" t="s">
-        <v>165</v>
-      </c>
-      <c r="E294" t="s">
-        <v>166</v>
+      <c r="D294" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F294" s="6">
         <v>45833</v>
@@ -6914,17 +6926,17 @@
       <c r="A295" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C295" s="5">
+      <c r="B295" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C295" s="4">
         <v>13</v>
       </c>
-      <c r="D295" t="s">
-        <v>165</v>
-      </c>
-      <c r="E295" t="s">
-        <v>166</v>
+      <c r="D295" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F295" s="6">
         <v>45833</v>
@@ -6934,17 +6946,17 @@
       <c r="A296" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C296" s="5">
+      <c r="B296" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C296" s="4">
         <v>6</v>
       </c>
-      <c r="D296" t="s">
-        <v>165</v>
-      </c>
-      <c r="E296" t="s">
-        <v>166</v>
+      <c r="D296" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F296" s="6">
         <v>45833</v>
@@ -6954,17 +6966,17 @@
       <c r="A297" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B297" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C297" s="5">
-        <v>3</v>
-      </c>
-      <c r="D297" t="s">
-        <v>169</v>
-      </c>
-      <c r="E297" t="s">
-        <v>173</v>
+      <c r="B297" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C297" s="4">
+        <v>3</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F297" s="6">
         <v>45833</v>
@@ -6974,17 +6986,17 @@
       <c r="A298" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C298" s="5">
-        <v>3</v>
-      </c>
-      <c r="D298" t="s">
+      <c r="B298" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C298" s="4">
+        <v>3</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E298" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E298" t="s">
-        <v>170</v>
       </c>
       <c r="F298" s="6">
         <v>45833</v>
@@ -6994,17 +7006,17 @@
       <c r="A299" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C299" s="5">
+      <c r="B299" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C299" s="4">
         <v>46</v>
       </c>
-      <c r="D299" t="s">
-        <v>169</v>
-      </c>
-      <c r="E299" t="s">
-        <v>173</v>
+      <c r="D299" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="F299" s="6">
         <v>45833</v>
@@ -7014,17 +7026,17 @@
       <c r="A300" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C300" s="5">
+      <c r="B300" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C300" s="4">
         <v>68</v>
       </c>
-      <c r="D300" t="s">
-        <v>167</v>
-      </c>
-      <c r="E300" t="s">
+      <c r="D300" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F300" s="6">
         <v>45833</v>
@@ -7034,17 +7046,17 @@
       <c r="A301" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C301" s="5">
+      <c r="B301" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C301" s="4">
         <v>1</v>
       </c>
-      <c r="D301" t="s">
-        <v>165</v>
-      </c>
-      <c r="E301" t="s">
-        <v>166</v>
+      <c r="D301" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F301" s="6">
         <v>45833</v>
@@ -7054,17 +7066,17 @@
       <c r="A302" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C302" s="5">
+      <c r="B302" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C302" s="4">
         <v>25</v>
       </c>
-      <c r="D302" t="s">
-        <v>174</v>
-      </c>
-      <c r="E302" t="s">
-        <v>166</v>
+      <c r="D302" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F302" s="6">
         <v>45833</v>
@@ -7074,17 +7086,17 @@
       <c r="A303" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C303" s="5">
+      <c r="B303" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C303" s="4">
         <v>110</v>
       </c>
-      <c r="D303" t="s">
-        <v>167</v>
-      </c>
-      <c r="E303" t="s">
+      <c r="D303" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F303" s="6">
         <v>45833</v>
@@ -7094,17 +7106,17 @@
       <c r="A304" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B304" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C304" s="5">
+      <c r="B304" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C304" s="4">
         <v>6</v>
       </c>
-      <c r="D304" t="s">
-        <v>165</v>
-      </c>
-      <c r="E304" t="s">
-        <v>166</v>
+      <c r="D304" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F304" s="6">
         <v>45833</v>
@@ -7114,17 +7126,17 @@
       <c r="A305" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B305" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C305" s="5">
+      <c r="B305" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C305" s="4">
         <v>68</v>
       </c>
-      <c r="D305" t="s">
-        <v>174</v>
-      </c>
-      <c r="E305" t="s">
-        <v>166</v>
+      <c r="D305" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F305" s="6">
         <v>45833</v>
@@ -7134,17 +7146,17 @@
       <c r="A306" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B306" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C306" s="5">
+      <c r="B306" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C306" s="4">
         <v>2</v>
       </c>
-      <c r="D306" t="s">
+      <c r="D306" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E306" t="s">
-        <v>170</v>
       </c>
       <c r="F306" s="6">
         <v>45833</v>
@@ -7154,17 +7166,17 @@
       <c r="A307" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B307" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C307" s="5">
+      <c r="B307" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C307" s="4">
         <v>4</v>
       </c>
-      <c r="D307" t="s">
-        <v>169</v>
-      </c>
-      <c r="E307" t="s">
-        <v>172</v>
+      <c r="D307" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="F307" s="6">
         <v>45833</v>
@@ -7174,17 +7186,17 @@
       <c r="A308" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B308" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C308" s="5">
+      <c r="B308" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C308" s="4">
         <v>8</v>
       </c>
-      <c r="D308" t="s">
-        <v>174</v>
-      </c>
-      <c r="E308" t="s">
-        <v>166</v>
+      <c r="D308" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F308" s="6">
         <v>45833</v>
@@ -7194,17 +7206,17 @@
       <c r="A309" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B309" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C309" s="5">
+      <c r="B309" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C309" s="4">
         <v>5</v>
       </c>
-      <c r="D309" t="s">
-        <v>167</v>
-      </c>
-      <c r="E309" t="s">
+      <c r="D309" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F309" s="6">
         <v>45833</v>
@@ -7214,17 +7226,17 @@
       <c r="A310" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C310" s="5">
+      <c r="B310" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C310" s="4">
         <v>303</v>
       </c>
-      <c r="D310" t="s">
-        <v>174</v>
-      </c>
-      <c r="E310" t="s">
-        <v>166</v>
+      <c r="D310" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F310" s="6">
         <v>45833</v>
@@ -7234,17 +7246,17 @@
       <c r="A311" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B311" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C311" s="5">
+      <c r="B311" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C311" s="4">
         <v>127</v>
       </c>
-      <c r="D311" t="s">
-        <v>169</v>
-      </c>
-      <c r="E311" t="s">
-        <v>175</v>
+      <c r="D311" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="F311" s="6">
         <v>45833</v>
@@ -7254,17 +7266,17 @@
       <c r="A312" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C312" s="5">
+      <c r="B312" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C312" s="4">
         <v>41</v>
       </c>
-      <c r="D312" t="s">
-        <v>168</v>
-      </c>
-      <c r="E312" t="s">
-        <v>166</v>
+      <c r="D312" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F312" s="6">
         <v>45833</v>
@@ -7274,17 +7286,17 @@
       <c r="A313" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C313" s="5">
+      <c r="B313" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C313" s="4">
         <v>4</v>
       </c>
-      <c r="D313" t="s">
+      <c r="D313" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="E313" t="s">
-        <v>170</v>
       </c>
       <c r="F313" s="6">
         <v>45833</v>
@@ -7294,17 +7306,17 @@
       <c r="A314" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="B314" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C314" s="5">
+      <c r="B314" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C314" s="4">
         <v>13</v>
       </c>
-      <c r="D314" t="s">
-        <v>167</v>
-      </c>
-      <c r="E314" t="s">
+      <c r="D314" s="2" t="s">
         <v>166</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F314" s="6">
         <v>45833</v>
@@ -7314,17 +7326,17 @@
       <c r="A315" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B315" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C315" s="5">
+      <c r="B315" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C315" s="4">
         <v>0</v>
       </c>
-      <c r="D315" t="s">
-        <v>174</v>
-      </c>
-      <c r="E315" t="s">
-        <v>166</v>
+      <c r="D315" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F315" s="6">
         <v>45833</v>
@@ -7334,17 +7346,17 @@
       <c r="A316" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C316" s="5">
+      <c r="B316" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C316" s="4">
         <v>52</v>
       </c>
-      <c r="D316" t="s">
-        <v>165</v>
-      </c>
-      <c r="E316" t="s">
-        <v>166</v>
+      <c r="D316" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F316" s="6">
         <v>45833</v>
@@ -7354,17 +7366,17 @@
       <c r="A317" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C317" s="5">
+      <c r="B317" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C317" s="4">
         <v>2</v>
       </c>
-      <c r="D317" t="s">
-        <v>165</v>
-      </c>
-      <c r="E317" t="s">
-        <v>166</v>
+      <c r="D317" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F317" s="6">
         <v>45833</v>
@@ -7374,17 +7386,17 @@
       <c r="A318" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C318" s="5">
+      <c r="B318" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C318" s="4">
         <v>20</v>
       </c>
-      <c r="D318" t="s">
-        <v>165</v>
-      </c>
-      <c r="E318" t="s">
-        <v>166</v>
+      <c r="D318" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F318" s="6">
         <v>45833</v>
@@ -7394,17 +7406,17 @@
       <c r="A319" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B319" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C319" s="5">
+      <c r="B319" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C319" s="4">
         <v>1</v>
       </c>
-      <c r="D319" t="s">
-        <v>168</v>
-      </c>
-      <c r="E319" t="s">
-        <v>166</v>
+      <c r="D319" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>165</v>
       </c>
       <c r="F319" s="6">
         <v>45833</v>

--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716E2EFA-0601-4DEC-8E8A-8ADF1CFD1C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E5A0F-47DD-4614-A8A2-CD2078735C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="178">
   <si>
     <t>cidade</t>
   </si>
@@ -562,6 +562,9 @@
   </si>
   <si>
     <t>Josiane</t>
+  </si>
+  <si>
+    <t>BARRA DO RIO AZUL/RS</t>
   </si>
 </sst>
 </file>
@@ -7423,806 +7426,3206 @@
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A320" s="4"/>
-      <c r="B320" s="2"/>
-      <c r="C320" s="5"/>
-    </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A321" s="4"/>
-      <c r="B321" s="2"/>
-      <c r="C321" s="5"/>
-    </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A322" s="4"/>
-      <c r="B322" s="2"/>
-      <c r="C322" s="5"/>
-    </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A323" s="4"/>
-      <c r="B323" s="2"/>
-      <c r="C323" s="5"/>
-    </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A324" s="4"/>
-      <c r="B324" s="2"/>
-      <c r="C324" s="5"/>
-    </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A325" s="4"/>
-      <c r="B325" s="2"/>
-      <c r="C325" s="5"/>
-    </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A326" s="4"/>
-      <c r="B326" s="2"/>
-      <c r="C326" s="5"/>
-    </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A327" s="4"/>
-      <c r="B327" s="2"/>
-      <c r="C327" s="5"/>
-    </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A328" s="4"/>
-      <c r="B328" s="2"/>
-      <c r="C328" s="5"/>
-    </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A329" s="4"/>
-      <c r="B329" s="2"/>
-      <c r="C329" s="5"/>
-    </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A330" s="4"/>
-      <c r="B330" s="2"/>
-      <c r="C330" s="5"/>
-    </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A331" s="4"/>
-      <c r="B331" s="2"/>
-      <c r="C331" s="5"/>
-    </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A332" s="4"/>
-      <c r="B332" s="2"/>
-      <c r="C332" s="5"/>
-    </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A333" s="4"/>
-      <c r="B333" s="2"/>
-      <c r="C333" s="5"/>
-    </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A334" s="4"/>
-      <c r="B334" s="2"/>
-      <c r="C334" s="5"/>
-    </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A335" s="4"/>
-      <c r="B335" s="2"/>
-      <c r="C335" s="5"/>
-    </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A336" s="4"/>
-      <c r="B336" s="2"/>
-      <c r="C336" s="5"/>
-    </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A337" s="4"/>
-      <c r="B337" s="2"/>
-      <c r="C337" s="5"/>
-    </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A338" s="4"/>
-      <c r="B338" s="2"/>
-      <c r="C338" s="5"/>
-    </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A339" s="4"/>
-      <c r="B339" s="2"/>
-      <c r="C339" s="5"/>
-    </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A340" s="4"/>
-      <c r="B340" s="2"/>
-      <c r="C340" s="5"/>
-    </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A341" s="4"/>
-      <c r="B341" s="2"/>
-      <c r="C341" s="5"/>
-    </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A342" s="4"/>
-      <c r="B342" s="2"/>
-      <c r="C342" s="5"/>
-    </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A343" s="4"/>
-      <c r="B343" s="2"/>
-      <c r="C343" s="5"/>
-    </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A344" s="4"/>
-      <c r="B344" s="2"/>
-      <c r="C344" s="5"/>
-    </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A345" s="4"/>
-      <c r="B345" s="2"/>
-      <c r="C345" s="5"/>
-    </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A346" s="4"/>
-      <c r="B346" s="2"/>
-      <c r="C346" s="5"/>
-    </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A347" s="4"/>
-      <c r="B347" s="2"/>
-      <c r="C347" s="5"/>
-    </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A348" s="4"/>
-      <c r="B348" s="2"/>
-      <c r="C348" s="5"/>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A349" s="4"/>
-      <c r="B349" s="2"/>
-      <c r="C349" s="5"/>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A350" s="4"/>
-      <c r="B350" s="2"/>
-      <c r="C350" s="5"/>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A351" s="4"/>
-      <c r="B351" s="2"/>
-      <c r="C351" s="5"/>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A352" s="4"/>
-      <c r="B352" s="2"/>
-      <c r="C352" s="5"/>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A353" s="4"/>
-      <c r="B353" s="2"/>
-      <c r="C353" s="5"/>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A354" s="4"/>
-      <c r="B354" s="2"/>
-      <c r="C354" s="5"/>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A355" s="4"/>
-      <c r="B355" s="2"/>
-      <c r="C355" s="5"/>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A356" s="4"/>
-      <c r="B356" s="2"/>
-      <c r="C356" s="5"/>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A357" s="4"/>
-      <c r="B357" s="2"/>
-      <c r="C357" s="5"/>
-    </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A358" s="4"/>
-      <c r="B358" s="2"/>
-      <c r="C358" s="5"/>
-    </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A359" s="4"/>
-      <c r="B359" s="2"/>
-      <c r="C359" s="5"/>
-    </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A360" s="4"/>
-      <c r="B360" s="2"/>
-      <c r="C360" s="5"/>
-    </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A361" s="4"/>
-      <c r="B361" s="2"/>
-      <c r="C361" s="5"/>
-    </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A362" s="4"/>
-      <c r="B362" s="2"/>
-      <c r="C362" s="5"/>
-    </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A363" s="4"/>
-      <c r="B363" s="2"/>
-      <c r="C363" s="5"/>
-    </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A364" s="4"/>
-      <c r="B364" s="2"/>
-      <c r="C364" s="5"/>
-    </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A365" s="4"/>
-      <c r="B365" s="2"/>
-      <c r="C365" s="5"/>
-    </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A366" s="4"/>
-      <c r="B366" s="2"/>
-      <c r="C366" s="5"/>
-    </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A367" s="4"/>
-      <c r="B367" s="2"/>
-      <c r="C367" s="5"/>
-    </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A368" s="4"/>
-      <c r="B368" s="2"/>
-      <c r="C368" s="5"/>
-    </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A369" s="4"/>
-      <c r="B369" s="2"/>
-      <c r="C369" s="5"/>
-    </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A370" s="4"/>
-      <c r="B370" s="2"/>
-      <c r="C370" s="5"/>
-    </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A371" s="4"/>
-      <c r="B371" s="2"/>
-      <c r="C371" s="5"/>
-    </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A372" s="4"/>
-      <c r="B372" s="2"/>
-      <c r="C372" s="5"/>
-    </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A373" s="4"/>
-      <c r="B373" s="2"/>
-      <c r="C373" s="5"/>
-    </row>
-    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A374" s="4"/>
-      <c r="B374" s="2"/>
-      <c r="C374" s="5"/>
-    </row>
-    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A375" s="4"/>
-      <c r="B375" s="2"/>
-      <c r="C375" s="5"/>
-    </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A376" s="4"/>
-      <c r="B376" s="2"/>
-      <c r="C376" s="5"/>
-    </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A377" s="4"/>
-      <c r="B377" s="2"/>
-      <c r="C377" s="5"/>
-    </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A378" s="4"/>
-      <c r="B378" s="2"/>
-      <c r="C378" s="5"/>
-    </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A379" s="4"/>
-      <c r="B379" s="2"/>
-      <c r="C379" s="5"/>
-    </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A380" s="4"/>
-      <c r="B380" s="2"/>
-      <c r="C380" s="5"/>
-    </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A381" s="4"/>
-      <c r="B381" s="2"/>
-      <c r="C381" s="5"/>
-    </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A382" s="4"/>
-      <c r="B382" s="2"/>
-      <c r="C382" s="5"/>
-    </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A383" s="4"/>
-      <c r="B383" s="2"/>
-      <c r="C383" s="5"/>
-    </row>
-    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A384" s="4"/>
-      <c r="B384" s="2"/>
-      <c r="C384" s="5"/>
-    </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A385" s="4"/>
-      <c r="B385" s="2"/>
-      <c r="C385" s="5"/>
-    </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A386" s="4"/>
-      <c r="B386" s="2"/>
-      <c r="C386" s="5"/>
-    </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A387" s="4"/>
-      <c r="B387" s="2"/>
-      <c r="C387" s="5"/>
-    </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A388" s="4"/>
-      <c r="B388" s="2"/>
-      <c r="C388" s="5"/>
-    </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A389" s="4"/>
-      <c r="B389" s="2"/>
-      <c r="C389" s="5"/>
-    </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A390" s="4"/>
-      <c r="B390" s="2"/>
-      <c r="C390" s="5"/>
-    </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A391" s="4"/>
-      <c r="B391" s="2"/>
-      <c r="C391" s="5"/>
-    </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A392" s="4"/>
-      <c r="B392" s="2"/>
-      <c r="C392" s="5"/>
-    </row>
-    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A393" s="4"/>
-      <c r="B393" s="2"/>
-      <c r="C393" s="5"/>
-    </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A394" s="4"/>
-      <c r="B394" s="2"/>
-      <c r="C394" s="5"/>
-    </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A395" s="4"/>
-      <c r="B395" s="2"/>
-      <c r="C395" s="5"/>
-    </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A396" s="4"/>
-      <c r="B396" s="2"/>
-      <c r="C396" s="5"/>
-    </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A397" s="4"/>
-      <c r="B397" s="2"/>
-      <c r="C397" s="5"/>
-    </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A398" s="4"/>
-      <c r="B398" s="2"/>
-      <c r="C398" s="5"/>
-    </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A399" s="4"/>
-      <c r="B399" s="2"/>
-      <c r="C399" s="5"/>
-    </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A400" s="4"/>
-      <c r="B400" s="2"/>
-      <c r="C400" s="5"/>
-    </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A401" s="4"/>
-      <c r="B401" s="2"/>
-      <c r="C401" s="5"/>
-    </row>
-    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A402" s="4"/>
-      <c r="B402" s="2"/>
-      <c r="C402" s="5"/>
-    </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A403" s="4"/>
-      <c r="B403" s="2"/>
-      <c r="C403" s="5"/>
-    </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A404" s="4"/>
-      <c r="B404" s="2"/>
-      <c r="C404" s="5"/>
-    </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A405" s="4"/>
-      <c r="B405" s="2"/>
-      <c r="C405" s="5"/>
-    </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A406" s="4"/>
-      <c r="B406" s="2"/>
-      <c r="C406" s="5"/>
-    </row>
-    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A407" s="4"/>
-      <c r="B407" s="2"/>
-      <c r="C407" s="5"/>
-    </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A408" s="4"/>
-      <c r="B408" s="2"/>
-      <c r="C408" s="5"/>
-    </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A409" s="4"/>
-      <c r="B409" s="2"/>
-      <c r="C409" s="5"/>
-    </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A410" s="4"/>
-      <c r="B410" s="2"/>
-      <c r="C410" s="5"/>
-    </row>
-    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A411" s="4"/>
-      <c r="B411" s="2"/>
-      <c r="C411" s="5"/>
-    </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A412" s="4"/>
-      <c r="B412" s="2"/>
-      <c r="C412" s="5"/>
-    </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A413" s="4"/>
-      <c r="B413" s="2"/>
-      <c r="C413" s="5"/>
-    </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A414" s="4"/>
-      <c r="B414" s="2"/>
-      <c r="C414" s="5"/>
-    </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A415" s="4"/>
-      <c r="B415" s="2"/>
-      <c r="C415" s="5"/>
-    </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A416" s="4"/>
-      <c r="B416" s="2"/>
-      <c r="C416" s="5"/>
-    </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A417" s="4"/>
-      <c r="B417" s="2"/>
-      <c r="C417" s="5"/>
-    </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A418" s="4"/>
-      <c r="B418" s="2"/>
-      <c r="C418" s="5"/>
-    </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A419" s="4"/>
-      <c r="B419" s="2"/>
-      <c r="C419" s="5"/>
-    </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A420" s="4"/>
-      <c r="B420" s="2"/>
-      <c r="C420" s="5"/>
-    </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A421" s="4"/>
-      <c r="B421" s="2"/>
-      <c r="C421" s="5"/>
-    </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A422" s="4"/>
-      <c r="B422" s="2"/>
-      <c r="C422" s="5"/>
-    </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A423" s="4"/>
-      <c r="B423" s="2"/>
-      <c r="C423" s="5"/>
-    </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A424" s="4"/>
-      <c r="B424" s="2"/>
-      <c r="C424" s="5"/>
-    </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A425" s="4"/>
-      <c r="B425" s="2"/>
-      <c r="C425" s="5"/>
-    </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A426" s="4"/>
-      <c r="B426" s="2"/>
-      <c r="C426" s="5"/>
-    </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A427" s="4"/>
-      <c r="B427" s="2"/>
-      <c r="C427" s="5"/>
-    </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A428" s="4"/>
-      <c r="B428" s="2"/>
-      <c r="C428" s="5"/>
-    </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A429" s="4"/>
-      <c r="B429" s="2"/>
-      <c r="C429" s="5"/>
-    </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A430" s="4"/>
-      <c r="B430" s="2"/>
-      <c r="C430" s="5"/>
-    </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A431" s="4"/>
-      <c r="B431" s="2"/>
-      <c r="C431" s="5"/>
-    </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A432" s="4"/>
-      <c r="B432" s="2"/>
-      <c r="C432" s="5"/>
-    </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A433" s="4"/>
-      <c r="B433" s="2"/>
-      <c r="C433" s="5"/>
-    </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A434" s="4"/>
-      <c r="B434" s="2"/>
-      <c r="C434" s="5"/>
-    </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A435" s="4"/>
-      <c r="B435" s="2"/>
-      <c r="C435" s="5"/>
-    </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A436" s="4"/>
-      <c r="B436" s="2"/>
-      <c r="C436" s="5"/>
-    </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A437" s="4"/>
-      <c r="B437" s="2"/>
-      <c r="C437" s="5"/>
-    </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A438" s="4"/>
-      <c r="B438" s="2"/>
-      <c r="C438" s="5"/>
-    </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A439" s="4"/>
-      <c r="B439" s="2"/>
-      <c r="C439" s="5"/>
-    </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A440" s="4"/>
-      <c r="B440" s="2"/>
-      <c r="C440" s="5"/>
-    </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A441" s="4"/>
-      <c r="B441" s="2"/>
-      <c r="C441" s="5"/>
-    </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A442" s="4"/>
-      <c r="B442" s="2"/>
-      <c r="C442" s="5"/>
-    </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A443" s="4"/>
-      <c r="B443" s="2"/>
-      <c r="C443" s="5"/>
-    </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A444" s="4"/>
-      <c r="B444" s="2"/>
-      <c r="C444" s="5"/>
-    </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A445" s="4"/>
-      <c r="B445" s="2"/>
-      <c r="C445" s="5"/>
-    </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A446" s="4"/>
-      <c r="B446" s="2"/>
-      <c r="C446" s="5"/>
-    </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A447" s="4"/>
-      <c r="B447" s="2"/>
-      <c r="C447" s="5"/>
-    </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A448" s="4"/>
-      <c r="B448" s="2"/>
-      <c r="C448" s="5"/>
-    </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A449" s="4"/>
-      <c r="B449" s="2"/>
-      <c r="C449" s="5"/>
-    </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A450" s="4"/>
-      <c r="B450" s="2"/>
-      <c r="C450" s="5"/>
-    </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A451" s="4"/>
-      <c r="B451" s="2"/>
-      <c r="C451" s="5"/>
-    </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A452" s="4"/>
-      <c r="B452" s="2"/>
-      <c r="C452" s="5"/>
-    </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A453" s="4"/>
-      <c r="B453" s="2"/>
-      <c r="C453" s="5"/>
-    </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A454" s="4"/>
-      <c r="B454" s="2"/>
-      <c r="C454" s="5"/>
-    </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A455" s="4"/>
-      <c r="B455" s="2"/>
-      <c r="C455" s="5"/>
-    </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A456" s="4"/>
-      <c r="B456" s="2"/>
-      <c r="C456" s="5"/>
-    </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A457" s="4"/>
-      <c r="B457" s="2"/>
-      <c r="C457" s="5"/>
-    </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A458" s="4"/>
-      <c r="B458" s="2"/>
-      <c r="C458" s="5"/>
-    </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A459" s="4"/>
-      <c r="B459" s="2"/>
-      <c r="C459" s="5"/>
-    </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A460" s="4"/>
-      <c r="B460" s="2"/>
-      <c r="C460" s="5"/>
-    </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A461" s="4"/>
-      <c r="B461" s="2"/>
-      <c r="C461" s="5"/>
-    </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A462" s="4"/>
-      <c r="B462" s="2"/>
-      <c r="C462" s="5"/>
-    </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A463" s="4"/>
-      <c r="B463" s="2"/>
-      <c r="C463" s="5"/>
-    </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A464" s="4"/>
-      <c r="B464" s="2"/>
-      <c r="C464" s="5"/>
-    </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A465" s="4"/>
-      <c r="B465" s="2"/>
-      <c r="C465" s="5"/>
-    </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A466" s="4"/>
-      <c r="B466" s="2"/>
-      <c r="C466" s="5"/>
-    </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A467" s="4"/>
-      <c r="B467" s="2"/>
-      <c r="C467" s="5"/>
-    </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A468" s="4"/>
-      <c r="B468" s="2"/>
-      <c r="C468" s="5"/>
-    </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A469" s="4"/>
-      <c r="B469" s="2"/>
-      <c r="C469" s="5"/>
-    </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A470" s="4"/>
-      <c r="B470" s="2"/>
-      <c r="C470" s="5"/>
-    </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A471" s="4"/>
-      <c r="B471" s="2"/>
-      <c r="C471" s="5"/>
-    </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A472" s="4"/>
-      <c r="B472" s="2"/>
-      <c r="C472" s="5"/>
-    </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A473" s="4"/>
-      <c r="B473" s="2"/>
-      <c r="C473" s="5"/>
-    </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A474" s="4"/>
-      <c r="B474" s="2"/>
-      <c r="C474" s="5"/>
-    </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A475" s="4"/>
-      <c r="B475" s="2"/>
-      <c r="C475" s="5"/>
-    </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A476" s="4"/>
-      <c r="B476" s="2"/>
-      <c r="C476" s="5"/>
-    </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A477" s="4"/>
-      <c r="B477" s="2"/>
-      <c r="C477" s="5"/>
-    </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A478" s="4"/>
-      <c r="B478" s="2"/>
-      <c r="C478" s="5"/>
-    </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A479" s="4"/>
-      <c r="B479" s="2"/>
-      <c r="C479" s="5"/>
-    </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C320" s="4">
+        <v>17</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F320" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A321" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C321" s="4">
+        <v>15</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F321" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A322" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C322" s="4">
+        <v>3</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F322" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A323" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C323" s="4">
+        <v>4</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F323" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A324" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C324" s="4">
+        <v>0</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F324" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A325" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C325" s="4">
+        <v>154</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F325" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A326" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C326" s="4">
+        <v>8</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F326" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A327" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C327" s="4">
+        <v>1</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F327" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A328" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B328" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C328" s="4">
+        <v>0</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F328" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A329" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B329" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C329" s="4">
+        <v>1</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F329" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A330" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B330" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C330" s="4">
+        <v>0</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F330" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A331" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B331" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C331" s="4">
+        <v>13</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F331" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A332" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B332" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C332" s="4">
+        <v>111</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F332" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A333" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B333" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C333" s="4">
+        <v>2</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F333" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A334" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C334" s="4">
+        <v>1</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F334" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A335" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C335" s="4">
+        <v>1</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F335" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A336" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B336" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C336" s="4">
+        <v>11</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F336" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A337" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B337" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C337" s="4">
+        <v>90</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F337" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A338" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B338" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C338" s="4">
+        <v>13</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F338" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A339" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C339" s="4">
+        <v>2</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F339" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A340" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C340" s="4">
+        <v>5</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F340" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A341" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C341" s="4">
+        <v>123</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F341" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A342" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C342" s="4">
+        <v>52</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F342" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A343" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C343" s="4">
+        <v>39</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F343" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A344" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C344" s="4">
+        <v>32</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F344" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A345" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B345" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C345" s="4">
+        <v>3</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F345" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A346" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B346" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C346" s="4">
+        <v>0</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F346" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A347" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B347" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C347" s="4">
+        <v>76</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F347" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A348" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B348" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C348" s="4">
+        <v>46</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F348" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A349" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B349" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C349" s="4">
+        <v>121</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F349" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A350" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B350" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C350" s="4">
+        <v>2</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F350" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A351" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B351" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C351" s="4">
+        <v>515</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F351" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A352" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B352" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C352" s="4">
+        <v>1</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F352" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A353" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B353" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C353" s="4">
+        <v>32</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F353" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A354" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B354" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C354" s="4">
+        <v>52</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F354" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A355" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B355" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C355" s="4">
+        <v>2</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F355" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A356" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B356" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C356" s="4">
+        <v>11</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F356" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A357" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B357" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C357" s="4">
+        <v>36</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F357" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A358" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B358" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C358" s="4">
+        <v>1</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F358" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A359" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B359" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C359" s="4">
+        <v>48</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F359" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A360" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B360" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C360" s="4">
+        <v>15</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F360" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A361" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B361" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C361" s="4">
+        <v>3</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F361" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A362" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B362" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C362" s="4">
+        <v>135</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F362" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A363" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B363" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C363" s="4">
+        <v>2</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F363" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A364" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C364" s="4">
+        <v>1</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F364" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A365" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C365" s="4">
+        <v>2</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F365" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A366" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B366" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C366" s="4">
+        <v>184</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F366" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A367" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B367" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C367" s="4">
+        <v>2</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F367" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A368" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B368" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C368" s="4">
+        <v>2</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F368" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A369" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B369" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C369" s="4">
+        <v>6</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F369" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A370" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B370" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C370" s="4">
+        <v>72</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F370" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A371" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B371" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C371" s="4">
+        <v>3</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F371" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A372" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B372" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C372" s="4">
+        <v>72</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F372" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A373" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C373" s="4">
+        <v>2</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F373" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A374" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B374" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C374" s="4">
+        <v>5</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F374" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A375" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B375" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C375" s="4">
+        <v>6</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F375" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A376" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B376" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C376" s="4">
+        <v>16</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F376" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A377" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B377" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C377" s="4">
+        <v>7</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F377" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A378" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B378" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C378" s="4">
+        <v>340</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F378" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A379" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B379" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C379" s="4">
+        <v>355</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F379" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A380" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C380" s="4">
+        <v>18</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F380" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A381" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C381" s="4">
+        <v>3</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F381" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A382" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B382" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C382" s="4">
+        <v>11</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F382" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A383" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B383" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C383" s="4">
+        <v>2</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F383" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A384" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B384" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C384" s="4">
+        <v>1</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F384" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A385" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B385" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C385" s="4">
+        <v>2</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F385" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A386" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B386" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C386" s="4">
+        <v>6</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F386" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A387" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B387" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C387" s="4">
+        <v>9</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F387" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A388" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C388" s="4">
+        <v>51</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F388" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A389" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C389" s="4">
+        <v>0</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F389" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A390" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C390" s="4">
+        <v>53</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F390" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A391" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B391" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C391" s="4">
+        <v>91</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F391" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A392" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C392" s="4">
+        <v>1</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F392" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A393" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C393" s="4">
+        <v>5</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F393" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A394" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B394" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C394" s="4">
+        <v>30</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F394" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A395" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B395" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C395" s="4">
+        <v>0</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F395" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A396" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B396" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C396" s="4">
+        <v>183</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F396" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A397" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B397" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C397" s="4">
+        <v>32</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F397" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A398" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B398" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C398" s="4">
+        <v>2</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F398" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A399" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B399" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C399" s="4">
+        <v>62</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F399" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A400" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B400" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C400" s="4">
+        <v>64</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F400" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A401" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B401" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C401" s="4">
+        <v>3</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F401" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A402" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B402" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C402" s="4">
+        <v>2</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F402" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A403" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B403" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C403" s="4">
+        <v>5</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E403" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F403" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A404" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B404" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C404" s="4">
+        <v>6</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F404" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A405" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B405" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C405" s="4">
+        <v>1</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E405" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F405" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A406" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B406" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C406" s="4">
+        <v>8</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F406" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A407" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B407" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C407" s="4">
+        <v>6</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E407" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F407" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A408" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B408" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C408" s="4">
+        <v>0</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F408" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A409" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B409" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C409" s="4">
+        <v>11</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E409" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F409" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A410" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B410" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C410" s="4">
+        <v>15</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E410" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F410" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A411" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B411" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C411" s="4">
+        <v>22</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F411" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A412" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B412" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C412" s="4">
+        <v>7</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E412" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F412" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A413" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B413" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C413" s="4">
+        <v>3</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E413" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F413" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A414" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B414" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C414" s="4">
+        <v>5</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E414" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F414" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A415" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B415" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C415" s="4">
+        <v>9</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F415" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A416" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B416" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C416" s="4">
+        <v>6</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E416" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F416" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A417" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B417" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C417" s="4">
+        <v>2</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E417" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F417" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A418" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B418" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C418" s="4">
+        <v>1</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E418" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F418" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A419" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B419" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C419" s="4">
+        <v>9</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E419" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F419" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A420" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B420" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C420" s="4">
+        <v>45</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F420" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A421" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C421" s="4">
+        <v>200</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F421" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A422" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B422" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C422" s="4">
+        <v>1</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E422" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F422" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A423" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B423" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C423" s="4">
+        <v>62</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E423" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F423" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A424" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B424" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C424" s="4">
+        <v>1</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F424" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A425" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B425" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C425" s="4">
+        <v>10</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F425" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A426" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B426" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C426" s="4">
+        <v>3</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E426" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F426" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A427" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B427" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C427" s="4">
+        <v>43</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E427" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F427" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A428" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B428" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C428" s="4">
+        <v>17</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E428" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F428" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A429" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B429" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C429" s="4">
+        <v>275</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E429" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F429" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A430" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B430" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C430" s="4">
+        <v>0</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E430" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F430" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A431" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B431" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C431" s="4">
+        <v>12</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E431" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F431" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A432" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B432" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C432" s="4">
+        <v>12</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E432" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F432" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A433" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B433" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C433" s="4">
+        <v>3</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F433" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A434" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B434" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C434" s="4">
+        <v>16</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F434" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A435" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B435" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C435" s="4">
+        <v>2</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F435" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A436" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B436" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C436" s="4">
+        <v>8</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F436" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A437" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B437" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C437" s="4">
+        <v>5</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F437" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A438" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B438" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C438" s="4">
+        <v>1</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F438" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A439" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B439" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C439" s="4">
+        <v>7</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F439" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A440" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B440" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C440" s="4">
+        <v>20</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E440" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F440" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A441" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B441" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C441" s="4">
+        <v>11</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E441" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F441" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A442" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B442" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C442" s="4">
+        <v>129</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E442" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F442" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A443" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B443" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C443" s="4">
+        <v>177</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E443" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F443" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A444" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B444" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C444" s="4">
+        <v>4</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F444" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A445" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B445" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C445" s="4">
+        <v>22</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E445" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F445" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A446" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B446" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C446" s="4">
+        <v>4</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F446" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A447" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B447" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C447" s="4">
+        <v>1</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F447" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A448" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B448" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C448" s="4">
+        <v>59</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F448" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A449" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B449" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C449" s="4">
+        <v>23</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F449" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A450" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B450" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C450" s="4">
+        <v>27</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F450" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A451" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B451" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C451" s="4">
+        <v>2</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F451" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A452" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B452" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C452" s="4">
+        <v>1</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F452" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A453" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B453" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C453" s="4">
+        <v>13</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F453" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A454" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B454" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C454" s="4">
+        <v>9</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F454" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A455" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B455" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C455" s="4">
+        <v>13</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E455" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F455" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A456" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B456" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C456" s="4">
+        <v>9</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F456" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A457" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B457" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C457" s="4">
+        <v>3</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F457" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A458" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B458" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C458" s="4">
+        <v>3</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F458" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A459" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B459" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C459" s="4">
+        <v>45</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F459" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A460" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B460" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C460" s="4">
+        <v>66</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F460" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A461" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B461" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C461" s="4">
+        <v>1</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F461" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A462" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B462" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C462" s="4">
+        <v>25</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F462" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A463" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B463" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C463" s="4">
+        <v>110</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F463" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A464" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B464" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C464" s="4">
+        <v>6</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F464" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A465" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B465" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C465" s="4">
+        <v>63</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E465" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F465" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A466" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B466" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C466" s="4">
+        <v>2</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E466" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F466" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A467" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B467" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C467" s="4">
+        <v>4</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F467" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A468" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B468" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C468" s="4">
+        <v>6</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F468" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A469" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B469" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C469" s="4">
+        <v>4</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F469" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A470" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B470" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C470" s="4">
+        <v>297</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F470" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A471" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B471" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C471" s="4">
+        <v>120</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E471" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F471" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A472" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B472" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C472" s="4">
+        <v>44</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E472" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F472" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A473" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B473" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C473" s="4">
+        <v>4</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E473" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F473" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A474" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B474" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C474" s="4">
+        <v>14</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F474" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A475" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B475" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C475" s="4">
+        <v>0</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F475" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A476" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B476" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C476" s="4">
+        <v>51</v>
+      </c>
+      <c r="D476" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E476" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F476" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A477" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B477" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C477" s="4">
+        <v>2</v>
+      </c>
+      <c r="D477" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E477" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F477" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A478" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B478" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C478" s="4">
+        <v>19</v>
+      </c>
+      <c r="D478" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E478" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F478" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A479" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B479" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C479" s="4">
+        <v>1</v>
+      </c>
+      <c r="D479" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E479" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F479" s="6">
+        <v>45863</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A480" s="4"/>
       <c r="B480" s="2"/>
       <c r="C480" s="5"/>

--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9E5A0F-47DD-4614-A8A2-CD2078735C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0642D4C-38C3-4417-9F01-CBB9E336A8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="178">
   <si>
     <t>cidade</t>
   </si>
@@ -10626,806 +10626,3206 @@
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A480" s="4"/>
-      <c r="B480" s="2"/>
-      <c r="C480" s="5"/>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A481" s="4"/>
-      <c r="B481" s="2"/>
-      <c r="C481" s="5"/>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A482" s="4"/>
-      <c r="B482" s="2"/>
-      <c r="C482" s="5"/>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A483" s="4"/>
-      <c r="B483" s="2"/>
-      <c r="C483" s="5"/>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A484" s="4"/>
-      <c r="B484" s="2"/>
-      <c r="C484" s="5"/>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A485" s="4"/>
-      <c r="B485" s="2"/>
-      <c r="C485" s="5"/>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A486" s="4"/>
-      <c r="B486" s="2"/>
-      <c r="C486" s="5"/>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A487" s="4"/>
-      <c r="B487" s="2"/>
-      <c r="C487" s="5"/>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A488" s="4"/>
-      <c r="B488" s="2"/>
-      <c r="C488" s="5"/>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A489" s="4"/>
-      <c r="B489" s="2"/>
-      <c r="C489" s="5"/>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A490" s="4"/>
-      <c r="B490" s="2"/>
-      <c r="C490" s="5"/>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A491" s="4"/>
-      <c r="B491" s="2"/>
-      <c r="C491" s="5"/>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A492" s="4"/>
-      <c r="B492" s="2"/>
-      <c r="C492" s="5"/>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A493" s="4"/>
-      <c r="B493" s="2"/>
-      <c r="C493" s="5"/>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A494" s="4"/>
-      <c r="B494" s="2"/>
-      <c r="C494" s="5"/>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A495" s="4"/>
-      <c r="B495" s="2"/>
-      <c r="C495" s="5"/>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A496" s="4"/>
-      <c r="B496" s="2"/>
-      <c r="C496" s="5"/>
-    </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A497" s="4"/>
-      <c r="B497" s="2"/>
-      <c r="C497" s="5"/>
-    </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A498" s="4"/>
-      <c r="B498" s="2"/>
-      <c r="C498" s="5"/>
-    </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A499" s="4"/>
-      <c r="B499" s="2"/>
-      <c r="C499" s="5"/>
-    </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A500" s="4"/>
-      <c r="B500" s="2"/>
-      <c r="C500" s="5"/>
-    </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A501" s="4"/>
-      <c r="B501" s="2"/>
-      <c r="C501" s="5"/>
-    </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A502" s="4"/>
-      <c r="B502" s="2"/>
-      <c r="C502" s="5"/>
-    </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A503" s="4"/>
-      <c r="B503" s="2"/>
-      <c r="C503" s="5"/>
-    </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A504" s="4"/>
-      <c r="B504" s="2"/>
-      <c r="C504" s="5"/>
-    </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A505" s="4"/>
-      <c r="B505" s="2"/>
-      <c r="C505" s="5"/>
-    </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A506" s="4"/>
-      <c r="B506" s="2"/>
-      <c r="C506" s="5"/>
-    </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A507" s="4"/>
-      <c r="B507" s="2"/>
-      <c r="C507" s="5"/>
-    </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A508" s="4"/>
-      <c r="B508" s="2"/>
-      <c r="C508" s="5"/>
-    </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A509" s="4"/>
-      <c r="B509" s="2"/>
-      <c r="C509" s="5"/>
-    </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A510" s="4"/>
-      <c r="B510" s="2"/>
-      <c r="C510" s="5"/>
-    </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A511" s="4"/>
-      <c r="B511" s="2"/>
-      <c r="C511" s="5"/>
-    </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A512" s="4"/>
-      <c r="B512" s="2"/>
-      <c r="C512" s="5"/>
-    </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A513" s="4"/>
-      <c r="B513" s="2"/>
-      <c r="C513" s="5"/>
-    </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A514" s="4"/>
-      <c r="B514" s="2"/>
-      <c r="C514" s="5"/>
-    </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A515" s="4"/>
-      <c r="B515" s="2"/>
-      <c r="C515" s="5"/>
-    </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A516" s="4"/>
-      <c r="B516" s="2"/>
-      <c r="C516" s="5"/>
-    </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A517" s="4"/>
-      <c r="B517" s="2"/>
-      <c r="C517" s="5"/>
-    </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A518" s="4"/>
-      <c r="B518" s="2"/>
-      <c r="C518" s="5"/>
-    </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A519" s="4"/>
-      <c r="B519" s="2"/>
-      <c r="C519" s="5"/>
-    </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A520" s="4"/>
-      <c r="B520" s="2"/>
-      <c r="C520" s="5"/>
-    </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A521" s="4"/>
-      <c r="B521" s="2"/>
-      <c r="C521" s="5"/>
-    </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A522" s="4"/>
-      <c r="B522" s="2"/>
-      <c r="C522" s="5"/>
-    </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A523" s="4"/>
-      <c r="B523" s="2"/>
-      <c r="C523" s="5"/>
-    </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A524" s="4"/>
-      <c r="B524" s="2"/>
-      <c r="C524" s="5"/>
-    </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A525" s="4"/>
-      <c r="B525" s="2"/>
-      <c r="C525" s="5"/>
-    </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A526" s="4"/>
-      <c r="B526" s="2"/>
-      <c r="C526" s="5"/>
-    </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A527" s="4"/>
-      <c r="B527" s="2"/>
-      <c r="C527" s="5"/>
-    </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A528" s="4"/>
-      <c r="B528" s="2"/>
-      <c r="C528" s="5"/>
-    </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A529" s="4"/>
-      <c r="B529" s="2"/>
-      <c r="C529" s="5"/>
-    </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A530" s="4"/>
-      <c r="B530" s="2"/>
-      <c r="C530" s="5"/>
-    </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A531" s="4"/>
-      <c r="B531" s="2"/>
-      <c r="C531" s="5"/>
-    </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A532" s="4"/>
-      <c r="B532" s="2"/>
-      <c r="C532" s="5"/>
-    </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A533" s="4"/>
-      <c r="B533" s="2"/>
-      <c r="C533" s="5"/>
-    </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A534" s="4"/>
-      <c r="B534" s="2"/>
-      <c r="C534" s="5"/>
-    </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A535" s="4"/>
-      <c r="B535" s="2"/>
-      <c r="C535" s="5"/>
-    </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A536" s="4"/>
-      <c r="B536" s="2"/>
-      <c r="C536" s="5"/>
-    </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A537" s="4"/>
-      <c r="B537" s="2"/>
-      <c r="C537" s="5"/>
-    </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A538" s="4"/>
-      <c r="B538" s="2"/>
-      <c r="C538" s="5"/>
-    </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A539" s="4"/>
-      <c r="B539" s="2"/>
-      <c r="C539" s="5"/>
-    </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A540" s="4"/>
-      <c r="B540" s="2"/>
-      <c r="C540" s="5"/>
-    </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A541" s="4"/>
-      <c r="B541" s="2"/>
-      <c r="C541" s="5"/>
-    </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A542" s="4"/>
-      <c r="B542" s="2"/>
-      <c r="C542" s="5"/>
-    </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A543" s="4"/>
-      <c r="B543" s="2"/>
-      <c r="C543" s="5"/>
-    </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A544" s="4"/>
-      <c r="B544" s="2"/>
-      <c r="C544" s="5"/>
-    </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A545" s="4"/>
-      <c r="B545" s="2"/>
-      <c r="C545" s="5"/>
-    </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A546" s="4"/>
-      <c r="B546" s="2"/>
-      <c r="C546" s="5"/>
-    </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A547" s="4"/>
-      <c r="B547" s="2"/>
-      <c r="C547" s="5"/>
-    </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A548" s="4"/>
-      <c r="B548" s="2"/>
-      <c r="C548" s="5"/>
-    </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A549" s="4"/>
-      <c r="B549" s="2"/>
-      <c r="C549" s="5"/>
-    </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A550" s="4"/>
-      <c r="B550" s="2"/>
-      <c r="C550" s="5"/>
-    </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A551" s="4"/>
-      <c r="B551" s="2"/>
-      <c r="C551" s="5"/>
-    </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A552" s="4"/>
-      <c r="B552" s="2"/>
-      <c r="C552" s="5"/>
-    </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A553" s="4"/>
-      <c r="B553" s="2"/>
-      <c r="C553" s="5"/>
-    </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A554" s="4"/>
-      <c r="B554" s="2"/>
-      <c r="C554" s="5"/>
-    </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A555" s="4"/>
-      <c r="B555" s="2"/>
-      <c r="C555" s="5"/>
-    </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A556" s="4"/>
-      <c r="B556" s="2"/>
-      <c r="C556" s="5"/>
-    </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A557" s="4"/>
-      <c r="B557" s="2"/>
-      <c r="C557" s="5"/>
-    </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A558" s="4"/>
-      <c r="B558" s="2"/>
-      <c r="C558" s="5"/>
-    </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A559" s="4"/>
-      <c r="B559" s="2"/>
-      <c r="C559" s="5"/>
-    </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A560" s="4"/>
-      <c r="B560" s="2"/>
-      <c r="C560" s="5"/>
-    </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A561" s="4"/>
-      <c r="B561" s="2"/>
-      <c r="C561" s="5"/>
-    </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A562" s="4"/>
-      <c r="B562" s="2"/>
-      <c r="C562" s="5"/>
-    </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A563" s="4"/>
-      <c r="B563" s="2"/>
-      <c r="C563" s="5"/>
-    </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A564" s="4"/>
-      <c r="B564" s="2"/>
-      <c r="C564" s="5"/>
-    </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A565" s="4"/>
-      <c r="B565" s="2"/>
-      <c r="C565" s="5"/>
-    </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A566" s="4"/>
-      <c r="B566" s="2"/>
-      <c r="C566" s="5"/>
-    </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A567" s="4"/>
-      <c r="B567" s="2"/>
-      <c r="C567" s="5"/>
-    </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A568" s="4"/>
-      <c r="B568" s="2"/>
-      <c r="C568" s="5"/>
-    </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A569" s="4"/>
-      <c r="B569" s="2"/>
-      <c r="C569" s="5"/>
-    </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A570" s="4"/>
-      <c r="B570" s="2"/>
-      <c r="C570" s="5"/>
-    </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A571" s="4"/>
-      <c r="B571" s="2"/>
-      <c r="C571" s="5"/>
-    </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A572" s="4"/>
-      <c r="B572" s="2"/>
-      <c r="C572" s="5"/>
-    </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A573" s="4"/>
-      <c r="B573" s="2"/>
-      <c r="C573" s="5"/>
-    </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A574" s="4"/>
-      <c r="B574" s="2"/>
-      <c r="C574" s="5"/>
-    </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A575" s="4"/>
-      <c r="B575" s="2"/>
-      <c r="C575" s="5"/>
-    </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A576" s="4"/>
-      <c r="B576" s="2"/>
-      <c r="C576" s="5"/>
-    </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A577" s="4"/>
-      <c r="B577" s="2"/>
-      <c r="C577" s="5"/>
-    </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A578" s="4"/>
-      <c r="B578" s="2"/>
-      <c r="C578" s="5"/>
-    </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A579" s="4"/>
-      <c r="B579" s="2"/>
-      <c r="C579" s="5"/>
-    </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A580" s="4"/>
-      <c r="B580" s="2"/>
-      <c r="C580" s="5"/>
-    </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A581" s="4"/>
-      <c r="B581" s="2"/>
-      <c r="C581" s="5"/>
-    </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A582" s="4"/>
-      <c r="B582" s="2"/>
-      <c r="C582" s="5"/>
-    </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A583" s="4"/>
-      <c r="B583" s="2"/>
-      <c r="C583" s="5"/>
-    </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A584" s="4"/>
-      <c r="B584" s="2"/>
-      <c r="C584" s="5"/>
-    </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A585" s="4"/>
-      <c r="B585" s="2"/>
-      <c r="C585" s="5"/>
-    </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A586" s="4"/>
-      <c r="B586" s="2"/>
-      <c r="C586" s="5"/>
-    </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A587" s="4"/>
-      <c r="B587" s="2"/>
-      <c r="C587" s="5"/>
-    </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A588" s="4"/>
-      <c r="B588" s="2"/>
-      <c r="C588" s="5"/>
-    </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A589" s="4"/>
-      <c r="B589" s="2"/>
-      <c r="C589" s="5"/>
-    </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A590" s="4"/>
-      <c r="B590" s="2"/>
-      <c r="C590" s="5"/>
-    </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A591" s="4"/>
-      <c r="B591" s="2"/>
-      <c r="C591" s="5"/>
-    </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A592" s="4"/>
-      <c r="B592" s="2"/>
-      <c r="C592" s="5"/>
-    </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A593" s="4"/>
-      <c r="B593" s="2"/>
-      <c r="C593" s="5"/>
-    </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A594" s="4"/>
-      <c r="B594" s="2"/>
-      <c r="C594" s="5"/>
-    </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A595" s="4"/>
-      <c r="B595" s="2"/>
-      <c r="C595" s="5"/>
-    </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A596" s="4"/>
-      <c r="B596" s="2"/>
-      <c r="C596" s="5"/>
-    </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A597" s="4"/>
-      <c r="B597" s="2"/>
-      <c r="C597" s="5"/>
-    </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A598" s="4"/>
-      <c r="B598" s="2"/>
-      <c r="C598" s="5"/>
-    </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A599" s="3"/>
-      <c r="B599" s="2"/>
-      <c r="C599" s="5"/>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A600" s="4"/>
-      <c r="B600" s="2"/>
-      <c r="C600" s="5"/>
-    </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A601" s="4"/>
-      <c r="B601" s="2"/>
-      <c r="C601" s="5"/>
-    </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A602" s="4"/>
-      <c r="B602" s="2"/>
-      <c r="C602" s="5"/>
-    </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A603" s="4"/>
-      <c r="B603" s="2"/>
-      <c r="C603" s="5"/>
-    </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A604" s="4"/>
-      <c r="B604" s="2"/>
-      <c r="C604" s="5"/>
-    </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A605" s="4"/>
-      <c r="B605" s="2"/>
-      <c r="C605" s="5"/>
-    </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A606" s="4"/>
-      <c r="B606" s="2"/>
-      <c r="C606" s="5"/>
-    </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A607" s="4"/>
-      <c r="B607" s="2"/>
-      <c r="C607" s="5"/>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A608" s="4"/>
-      <c r="B608" s="2"/>
-      <c r="C608" s="5"/>
-    </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A609" s="4"/>
-      <c r="B609" s="2"/>
-      <c r="C609" s="5"/>
-    </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A610" s="4"/>
-      <c r="B610" s="2"/>
-      <c r="C610" s="5"/>
-    </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A611" s="4"/>
-      <c r="B611" s="2"/>
-      <c r="C611" s="5"/>
-    </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A612" s="4"/>
-      <c r="B612" s="2"/>
-      <c r="C612" s="5"/>
-    </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A613" s="4"/>
-      <c r="B613" s="2"/>
-      <c r="C613" s="5"/>
-    </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A614" s="4"/>
-      <c r="B614" s="2"/>
-      <c r="C614" s="5"/>
-    </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A615" s="4"/>
-      <c r="B615" s="2"/>
-      <c r="C615" s="5"/>
-    </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A616" s="4"/>
-      <c r="B616" s="2"/>
-      <c r="C616" s="5"/>
-    </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A617" s="4"/>
-      <c r="B617" s="2"/>
-      <c r="C617" s="5"/>
-    </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A618" s="4"/>
-      <c r="B618" s="2"/>
-      <c r="C618" s="5"/>
-    </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A619" s="4"/>
-      <c r="B619" s="2"/>
-      <c r="C619" s="5"/>
-    </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A620" s="4"/>
-      <c r="B620" s="2"/>
-      <c r="C620" s="5"/>
-    </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A621" s="4"/>
-      <c r="B621" s="2"/>
-      <c r="C621" s="5"/>
-    </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A622" s="4"/>
-      <c r="B622" s="2"/>
-      <c r="C622" s="5"/>
-    </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A623" s="4"/>
-      <c r="B623" s="2"/>
-      <c r="C623" s="5"/>
-    </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A624" s="4"/>
-      <c r="B624" s="2"/>
-      <c r="C624" s="5"/>
-    </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A625" s="4"/>
-      <c r="B625" s="2"/>
-      <c r="C625" s="5"/>
-    </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A626" s="4"/>
-      <c r="B626" s="2"/>
-      <c r="C626" s="5"/>
-    </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A627" s="4"/>
-      <c r="B627" s="2"/>
-      <c r="C627" s="5"/>
-    </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A628" s="4"/>
-      <c r="B628" s="2"/>
-      <c r="C628" s="5"/>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A629" s="4"/>
-      <c r="B629" s="2"/>
-      <c r="C629" s="5"/>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A630" s="4"/>
-      <c r="B630" s="2"/>
-      <c r="C630" s="5"/>
-    </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A631" s="4"/>
-      <c r="B631" s="2"/>
-      <c r="C631" s="5"/>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A632" s="4"/>
-      <c r="B632" s="2"/>
-      <c r="C632" s="5"/>
-    </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A633" s="4"/>
-      <c r="B633" s="2"/>
-      <c r="C633" s="5"/>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A634" s="4"/>
-      <c r="B634" s="2"/>
-      <c r="C634" s="5"/>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A635" s="4"/>
-      <c r="B635" s="2"/>
-      <c r="C635" s="5"/>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A636" s="4"/>
-      <c r="B636" s="2"/>
-      <c r="C636" s="5"/>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A637" s="4"/>
-      <c r="B637" s="2"/>
-      <c r="C637" s="5"/>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A638" s="4"/>
-      <c r="B638" s="2"/>
-      <c r="C638" s="5"/>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A639" s="4"/>
-      <c r="B639" s="2"/>
-      <c r="C639" s="5"/>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A480" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B480" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C480" s="5">
+        <v>17</v>
+      </c>
+      <c r="D480" t="s">
+        <v>176</v>
+      </c>
+      <c r="E480" t="s">
+        <v>165</v>
+      </c>
+      <c r="F480" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A481" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B481" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C481" s="5">
+        <v>14</v>
+      </c>
+      <c r="D481" t="s">
+        <v>176</v>
+      </c>
+      <c r="E481" t="s">
+        <v>165</v>
+      </c>
+      <c r="F481" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A482" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B482" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C482" s="5">
+        <v>3</v>
+      </c>
+      <c r="D482" t="s">
+        <v>176</v>
+      </c>
+      <c r="E482" t="s">
+        <v>165</v>
+      </c>
+      <c r="F482" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A483" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C483" s="5">
+        <v>4</v>
+      </c>
+      <c r="D483" t="s">
+        <v>166</v>
+      </c>
+      <c r="E483" t="s">
+        <v>165</v>
+      </c>
+      <c r="F483" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A484" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B484" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C484" s="5">
+        <v>0</v>
+      </c>
+      <c r="D484" t="s">
+        <v>176</v>
+      </c>
+      <c r="E484" t="s">
+        <v>165</v>
+      </c>
+      <c r="F484" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A485" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B485" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C485" s="5">
+        <v>157</v>
+      </c>
+      <c r="D485" t="s">
+        <v>167</v>
+      </c>
+      <c r="E485" t="s">
+        <v>165</v>
+      </c>
+      <c r="F485" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A486" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B486" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C486" s="5">
+        <v>8</v>
+      </c>
+      <c r="D486" t="s">
+        <v>168</v>
+      </c>
+      <c r="E486" t="s">
+        <v>169</v>
+      </c>
+      <c r="F486" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A487" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C487" s="5">
+        <v>1</v>
+      </c>
+      <c r="D487" t="s">
+        <v>168</v>
+      </c>
+      <c r="E487" t="s">
+        <v>169</v>
+      </c>
+      <c r="F487" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A488" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B488" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C488" s="5">
+        <v>0</v>
+      </c>
+      <c r="D488" t="s">
+        <v>170</v>
+      </c>
+      <c r="E488" t="s">
+        <v>165</v>
+      </c>
+      <c r="F488" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A489" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B489" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C489" s="5">
+        <v>1</v>
+      </c>
+      <c r="D489" t="s">
+        <v>168</v>
+      </c>
+      <c r="E489" t="s">
+        <v>169</v>
+      </c>
+      <c r="F489" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A490" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B490" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C490" s="5">
+        <v>0</v>
+      </c>
+      <c r="D490" t="s">
+        <v>168</v>
+      </c>
+      <c r="E490" t="s">
+        <v>171</v>
+      </c>
+      <c r="F490" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A491" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B491" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C491" s="5">
+        <v>13</v>
+      </c>
+      <c r="D491" t="s">
+        <v>168</v>
+      </c>
+      <c r="E491" t="s">
+        <v>172</v>
+      </c>
+      <c r="F491" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A492" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B492" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C492" s="5">
+        <v>111</v>
+      </c>
+      <c r="D492" t="s">
+        <v>167</v>
+      </c>
+      <c r="E492" t="s">
+        <v>165</v>
+      </c>
+      <c r="F492" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A493" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B493" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C493" s="5">
+        <v>2</v>
+      </c>
+      <c r="D493" t="s">
+        <v>170</v>
+      </c>
+      <c r="E493" t="s">
+        <v>165</v>
+      </c>
+      <c r="F493" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A494" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B494" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C494" s="5">
+        <v>1</v>
+      </c>
+      <c r="D494" t="s">
+        <v>176</v>
+      </c>
+      <c r="E494" t="s">
+        <v>165</v>
+      </c>
+      <c r="F494" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A495" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B495" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C495" s="5">
+        <v>1</v>
+      </c>
+      <c r="D495" t="s">
+        <v>176</v>
+      </c>
+      <c r="E495" t="s">
+        <v>165</v>
+      </c>
+      <c r="F495" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A496" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B496" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C496" s="5">
+        <v>11</v>
+      </c>
+      <c r="D496" t="s">
+        <v>166</v>
+      </c>
+      <c r="E496" t="s">
+        <v>165</v>
+      </c>
+      <c r="F496" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A497" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B497" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C497" s="5">
+        <v>90</v>
+      </c>
+      <c r="D497" t="s">
+        <v>167</v>
+      </c>
+      <c r="E497" t="s">
+        <v>165</v>
+      </c>
+      <c r="F497" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A498" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B498" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C498" s="5">
+        <v>13</v>
+      </c>
+      <c r="D498" t="s">
+        <v>176</v>
+      </c>
+      <c r="E498" t="s">
+        <v>165</v>
+      </c>
+      <c r="F498" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A499" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B499" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C499" s="5">
+        <v>2</v>
+      </c>
+      <c r="D499" t="s">
+        <v>168</v>
+      </c>
+      <c r="E499" t="s">
+        <v>169</v>
+      </c>
+      <c r="F499" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A500" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C500" s="5">
+        <v>5</v>
+      </c>
+      <c r="D500" t="s">
+        <v>176</v>
+      </c>
+      <c r="E500" t="s">
+        <v>165</v>
+      </c>
+      <c r="F500" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A501" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B501" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C501" s="5">
+        <v>128</v>
+      </c>
+      <c r="D501" t="s">
+        <v>167</v>
+      </c>
+      <c r="E501" t="s">
+        <v>165</v>
+      </c>
+      <c r="F501" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A502" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B502" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C502" s="5">
+        <v>52</v>
+      </c>
+      <c r="D502" t="s">
+        <v>166</v>
+      </c>
+      <c r="E502" t="s">
+        <v>165</v>
+      </c>
+      <c r="F502" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A503" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B503" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C503" s="5">
+        <v>38</v>
+      </c>
+      <c r="D503" t="s">
+        <v>167</v>
+      </c>
+      <c r="E503" t="s">
+        <v>165</v>
+      </c>
+      <c r="F503" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A504" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B504" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C504" s="5">
+        <v>33</v>
+      </c>
+      <c r="D504" t="s">
+        <v>168</v>
+      </c>
+      <c r="E504" t="s">
+        <v>171</v>
+      </c>
+      <c r="F504" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A505" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B505" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C505" s="5">
+        <v>2</v>
+      </c>
+      <c r="D505" t="s">
+        <v>167</v>
+      </c>
+      <c r="E505" t="s">
+        <v>165</v>
+      </c>
+      <c r="F505" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A506" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B506" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C506" s="5">
+        <v>0</v>
+      </c>
+      <c r="D506" t="s">
+        <v>168</v>
+      </c>
+      <c r="E506" t="s">
+        <v>169</v>
+      </c>
+      <c r="F506" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A507" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B507" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C507" s="5">
+        <v>75</v>
+      </c>
+      <c r="D507" t="s">
+        <v>173</v>
+      </c>
+      <c r="E507" t="s">
+        <v>165</v>
+      </c>
+      <c r="F507" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A508" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B508" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C508" s="5">
+        <v>46</v>
+      </c>
+      <c r="D508" t="s">
+        <v>166</v>
+      </c>
+      <c r="E508" t="s">
+        <v>165</v>
+      </c>
+      <c r="F508" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A509" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B509" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C509" s="5">
+        <v>122</v>
+      </c>
+      <c r="D509" t="s">
+        <v>167</v>
+      </c>
+      <c r="E509" t="s">
+        <v>165</v>
+      </c>
+      <c r="F509" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A510" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B510" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C510" s="5">
+        <v>2</v>
+      </c>
+      <c r="D510" t="s">
+        <v>168</v>
+      </c>
+      <c r="E510" t="s">
+        <v>169</v>
+      </c>
+      <c r="F510" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A511" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B511" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C511" s="5">
+        <v>504</v>
+      </c>
+      <c r="D511" t="s">
+        <v>176</v>
+      </c>
+      <c r="E511" t="s">
+        <v>165</v>
+      </c>
+      <c r="F511" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A512" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B512" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C512" s="5">
+        <v>1</v>
+      </c>
+      <c r="D512" t="s">
+        <v>168</v>
+      </c>
+      <c r="E512" t="s">
+        <v>172</v>
+      </c>
+      <c r="F512" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A513" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B513" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C513" s="5">
+        <v>32</v>
+      </c>
+      <c r="D513" t="s">
+        <v>176</v>
+      </c>
+      <c r="E513" t="s">
+        <v>165</v>
+      </c>
+      <c r="F513" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A514" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C514" s="5">
+        <v>52</v>
+      </c>
+      <c r="D514" t="s">
+        <v>176</v>
+      </c>
+      <c r="E514" t="s">
+        <v>165</v>
+      </c>
+      <c r="F514" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A515" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B515" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C515" s="5">
+        <v>2</v>
+      </c>
+      <c r="D515" t="s">
+        <v>176</v>
+      </c>
+      <c r="E515" t="s">
+        <v>165</v>
+      </c>
+      <c r="F515" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A516" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B516" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C516" s="5">
+        <v>11</v>
+      </c>
+      <c r="D516" t="s">
+        <v>170</v>
+      </c>
+      <c r="E516" t="s">
+        <v>165</v>
+      </c>
+      <c r="F516" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A517" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B517" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C517" s="5">
+        <v>37</v>
+      </c>
+      <c r="D517" t="s">
+        <v>170</v>
+      </c>
+      <c r="E517" t="s">
+        <v>165</v>
+      </c>
+      <c r="F517" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A518" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B518" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C518" s="5">
+        <v>1</v>
+      </c>
+      <c r="D518" t="s">
+        <v>168</v>
+      </c>
+      <c r="E518" t="s">
+        <v>169</v>
+      </c>
+      <c r="F518" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A519" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B519" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C519" s="5">
+        <v>47</v>
+      </c>
+      <c r="D519" t="s">
+        <v>173</v>
+      </c>
+      <c r="E519" t="s">
+        <v>165</v>
+      </c>
+      <c r="F519" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A520" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B520" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C520" s="5">
+        <v>15</v>
+      </c>
+      <c r="D520" t="s">
+        <v>176</v>
+      </c>
+      <c r="E520" t="s">
+        <v>165</v>
+      </c>
+      <c r="F520" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A521" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B521" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C521" s="5">
+        <v>3</v>
+      </c>
+      <c r="D521" t="s">
+        <v>176</v>
+      </c>
+      <c r="E521" t="s">
+        <v>165</v>
+      </c>
+      <c r="F521" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A522" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B522" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C522" s="5">
+        <v>135</v>
+      </c>
+      <c r="D522" t="s">
+        <v>173</v>
+      </c>
+      <c r="E522" t="s">
+        <v>165</v>
+      </c>
+      <c r="F522" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A523" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B523" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C523" s="5">
+        <v>2</v>
+      </c>
+      <c r="D523" t="s">
+        <v>168</v>
+      </c>
+      <c r="E523" t="s">
+        <v>169</v>
+      </c>
+      <c r="F523" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A524" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B524" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C524" s="5">
+        <v>1</v>
+      </c>
+      <c r="D524" t="s">
+        <v>176</v>
+      </c>
+      <c r="E524" t="s">
+        <v>165</v>
+      </c>
+      <c r="F524" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A525" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B525" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C525" s="5">
+        <v>3</v>
+      </c>
+      <c r="D525" t="s">
+        <v>168</v>
+      </c>
+      <c r="E525" t="s">
+        <v>172</v>
+      </c>
+      <c r="F525" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A526" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B526" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C526" s="5">
+        <v>184</v>
+      </c>
+      <c r="D526" t="s">
+        <v>168</v>
+      </c>
+      <c r="E526" t="s">
+        <v>169</v>
+      </c>
+      <c r="F526" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A527" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B527" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C527" s="5">
+        <v>1</v>
+      </c>
+      <c r="D527" t="s">
+        <v>168</v>
+      </c>
+      <c r="E527" t="s">
+        <v>169</v>
+      </c>
+      <c r="F527" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A528" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B528" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C528" s="5">
+        <v>3</v>
+      </c>
+      <c r="D528" t="s">
+        <v>168</v>
+      </c>
+      <c r="E528" t="s">
+        <v>172</v>
+      </c>
+      <c r="F528" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A529" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B529" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C529" s="5">
+        <v>6</v>
+      </c>
+      <c r="D529" t="s">
+        <v>167</v>
+      </c>
+      <c r="E529" t="s">
+        <v>165</v>
+      </c>
+      <c r="F529" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A530" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B530" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C530" s="5">
+        <v>72</v>
+      </c>
+      <c r="D530" t="s">
+        <v>167</v>
+      </c>
+      <c r="E530" t="s">
+        <v>165</v>
+      </c>
+      <c r="F530" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A531" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B531" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C531" s="5">
+        <v>3</v>
+      </c>
+      <c r="D531" t="s">
+        <v>176</v>
+      </c>
+      <c r="E531" t="s">
+        <v>165</v>
+      </c>
+      <c r="F531" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A532" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B532" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C532" s="5">
+        <v>71</v>
+      </c>
+      <c r="D532" t="s">
+        <v>170</v>
+      </c>
+      <c r="E532" t="s">
+        <v>165</v>
+      </c>
+      <c r="F532" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A533" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B533" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C533" s="5">
+        <v>2</v>
+      </c>
+      <c r="D533" t="s">
+        <v>176</v>
+      </c>
+      <c r="E533" t="s">
+        <v>165</v>
+      </c>
+      <c r="F533" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A534" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B534" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C534" s="5">
+        <v>5</v>
+      </c>
+      <c r="D534" t="s">
+        <v>167</v>
+      </c>
+      <c r="E534" t="s">
+        <v>165</v>
+      </c>
+      <c r="F534" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A535" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B535" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C535" s="5">
+        <v>9</v>
+      </c>
+      <c r="D535" t="s">
+        <v>168</v>
+      </c>
+      <c r="E535" t="s">
+        <v>169</v>
+      </c>
+      <c r="F535" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A536" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B536" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C536" s="5">
+        <v>16</v>
+      </c>
+      <c r="D536" t="s">
+        <v>168</v>
+      </c>
+      <c r="E536" t="s">
+        <v>172</v>
+      </c>
+      <c r="F536" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A537" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B537" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C537" s="5">
+        <v>7</v>
+      </c>
+      <c r="D537" t="s">
+        <v>173</v>
+      </c>
+      <c r="E537" t="s">
+        <v>165</v>
+      </c>
+      <c r="F537" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A538" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B538" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C538" s="5">
+        <v>336</v>
+      </c>
+      <c r="D538" t="s">
+        <v>167</v>
+      </c>
+      <c r="E538" t="s">
+        <v>165</v>
+      </c>
+      <c r="F538" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A539" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B539" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C539" s="5">
+        <v>353</v>
+      </c>
+      <c r="D539" t="s">
+        <v>166</v>
+      </c>
+      <c r="E539" t="s">
+        <v>165</v>
+      </c>
+      <c r="F539" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A540" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B540" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C540" s="5">
+        <v>18</v>
+      </c>
+      <c r="D540" t="s">
+        <v>176</v>
+      </c>
+      <c r="E540" t="s">
+        <v>165</v>
+      </c>
+      <c r="F540" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A541" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B541" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C541" s="5">
+        <v>3</v>
+      </c>
+      <c r="D541" t="s">
+        <v>168</v>
+      </c>
+      <c r="E541" t="s">
+        <v>174</v>
+      </c>
+      <c r="F541" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A542" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C542" s="5">
+        <v>12</v>
+      </c>
+      <c r="D542" t="s">
+        <v>170</v>
+      </c>
+      <c r="E542" t="s">
+        <v>165</v>
+      </c>
+      <c r="F542" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A543" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C543" s="5">
+        <v>3</v>
+      </c>
+      <c r="D543" t="s">
+        <v>176</v>
+      </c>
+      <c r="E543" t="s">
+        <v>165</v>
+      </c>
+      <c r="F543" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A544" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B544" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C544" s="5">
+        <v>1</v>
+      </c>
+      <c r="D544" t="s">
+        <v>168</v>
+      </c>
+      <c r="E544" t="s">
+        <v>172</v>
+      </c>
+      <c r="F544" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A545" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B545" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C545" s="5">
+        <v>2</v>
+      </c>
+      <c r="D545" t="s">
+        <v>176</v>
+      </c>
+      <c r="E545" t="s">
+        <v>165</v>
+      </c>
+      <c r="F545" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A546" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B546" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C546" s="5">
+        <v>5</v>
+      </c>
+      <c r="D546" t="s">
+        <v>176</v>
+      </c>
+      <c r="E546" t="s">
+        <v>165</v>
+      </c>
+      <c r="F546" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A547" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B547" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C547" s="5">
+        <v>9</v>
+      </c>
+      <c r="D547" t="s">
+        <v>176</v>
+      </c>
+      <c r="E547" t="s">
+        <v>165</v>
+      </c>
+      <c r="F547" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A548" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B548" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C548" s="5">
+        <v>51</v>
+      </c>
+      <c r="D548" t="s">
+        <v>166</v>
+      </c>
+      <c r="E548" t="s">
+        <v>165</v>
+      </c>
+      <c r="F548" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A549" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B549" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C549" s="5">
+        <v>0</v>
+      </c>
+      <c r="D549" t="s">
+        <v>176</v>
+      </c>
+      <c r="E549" t="s">
+        <v>165</v>
+      </c>
+      <c r="F549" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A550" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B550" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C550" s="5">
+        <v>52</v>
+      </c>
+      <c r="D550" t="s">
+        <v>170</v>
+      </c>
+      <c r="E550" t="s">
+        <v>165</v>
+      </c>
+      <c r="F550" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A551" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B551" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C551" s="5">
+        <v>91</v>
+      </c>
+      <c r="D551" t="s">
+        <v>166</v>
+      </c>
+      <c r="E551" t="s">
+        <v>165</v>
+      </c>
+      <c r="F551" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A552" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B552" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C552" s="5">
+        <v>1</v>
+      </c>
+      <c r="D552" t="s">
+        <v>168</v>
+      </c>
+      <c r="E552" t="s">
+        <v>169</v>
+      </c>
+      <c r="F552" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A553" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B553" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C553" s="5">
+        <v>4</v>
+      </c>
+      <c r="D553" t="s">
+        <v>168</v>
+      </c>
+      <c r="E553" t="s">
+        <v>169</v>
+      </c>
+      <c r="F553" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A554" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B554" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C554" s="5">
+        <v>30</v>
+      </c>
+      <c r="D554" t="s">
+        <v>176</v>
+      </c>
+      <c r="E554" t="s">
+        <v>165</v>
+      </c>
+      <c r="F554" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A555" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B555" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C555" s="5">
+        <v>0</v>
+      </c>
+      <c r="D555" t="s">
+        <v>176</v>
+      </c>
+      <c r="E555" t="s">
+        <v>165</v>
+      </c>
+      <c r="F555" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A556" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C556" s="5">
+        <v>182</v>
+      </c>
+      <c r="D556" t="s">
+        <v>170</v>
+      </c>
+      <c r="E556" t="s">
+        <v>165</v>
+      </c>
+      <c r="F556" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A557" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C557" s="5">
+        <v>32</v>
+      </c>
+      <c r="D557" t="s">
+        <v>168</v>
+      </c>
+      <c r="E557" t="s">
+        <v>174</v>
+      </c>
+      <c r="F557" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A558" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C558" s="5">
+        <v>2</v>
+      </c>
+      <c r="D558" t="s">
+        <v>176</v>
+      </c>
+      <c r="E558" t="s">
+        <v>165</v>
+      </c>
+      <c r="F558" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A559" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C559" s="5">
+        <v>62</v>
+      </c>
+      <c r="D559" t="s">
+        <v>167</v>
+      </c>
+      <c r="E559" t="s">
+        <v>165</v>
+      </c>
+      <c r="F559" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A560" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B560" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C560" s="5">
+        <v>64</v>
+      </c>
+      <c r="D560" t="s">
+        <v>176</v>
+      </c>
+      <c r="E560" t="s">
+        <v>165</v>
+      </c>
+      <c r="F560" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A561" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B561" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C561" s="5">
+        <v>3</v>
+      </c>
+      <c r="D561" t="s">
+        <v>168</v>
+      </c>
+      <c r="E561" t="s">
+        <v>169</v>
+      </c>
+      <c r="F561" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A562" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B562" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C562" s="5">
+        <v>2</v>
+      </c>
+      <c r="D562" t="s">
+        <v>173</v>
+      </c>
+      <c r="E562" t="s">
+        <v>165</v>
+      </c>
+      <c r="F562" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A563" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B563" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C563" s="5">
+        <v>4</v>
+      </c>
+      <c r="D563" t="s">
+        <v>176</v>
+      </c>
+      <c r="E563" t="s">
+        <v>165</v>
+      </c>
+      <c r="F563" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A564" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B564" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C564" s="5">
+        <v>6</v>
+      </c>
+      <c r="D564" t="s">
+        <v>173</v>
+      </c>
+      <c r="E564" t="s">
+        <v>165</v>
+      </c>
+      <c r="F564" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A565" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B565" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C565" s="5">
+        <v>1</v>
+      </c>
+      <c r="D565" t="s">
+        <v>168</v>
+      </c>
+      <c r="E565" t="s">
+        <v>169</v>
+      </c>
+      <c r="F565" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A566" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B566" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C566" s="5">
+        <v>8</v>
+      </c>
+      <c r="D566" t="s">
+        <v>173</v>
+      </c>
+      <c r="E566" t="s">
+        <v>165</v>
+      </c>
+      <c r="F566" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A567" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B567" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C567" s="5">
+        <v>6</v>
+      </c>
+      <c r="D567" t="s">
+        <v>176</v>
+      </c>
+      <c r="E567" t="s">
+        <v>165</v>
+      </c>
+      <c r="F567" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A568" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B568" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C568" s="5">
+        <v>0</v>
+      </c>
+      <c r="D568" t="s">
+        <v>176</v>
+      </c>
+      <c r="E568" t="s">
+        <v>165</v>
+      </c>
+      <c r="F568" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A569" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B569" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C569" s="5">
+        <v>11</v>
+      </c>
+      <c r="D569" t="s">
+        <v>170</v>
+      </c>
+      <c r="E569" t="s">
+        <v>165</v>
+      </c>
+      <c r="F569" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A570" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B570" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C570" s="5">
+        <v>15</v>
+      </c>
+      <c r="D570" t="s">
+        <v>173</v>
+      </c>
+      <c r="E570" t="s">
+        <v>165</v>
+      </c>
+      <c r="F570" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A571" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B571" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C571" s="5">
+        <v>22</v>
+      </c>
+      <c r="D571" t="s">
+        <v>168</v>
+      </c>
+      <c r="E571" t="s">
+        <v>171</v>
+      </c>
+      <c r="F571" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A572" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B572" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C572" s="5">
+        <v>9</v>
+      </c>
+      <c r="D572" t="s">
+        <v>176</v>
+      </c>
+      <c r="E572" t="s">
+        <v>165</v>
+      </c>
+      <c r="F572" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A573" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B573" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C573" s="5">
+        <v>3</v>
+      </c>
+      <c r="D573" t="s">
+        <v>176</v>
+      </c>
+      <c r="E573" t="s">
+        <v>165</v>
+      </c>
+      <c r="F573" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A574" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B574" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C574" s="5">
+        <v>5</v>
+      </c>
+      <c r="D574" t="s">
+        <v>173</v>
+      </c>
+      <c r="E574" t="s">
+        <v>165</v>
+      </c>
+      <c r="F574" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A575" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B575" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C575" s="5">
+        <v>10</v>
+      </c>
+      <c r="D575" t="s">
+        <v>167</v>
+      </c>
+      <c r="E575" t="s">
+        <v>165</v>
+      </c>
+      <c r="F575" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A576" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B576" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C576" s="5">
+        <v>6</v>
+      </c>
+      <c r="D576" t="s">
+        <v>173</v>
+      </c>
+      <c r="E576" t="s">
+        <v>165</v>
+      </c>
+      <c r="F576" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A577" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B577" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C577" s="5">
+        <v>2</v>
+      </c>
+      <c r="D577" t="s">
+        <v>176</v>
+      </c>
+      <c r="E577" t="s">
+        <v>165</v>
+      </c>
+      <c r="F577" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A578" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B578" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C578" s="5">
+        <v>1</v>
+      </c>
+      <c r="D578" t="s">
+        <v>168</v>
+      </c>
+      <c r="E578" t="s">
+        <v>169</v>
+      </c>
+      <c r="F578" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A579" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B579" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C579" s="5">
+        <v>9</v>
+      </c>
+      <c r="D579" t="s">
+        <v>170</v>
+      </c>
+      <c r="E579" t="s">
+        <v>165</v>
+      </c>
+      <c r="F579" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A580" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B580" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C580" s="5">
+        <v>42</v>
+      </c>
+      <c r="D580" t="s">
+        <v>176</v>
+      </c>
+      <c r="E580" t="s">
+        <v>165</v>
+      </c>
+      <c r="F580" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A581" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B581" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C581" s="5">
+        <v>199</v>
+      </c>
+      <c r="D581" t="s">
+        <v>168</v>
+      </c>
+      <c r="E581" t="s">
+        <v>172</v>
+      </c>
+      <c r="F581" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A582" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B582" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C582" s="5">
+        <v>1</v>
+      </c>
+      <c r="D582" t="s">
+        <v>176</v>
+      </c>
+      <c r="E582" t="s">
+        <v>165</v>
+      </c>
+      <c r="F582" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A583" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B583" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C583" s="5">
+        <v>60</v>
+      </c>
+      <c r="D583" t="s">
+        <v>176</v>
+      </c>
+      <c r="E583" t="s">
+        <v>165</v>
+      </c>
+      <c r="F583" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A584" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B584" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C584" s="5">
+        <v>1</v>
+      </c>
+      <c r="D584" t="s">
+        <v>168</v>
+      </c>
+      <c r="E584" t="s">
+        <v>169</v>
+      </c>
+      <c r="F584" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A585" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B585" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C585" s="5">
+        <v>11</v>
+      </c>
+      <c r="D585" t="s">
+        <v>173</v>
+      </c>
+      <c r="E585" t="s">
+        <v>165</v>
+      </c>
+      <c r="F585" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A586" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C586" s="5">
+        <v>3</v>
+      </c>
+      <c r="D586" t="s">
+        <v>173</v>
+      </c>
+      <c r="E586" t="s">
+        <v>165</v>
+      </c>
+      <c r="F586" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A587" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B587" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C587" s="5">
+        <v>42</v>
+      </c>
+      <c r="D587" t="s">
+        <v>176</v>
+      </c>
+      <c r="E587" t="s">
+        <v>165</v>
+      </c>
+      <c r="F587" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A588" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B588" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C588" s="5">
+        <v>19</v>
+      </c>
+      <c r="D588" t="s">
+        <v>176</v>
+      </c>
+      <c r="E588" t="s">
+        <v>165</v>
+      </c>
+      <c r="F588" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A589" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B589" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C589" s="5">
+        <v>274</v>
+      </c>
+      <c r="D589" t="s">
+        <v>166</v>
+      </c>
+      <c r="E589" t="s">
+        <v>165</v>
+      </c>
+      <c r="F589" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A590" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B590" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C590" s="5">
+        <v>0</v>
+      </c>
+      <c r="D590" t="s">
+        <v>168</v>
+      </c>
+      <c r="E590" t="s">
+        <v>169</v>
+      </c>
+      <c r="F590" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A591" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B591" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C591" s="5">
+        <v>12</v>
+      </c>
+      <c r="D591" t="s">
+        <v>176</v>
+      </c>
+      <c r="E591" t="s">
+        <v>165</v>
+      </c>
+      <c r="F591" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A592" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B592" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C592" s="5">
+        <v>13</v>
+      </c>
+      <c r="D592" t="s">
+        <v>166</v>
+      </c>
+      <c r="E592" t="s">
+        <v>165</v>
+      </c>
+      <c r="F592" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A593" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B593" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C593" s="5">
+        <v>3</v>
+      </c>
+      <c r="D593" t="s">
+        <v>168</v>
+      </c>
+      <c r="E593" t="s">
+        <v>172</v>
+      </c>
+      <c r="F593" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A594" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B594" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C594" s="5">
+        <v>19</v>
+      </c>
+      <c r="D594" t="s">
+        <v>166</v>
+      </c>
+      <c r="E594" t="s">
+        <v>165</v>
+      </c>
+      <c r="F594" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A595" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B595" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C595" s="5">
+        <v>3</v>
+      </c>
+      <c r="D595" t="s">
+        <v>166</v>
+      </c>
+      <c r="E595" t="s">
+        <v>165</v>
+      </c>
+      <c r="F595" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A596" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B596" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C596" s="5">
+        <v>8</v>
+      </c>
+      <c r="D596" t="s">
+        <v>176</v>
+      </c>
+      <c r="E596" t="s">
+        <v>165</v>
+      </c>
+      <c r="F596" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A597" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B597" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C597" s="5">
+        <v>6</v>
+      </c>
+      <c r="D597" t="s">
+        <v>176</v>
+      </c>
+      <c r="E597" t="s">
+        <v>165</v>
+      </c>
+      <c r="F597" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A598" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B598" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C598" s="5">
+        <v>1</v>
+      </c>
+      <c r="D598" t="s">
+        <v>168</v>
+      </c>
+      <c r="E598" t="s">
+        <v>171</v>
+      </c>
+      <c r="F598" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A599" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B599" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C599" s="5">
+        <v>7</v>
+      </c>
+      <c r="D599" t="s">
+        <v>176</v>
+      </c>
+      <c r="E599" t="s">
+        <v>165</v>
+      </c>
+      <c r="F599" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A600" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B600" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C600" s="5">
+        <v>20</v>
+      </c>
+      <c r="D600" t="s">
+        <v>168</v>
+      </c>
+      <c r="E600" t="s">
+        <v>174</v>
+      </c>
+      <c r="F600" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A601" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B601" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C601" s="5">
+        <v>11</v>
+      </c>
+      <c r="D601" t="s">
+        <v>168</v>
+      </c>
+      <c r="E601" t="s">
+        <v>171</v>
+      </c>
+      <c r="F601" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A602" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B602" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C602" s="5">
+        <v>130</v>
+      </c>
+      <c r="D602" t="s">
+        <v>167</v>
+      </c>
+      <c r="E602" t="s">
+        <v>165</v>
+      </c>
+      <c r="F602" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A603" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C603" s="5">
+        <v>175</v>
+      </c>
+      <c r="D603" t="s">
+        <v>167</v>
+      </c>
+      <c r="E603" t="s">
+        <v>165</v>
+      </c>
+      <c r="F603" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A604" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B604" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C604" s="5">
+        <v>4</v>
+      </c>
+      <c r="D604" t="s">
+        <v>176</v>
+      </c>
+      <c r="E604" t="s">
+        <v>165</v>
+      </c>
+      <c r="F604" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A605" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B605" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C605" s="5">
+        <v>21</v>
+      </c>
+      <c r="D605" t="s">
+        <v>176</v>
+      </c>
+      <c r="E605" t="s">
+        <v>165</v>
+      </c>
+      <c r="F605" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A606" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B606" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C606" s="5">
+        <v>3</v>
+      </c>
+      <c r="D606" t="s">
+        <v>168</v>
+      </c>
+      <c r="E606" t="s">
+        <v>174</v>
+      </c>
+      <c r="F606" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A607" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B607" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C607" s="5">
+        <v>1</v>
+      </c>
+      <c r="D607" t="s">
+        <v>173</v>
+      </c>
+      <c r="E607" t="s">
+        <v>165</v>
+      </c>
+      <c r="F607" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A608" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B608" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C608" s="5">
+        <v>58</v>
+      </c>
+      <c r="D608" t="s">
+        <v>170</v>
+      </c>
+      <c r="E608" t="s">
+        <v>165</v>
+      </c>
+      <c r="F608" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A609" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B609" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C609" s="5">
+        <v>23</v>
+      </c>
+      <c r="D609" t="s">
+        <v>166</v>
+      </c>
+      <c r="E609" t="s">
+        <v>165</v>
+      </c>
+      <c r="F609" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A610" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C610" s="5">
+        <v>27</v>
+      </c>
+      <c r="D610" t="s">
+        <v>166</v>
+      </c>
+      <c r="E610" t="s">
+        <v>165</v>
+      </c>
+      <c r="F610" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A611" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B611" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C611" s="5">
+        <v>2</v>
+      </c>
+      <c r="D611" t="s">
+        <v>176</v>
+      </c>
+      <c r="E611" t="s">
+        <v>165</v>
+      </c>
+      <c r="F611" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A612" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B612" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C612" s="5">
+        <v>1</v>
+      </c>
+      <c r="D612" t="s">
+        <v>173</v>
+      </c>
+      <c r="E612" t="s">
+        <v>165</v>
+      </c>
+      <c r="F612" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A613" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B613" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C613" s="5">
+        <v>13</v>
+      </c>
+      <c r="D613" t="s">
+        <v>168</v>
+      </c>
+      <c r="E613" t="s">
+        <v>171</v>
+      </c>
+      <c r="F613" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A614" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C614" s="5">
+        <v>9</v>
+      </c>
+      <c r="D614" t="s">
+        <v>176</v>
+      </c>
+      <c r="E614" t="s">
+        <v>165</v>
+      </c>
+      <c r="F614" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A615" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B615" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C615" s="5">
+        <v>13</v>
+      </c>
+      <c r="D615" t="s">
+        <v>176</v>
+      </c>
+      <c r="E615" t="s">
+        <v>165</v>
+      </c>
+      <c r="F615" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A616" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C616" s="5">
+        <v>9</v>
+      </c>
+      <c r="D616" t="s">
+        <v>176</v>
+      </c>
+      <c r="E616" t="s">
+        <v>165</v>
+      </c>
+      <c r="F616" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A617" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B617" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C617" s="5">
+        <v>3</v>
+      </c>
+      <c r="D617" t="s">
+        <v>168</v>
+      </c>
+      <c r="E617" t="s">
+        <v>172</v>
+      </c>
+      <c r="F617" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A618" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B618" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C618" s="5">
+        <v>3</v>
+      </c>
+      <c r="D618" t="s">
+        <v>168</v>
+      </c>
+      <c r="E618" t="s">
+        <v>169</v>
+      </c>
+      <c r="F618" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A619" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B619" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C619" s="5">
+        <v>49</v>
+      </c>
+      <c r="D619" t="s">
+        <v>168</v>
+      </c>
+      <c r="E619" t="s">
+        <v>172</v>
+      </c>
+      <c r="F619" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A620" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B620" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C620" s="5">
+        <v>65</v>
+      </c>
+      <c r="D620" t="s">
+        <v>166</v>
+      </c>
+      <c r="E620" t="s">
+        <v>165</v>
+      </c>
+      <c r="F620" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A621" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B621" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C621" s="5">
+        <v>1</v>
+      </c>
+      <c r="D621" t="s">
+        <v>176</v>
+      </c>
+      <c r="E621" t="s">
+        <v>165</v>
+      </c>
+      <c r="F621" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A622" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B622" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C622" s="5">
+        <v>25</v>
+      </c>
+      <c r="D622" t="s">
+        <v>173</v>
+      </c>
+      <c r="E622" t="s">
+        <v>165</v>
+      </c>
+      <c r="F622" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A623" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B623" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C623" s="5">
+        <v>112</v>
+      </c>
+      <c r="D623" t="s">
+        <v>166</v>
+      </c>
+      <c r="E623" t="s">
+        <v>165</v>
+      </c>
+      <c r="F623" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A624" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C624" s="5">
+        <v>6</v>
+      </c>
+      <c r="D624" t="s">
+        <v>176</v>
+      </c>
+      <c r="E624" t="s">
+        <v>165</v>
+      </c>
+      <c r="F624" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A625" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B625" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C625" s="5">
+        <v>63</v>
+      </c>
+      <c r="D625" t="s">
+        <v>173</v>
+      </c>
+      <c r="E625" t="s">
+        <v>165</v>
+      </c>
+      <c r="F625" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A626" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B626" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C626" s="5">
+        <v>4</v>
+      </c>
+      <c r="D626" t="s">
+        <v>168</v>
+      </c>
+      <c r="E626" t="s">
+        <v>169</v>
+      </c>
+      <c r="F626" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A627" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C627" s="5">
+        <v>4</v>
+      </c>
+      <c r="D627" t="s">
+        <v>168</v>
+      </c>
+      <c r="E627" t="s">
+        <v>171</v>
+      </c>
+      <c r="F627" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A628" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C628" s="5">
+        <v>6</v>
+      </c>
+      <c r="D628" t="s">
+        <v>173</v>
+      </c>
+      <c r="E628" t="s">
+        <v>165</v>
+      </c>
+      <c r="F628" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A629" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B629" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C629" s="5">
+        <v>4</v>
+      </c>
+      <c r="D629" t="s">
+        <v>166</v>
+      </c>
+      <c r="E629" t="s">
+        <v>165</v>
+      </c>
+      <c r="F629" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A630" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B630" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C630" s="5">
+        <v>295</v>
+      </c>
+      <c r="D630" t="s">
+        <v>173</v>
+      </c>
+      <c r="E630" t="s">
+        <v>165</v>
+      </c>
+      <c r="F630" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A631" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B631" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C631" s="5">
+        <v>120</v>
+      </c>
+      <c r="D631" t="s">
+        <v>168</v>
+      </c>
+      <c r="E631" t="s">
+        <v>174</v>
+      </c>
+      <c r="F631" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A632" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C632" s="5">
+        <v>45</v>
+      </c>
+      <c r="D632" t="s">
+        <v>167</v>
+      </c>
+      <c r="E632" t="s">
+        <v>165</v>
+      </c>
+      <c r="F632" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A633" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B633" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C633" s="5">
+        <v>4</v>
+      </c>
+      <c r="D633" t="s">
+        <v>168</v>
+      </c>
+      <c r="E633" t="s">
+        <v>169</v>
+      </c>
+      <c r="F633" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A634" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C634" s="5">
+        <v>14</v>
+      </c>
+      <c r="D634" t="s">
+        <v>166</v>
+      </c>
+      <c r="E634" t="s">
+        <v>165</v>
+      </c>
+      <c r="F634" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A635" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C635" s="5">
+        <v>0</v>
+      </c>
+      <c r="D635" t="s">
+        <v>173</v>
+      </c>
+      <c r="E635" t="s">
+        <v>165</v>
+      </c>
+      <c r="F635" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A636" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C636" s="5">
+        <v>51</v>
+      </c>
+      <c r="D636" t="s">
+        <v>176</v>
+      </c>
+      <c r="E636" t="s">
+        <v>165</v>
+      </c>
+      <c r="F636" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A637" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C637" s="5">
+        <v>2</v>
+      </c>
+      <c r="D637" t="s">
+        <v>176</v>
+      </c>
+      <c r="E637" t="s">
+        <v>165</v>
+      </c>
+      <c r="F637" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A638" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B638" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C638" s="5">
+        <v>19</v>
+      </c>
+      <c r="D638" t="s">
+        <v>176</v>
+      </c>
+      <c r="E638" t="s">
+        <v>165</v>
+      </c>
+      <c r="F638" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A639" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B639" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C639" s="5">
+        <v>1</v>
+      </c>
+      <c r="D639" t="s">
+        <v>167</v>
+      </c>
+      <c r="E639" t="s">
+        <v>165</v>
+      </c>
+      <c r="F639" s="6">
+        <v>45894</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A640" s="4"/>
       <c r="B640" s="2"/>
       <c r="C640" s="5"/>

--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0642D4C-38C3-4417-9F01-CBB9E336A8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFB2AFB-2051-444B-8358-E0B492FA079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2558" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="178">
   <si>
     <t>cidade</t>
   </si>
@@ -13826,806 +13826,3206 @@
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A640" s="4"/>
-      <c r="B640" s="2"/>
-      <c r="C640" s="5"/>
-    </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A641" s="4"/>
-      <c r="B641" s="2"/>
-      <c r="C641" s="5"/>
-    </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A642" s="4"/>
-      <c r="B642" s="2"/>
-      <c r="C642" s="5"/>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A643" s="4"/>
-      <c r="B643" s="2"/>
-      <c r="C643" s="5"/>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A644" s="4"/>
-      <c r="B644" s="2"/>
-      <c r="C644" s="5"/>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A645" s="4"/>
-      <c r="B645" s="2"/>
-      <c r="C645" s="5"/>
-    </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A646" s="4"/>
-      <c r="B646" s="2"/>
-      <c r="C646" s="5"/>
-    </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A647" s="4"/>
-      <c r="B647" s="2"/>
-      <c r="C647" s="5"/>
-    </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A648" s="4"/>
-      <c r="B648" s="2"/>
-      <c r="C648" s="5"/>
-    </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A649" s="4"/>
-      <c r="B649" s="2"/>
-      <c r="C649" s="5"/>
-    </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A650" s="4"/>
-      <c r="B650" s="2"/>
-      <c r="C650" s="5"/>
-    </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A651" s="4"/>
-      <c r="B651" s="2"/>
-      <c r="C651" s="5"/>
-    </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A652" s="4"/>
-      <c r="B652" s="2"/>
-      <c r="C652" s="5"/>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A653" s="4"/>
-      <c r="B653" s="2"/>
-      <c r="C653" s="5"/>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A654" s="4"/>
-      <c r="B654" s="2"/>
-      <c r="C654" s="5"/>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A655" s="4"/>
-      <c r="B655" s="2"/>
-      <c r="C655" s="5"/>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A656" s="4"/>
-      <c r="B656" s="2"/>
-      <c r="C656" s="5"/>
-    </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A657" s="4"/>
-      <c r="B657" s="2"/>
-      <c r="C657" s="5"/>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A658" s="4"/>
-      <c r="B658" s="2"/>
-      <c r="C658" s="5"/>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A659" s="4"/>
-      <c r="B659" s="2"/>
-      <c r="C659" s="5"/>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A660" s="4"/>
-      <c r="B660" s="2"/>
-      <c r="C660" s="5"/>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A661" s="4"/>
-      <c r="B661" s="2"/>
-      <c r="C661" s="5"/>
-    </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A662" s="4"/>
-      <c r="B662" s="2"/>
-      <c r="C662" s="5"/>
-    </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A663" s="4"/>
-      <c r="B663" s="2"/>
-      <c r="C663" s="5"/>
-    </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A664" s="4"/>
-      <c r="B664" s="2"/>
-      <c r="C664" s="5"/>
-    </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A665" s="4"/>
-      <c r="B665" s="2"/>
-      <c r="C665" s="5"/>
-    </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A666" s="4"/>
-      <c r="B666" s="2"/>
-      <c r="C666" s="5"/>
-    </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A667" s="4"/>
-      <c r="B667" s="2"/>
-      <c r="C667" s="5"/>
-    </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A668" s="4"/>
-      <c r="B668" s="2"/>
-      <c r="C668" s="5"/>
-    </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A669" s="4"/>
-      <c r="B669" s="2"/>
-      <c r="C669" s="5"/>
-    </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A670" s="4"/>
-      <c r="B670" s="2"/>
-      <c r="C670" s="5"/>
-    </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A671" s="4"/>
-      <c r="B671" s="2"/>
-      <c r="C671" s="5"/>
-    </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A672" s="4"/>
-      <c r="B672" s="2"/>
-      <c r="C672" s="5"/>
-    </row>
-    <row r="673" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A673" s="4"/>
-      <c r="B673" s="2"/>
-      <c r="C673" s="5"/>
-    </row>
-    <row r="674" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A674" s="4"/>
-      <c r="B674" s="2"/>
-      <c r="C674" s="5"/>
-    </row>
-    <row r="675" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A675" s="4"/>
-      <c r="B675" s="2"/>
-      <c r="C675" s="5"/>
-    </row>
-    <row r="676" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A676" s="4"/>
-      <c r="B676" s="2"/>
-      <c r="C676" s="5"/>
-    </row>
-    <row r="677" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A677" s="4"/>
-      <c r="B677" s="2"/>
-      <c r="C677" s="5"/>
-    </row>
-    <row r="678" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A678" s="4"/>
-      <c r="B678" s="2"/>
-      <c r="C678" s="5"/>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A679" s="4"/>
-      <c r="B679" s="2"/>
-      <c r="C679" s="5"/>
-    </row>
-    <row r="680" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A680" s="4"/>
-      <c r="B680" s="2"/>
-      <c r="C680" s="5"/>
-    </row>
-    <row r="681" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A681" s="4"/>
-      <c r="B681" s="2"/>
-      <c r="C681" s="5"/>
-    </row>
-    <row r="682" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A682" s="4"/>
-      <c r="B682" s="2"/>
-      <c r="C682" s="5"/>
-    </row>
-    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A683" s="4"/>
-      <c r="B683" s="2"/>
-      <c r="C683" s="5"/>
-    </row>
-    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A684" s="4"/>
-      <c r="B684" s="2"/>
-      <c r="C684" s="5"/>
-    </row>
-    <row r="685" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A685" s="4"/>
-      <c r="B685" s="2"/>
-      <c r="C685" s="5"/>
-    </row>
-    <row r="686" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A686" s="4"/>
-      <c r="B686" s="2"/>
-      <c r="C686" s="5"/>
-    </row>
-    <row r="687" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A687" s="4"/>
-      <c r="B687" s="2"/>
-      <c r="C687" s="5"/>
-    </row>
-    <row r="688" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A688" s="4"/>
-      <c r="B688" s="2"/>
-      <c r="C688" s="5"/>
-    </row>
-    <row r="689" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A689" s="4"/>
-      <c r="B689" s="2"/>
-      <c r="C689" s="5"/>
-    </row>
-    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A690" s="4"/>
-      <c r="B690" s="2"/>
-      <c r="C690" s="5"/>
-    </row>
-    <row r="691" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A691" s="4"/>
-      <c r="B691" s="2"/>
-      <c r="C691" s="5"/>
-    </row>
-    <row r="692" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A692" s="4"/>
-      <c r="B692" s="2"/>
-      <c r="C692" s="5"/>
-    </row>
-    <row r="693" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A693" s="4"/>
-      <c r="B693" s="2"/>
-      <c r="C693" s="5"/>
-    </row>
-    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A694" s="4"/>
-      <c r="B694" s="2"/>
-      <c r="C694" s="5"/>
-    </row>
-    <row r="695" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A695" s="4"/>
-      <c r="B695" s="2"/>
-      <c r="C695" s="5"/>
-    </row>
-    <row r="696" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A696" s="4"/>
-      <c r="B696" s="2"/>
-      <c r="C696" s="5"/>
-    </row>
-    <row r="697" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A697" s="4"/>
-      <c r="B697" s="2"/>
-      <c r="C697" s="5"/>
-    </row>
-    <row r="698" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A698" s="4"/>
-      <c r="B698" s="2"/>
-      <c r="C698" s="5"/>
-    </row>
-    <row r="699" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A699" s="4"/>
-      <c r="B699" s="2"/>
-      <c r="C699" s="5"/>
-    </row>
-    <row r="700" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A700" s="4"/>
-      <c r="B700" s="2"/>
-      <c r="C700" s="5"/>
-    </row>
-    <row r="701" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A701" s="4"/>
-      <c r="B701" s="2"/>
-      <c r="C701" s="5"/>
-    </row>
-    <row r="702" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A702" s="4"/>
-      <c r="B702" s="2"/>
-      <c r="C702" s="5"/>
-    </row>
-    <row r="703" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A703" s="4"/>
-      <c r="B703" s="2"/>
-      <c r="C703" s="5"/>
-    </row>
-    <row r="704" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A704" s="4"/>
-      <c r="B704" s="2"/>
-      <c r="C704" s="5"/>
-    </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A705" s="4"/>
-      <c r="B705" s="2"/>
-      <c r="C705" s="5"/>
-    </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A706" s="4"/>
-      <c r="B706" s="2"/>
-      <c r="C706" s="5"/>
-    </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A707" s="4"/>
-      <c r="B707" s="2"/>
-      <c r="C707" s="5"/>
-    </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A708" s="4"/>
-      <c r="B708" s="2"/>
-      <c r="C708" s="5"/>
-    </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A709" s="4"/>
-      <c r="B709" s="2"/>
-      <c r="C709" s="5"/>
-    </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A710" s="4"/>
-      <c r="B710" s="2"/>
-      <c r="C710" s="5"/>
-    </row>
-    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A711" s="4"/>
-      <c r="B711" s="2"/>
-      <c r="C711" s="5"/>
-    </row>
-    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A712" s="4"/>
-      <c r="B712" s="2"/>
-      <c r="C712" s="5"/>
-    </row>
-    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A713" s="4"/>
-      <c r="B713" s="2"/>
-      <c r="C713" s="5"/>
-    </row>
-    <row r="714" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A714" s="4"/>
-      <c r="B714" s="2"/>
-      <c r="C714" s="5"/>
-    </row>
-    <row r="715" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A715" s="4"/>
-      <c r="B715" s="2"/>
-      <c r="C715" s="5"/>
-    </row>
-    <row r="716" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A716" s="4"/>
-      <c r="B716" s="2"/>
-      <c r="C716" s="5"/>
-    </row>
-    <row r="717" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A717" s="4"/>
-      <c r="B717" s="2"/>
-      <c r="C717" s="5"/>
-    </row>
-    <row r="718" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A718" s="4"/>
-      <c r="B718" s="2"/>
-      <c r="C718" s="5"/>
-    </row>
-    <row r="719" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A719" s="4"/>
-      <c r="B719" s="2"/>
-      <c r="C719" s="5"/>
-    </row>
-    <row r="720" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A720" s="4"/>
-      <c r="B720" s="2"/>
-      <c r="C720" s="5"/>
-    </row>
-    <row r="721" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A721" s="4"/>
-      <c r="B721" s="2"/>
-      <c r="C721" s="5"/>
-    </row>
-    <row r="722" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A722" s="4"/>
-      <c r="B722" s="2"/>
-      <c r="C722" s="5"/>
-    </row>
-    <row r="723" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A723" s="4"/>
-      <c r="B723" s="2"/>
-      <c r="C723" s="5"/>
-    </row>
-    <row r="724" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A724" s="4"/>
-      <c r="B724" s="2"/>
-      <c r="C724" s="5"/>
-    </row>
-    <row r="725" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A725" s="4"/>
-      <c r="B725" s="2"/>
-      <c r="C725" s="5"/>
-    </row>
-    <row r="726" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A726" s="4"/>
-      <c r="B726" s="2"/>
-      <c r="C726" s="5"/>
-    </row>
-    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A727" s="4"/>
-      <c r="B727" s="2"/>
-      <c r="C727" s="5"/>
-    </row>
-    <row r="728" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A728" s="4"/>
-      <c r="B728" s="2"/>
-      <c r="C728" s="5"/>
-    </row>
-    <row r="729" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A729" s="4"/>
-      <c r="B729" s="2"/>
-      <c r="C729" s="5"/>
-    </row>
-    <row r="730" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A730" s="4"/>
-      <c r="B730" s="2"/>
-      <c r="C730" s="5"/>
-    </row>
-    <row r="731" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A731" s="4"/>
-      <c r="B731" s="2"/>
-      <c r="C731" s="5"/>
-    </row>
-    <row r="732" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A732" s="4"/>
-      <c r="B732" s="2"/>
-      <c r="C732" s="5"/>
-    </row>
-    <row r="733" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A733" s="4"/>
-      <c r="B733" s="2"/>
-      <c r="C733" s="5"/>
-    </row>
-    <row r="734" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A734" s="4"/>
-      <c r="B734" s="2"/>
-      <c r="C734" s="5"/>
-    </row>
-    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A735" s="4"/>
-      <c r="B735" s="2"/>
-      <c r="C735" s="5"/>
-    </row>
-    <row r="736" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A736" s="4"/>
-      <c r="B736" s="2"/>
-      <c r="C736" s="5"/>
-    </row>
-    <row r="737" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A737" s="4"/>
-      <c r="B737" s="2"/>
-      <c r="C737" s="5"/>
-    </row>
-    <row r="738" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A738" s="4"/>
-      <c r="B738" s="2"/>
-      <c r="C738" s="5"/>
-    </row>
-    <row r="739" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A739" s="4"/>
-      <c r="B739" s="2"/>
-      <c r="C739" s="5"/>
-    </row>
-    <row r="740" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A740" s="4"/>
-      <c r="B740" s="2"/>
-      <c r="C740" s="5"/>
-    </row>
-    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A741" s="4"/>
-      <c r="B741" s="2"/>
-      <c r="C741" s="5"/>
-    </row>
-    <row r="742" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A742" s="4"/>
-      <c r="B742" s="2"/>
-      <c r="C742" s="5"/>
-    </row>
-    <row r="743" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A743" s="4"/>
-      <c r="B743" s="2"/>
-      <c r="C743" s="5"/>
-    </row>
-    <row r="744" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A744" s="4"/>
-      <c r="B744" s="2"/>
-      <c r="C744" s="5"/>
-    </row>
-    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A745" s="4"/>
-      <c r="B745" s="2"/>
-      <c r="C745" s="5"/>
-    </row>
-    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A746" s="4"/>
-      <c r="B746" s="2"/>
-      <c r="C746" s="5"/>
-    </row>
-    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A747" s="4"/>
-      <c r="B747" s="2"/>
-      <c r="C747" s="5"/>
-    </row>
-    <row r="748" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A748" s="4"/>
-      <c r="B748" s="2"/>
-      <c r="C748" s="5"/>
-    </row>
-    <row r="749" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A749" s="4"/>
-      <c r="B749" s="2"/>
-      <c r="C749" s="5"/>
-    </row>
-    <row r="750" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A750" s="4"/>
-      <c r="B750" s="2"/>
-      <c r="C750" s="5"/>
-    </row>
-    <row r="751" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A751" s="4"/>
-      <c r="B751" s="2"/>
-      <c r="C751" s="5"/>
-    </row>
-    <row r="752" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A752" s="4"/>
-      <c r="B752" s="2"/>
-      <c r="C752" s="5"/>
-    </row>
-    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A753" s="4"/>
-      <c r="B753" s="2"/>
-      <c r="C753" s="5"/>
-    </row>
-    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A754" s="4"/>
-      <c r="B754" s="2"/>
-      <c r="C754" s="5"/>
-    </row>
-    <row r="755" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A755" s="4"/>
-      <c r="B755" s="2"/>
-      <c r="C755" s="5"/>
-    </row>
-    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A756" s="4"/>
-      <c r="B756" s="2"/>
-      <c r="C756" s="5"/>
-    </row>
-    <row r="757" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A757" s="4"/>
-      <c r="B757" s="2"/>
-      <c r="C757" s="5"/>
-    </row>
-    <row r="758" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A758" s="4"/>
-      <c r="B758" s="2"/>
-      <c r="C758" s="5"/>
-    </row>
-    <row r="759" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A759" s="4"/>
-      <c r="B759" s="2"/>
-      <c r="C759" s="5"/>
-    </row>
-    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A760" s="4"/>
-      <c r="B760" s="2"/>
-      <c r="C760" s="5"/>
-    </row>
-    <row r="761" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A761" s="4"/>
-      <c r="B761" s="2"/>
-      <c r="C761" s="5"/>
-    </row>
-    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A762" s="4"/>
-      <c r="B762" s="2"/>
-      <c r="C762" s="5"/>
-    </row>
-    <row r="763" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A763" s="4"/>
-      <c r="B763" s="2"/>
-      <c r="C763" s="5"/>
-    </row>
-    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A764" s="4"/>
-      <c r="B764" s="2"/>
-      <c r="C764" s="5"/>
-    </row>
-    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A765" s="4"/>
-      <c r="B765" s="2"/>
-      <c r="C765" s="5"/>
-    </row>
-    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A766" s="4"/>
-      <c r="B766" s="2"/>
-      <c r="C766" s="5"/>
-    </row>
-    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A767" s="4"/>
-      <c r="B767" s="2"/>
-      <c r="C767" s="5"/>
-    </row>
-    <row r="768" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A768" s="4"/>
-      <c r="B768" s="2"/>
-      <c r="C768" s="5"/>
-    </row>
-    <row r="769" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A769" s="4"/>
-      <c r="B769" s="2"/>
-      <c r="C769" s="5"/>
-    </row>
-    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A770" s="4"/>
-      <c r="B770" s="2"/>
-      <c r="C770" s="5"/>
-    </row>
-    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A771" s="4"/>
-      <c r="B771" s="2"/>
-      <c r="C771" s="5"/>
-    </row>
-    <row r="772" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A772" s="4"/>
-      <c r="B772" s="2"/>
-      <c r="C772" s="5"/>
-    </row>
-    <row r="773" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A773" s="4"/>
-      <c r="B773" s="2"/>
-      <c r="C773" s="5"/>
-    </row>
-    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A774" s="4"/>
-      <c r="B774" s="2"/>
-      <c r="C774" s="5"/>
-    </row>
-    <row r="775" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A775" s="4"/>
-      <c r="B775" s="2"/>
-      <c r="C775" s="5"/>
-    </row>
-    <row r="776" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A776" s="4"/>
-      <c r="B776" s="2"/>
-      <c r="C776" s="5"/>
-    </row>
-    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A777" s="4"/>
-      <c r="B777" s="2"/>
-      <c r="C777" s="5"/>
-    </row>
-    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A778" s="4"/>
-      <c r="B778" s="2"/>
-      <c r="C778" s="5"/>
-    </row>
-    <row r="779" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A779" s="4"/>
-      <c r="B779" s="2"/>
-      <c r="C779" s="5"/>
-    </row>
-    <row r="780" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A780" s="4"/>
-      <c r="B780" s="2"/>
-      <c r="C780" s="5"/>
-    </row>
-    <row r="781" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A781" s="4"/>
-      <c r="B781" s="2"/>
-      <c r="C781" s="5"/>
-    </row>
-    <row r="782" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A782" s="4"/>
-      <c r="B782" s="2"/>
-      <c r="C782" s="5"/>
-    </row>
-    <row r="783" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A783" s="4"/>
-      <c r="B783" s="2"/>
-      <c r="C783" s="5"/>
-    </row>
-    <row r="784" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A784" s="4"/>
-      <c r="B784" s="2"/>
-      <c r="C784" s="5"/>
-    </row>
-    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A785" s="4"/>
-      <c r="B785" s="2"/>
-      <c r="C785" s="5"/>
-    </row>
-    <row r="786" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A786" s="4"/>
-      <c r="B786" s="2"/>
-      <c r="C786" s="5"/>
-    </row>
-    <row r="787" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A787" s="4"/>
-      <c r="B787" s="2"/>
-      <c r="C787" s="5"/>
-    </row>
-    <row r="788" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A788" s="4"/>
-      <c r="B788" s="2"/>
-      <c r="C788" s="5"/>
-    </row>
-    <row r="789" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A789" s="4"/>
-      <c r="B789" s="2"/>
-      <c r="C789" s="5"/>
-    </row>
-    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A790" s="4"/>
-      <c r="B790" s="2"/>
-      <c r="C790" s="5"/>
-    </row>
-    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A791" s="4"/>
-      <c r="B791" s="2"/>
-      <c r="C791" s="5"/>
-    </row>
-    <row r="792" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A792" s="4"/>
-      <c r="B792" s="2"/>
-      <c r="C792" s="5"/>
-    </row>
-    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A793" s="4"/>
-      <c r="B793" s="2"/>
-      <c r="C793" s="5"/>
-    </row>
-    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A794" s="4"/>
-      <c r="B794" s="2"/>
-      <c r="C794" s="5"/>
-    </row>
-    <row r="795" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A795" s="4"/>
-      <c r="B795" s="2"/>
-      <c r="C795" s="5"/>
-    </row>
-    <row r="796" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A796" s="4"/>
-      <c r="B796" s="2"/>
-      <c r="C796" s="5"/>
-    </row>
-    <row r="797" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A797" s="4"/>
-      <c r="B797" s="2"/>
-      <c r="C797" s="5"/>
-    </row>
-    <row r="798" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A798" s="4"/>
-      <c r="B798" s="2"/>
-      <c r="C798" s="5"/>
-    </row>
-    <row r="799" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A799" s="4"/>
-      <c r="B799" s="2"/>
-      <c r="C799" s="5"/>
-    </row>
-    <row r="800" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A640" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B640" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C640" s="5">
+        <v>26</v>
+      </c>
+      <c r="D640" t="s">
+        <v>176</v>
+      </c>
+      <c r="E640" t="s">
+        <v>165</v>
+      </c>
+      <c r="F640" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A641" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B641" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C641" s="5">
+        <v>13</v>
+      </c>
+      <c r="D641" t="s">
+        <v>176</v>
+      </c>
+      <c r="E641" t="s">
+        <v>165</v>
+      </c>
+      <c r="F641" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A642" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B642" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C642" s="5">
+        <v>4</v>
+      </c>
+      <c r="D642" t="s">
+        <v>176</v>
+      </c>
+      <c r="E642" t="s">
+        <v>165</v>
+      </c>
+      <c r="F642" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A643" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B643" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C643" s="5">
+        <v>6</v>
+      </c>
+      <c r="D643" t="s">
+        <v>166</v>
+      </c>
+      <c r="E643" t="s">
+        <v>165</v>
+      </c>
+      <c r="F643" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A644" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B644" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C644" s="5">
+        <v>0</v>
+      </c>
+      <c r="D644" t="s">
+        <v>176</v>
+      </c>
+      <c r="E644" t="s">
+        <v>165</v>
+      </c>
+      <c r="F644" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A645" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B645" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C645" s="5">
+        <v>121</v>
+      </c>
+      <c r="D645" t="s">
+        <v>167</v>
+      </c>
+      <c r="E645" t="s">
+        <v>165</v>
+      </c>
+      <c r="F645" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A646" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B646" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C646" s="5">
+        <v>16</v>
+      </c>
+      <c r="D646" t="s">
+        <v>168</v>
+      </c>
+      <c r="E646" t="s">
+        <v>169</v>
+      </c>
+      <c r="F646" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A647" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B647" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C647" s="5">
+        <v>4</v>
+      </c>
+      <c r="D647" t="s">
+        <v>168</v>
+      </c>
+      <c r="E647" t="s">
+        <v>169</v>
+      </c>
+      <c r="F647" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A648" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B648" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C648" s="5">
+        <v>0</v>
+      </c>
+      <c r="D648" t="s">
+        <v>170</v>
+      </c>
+      <c r="E648" t="s">
+        <v>165</v>
+      </c>
+      <c r="F648" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A649" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B649" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C649" s="5">
+        <v>2</v>
+      </c>
+      <c r="D649" t="s">
+        <v>168</v>
+      </c>
+      <c r="E649" t="s">
+        <v>169</v>
+      </c>
+      <c r="F649" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="650" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A650" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B650" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C650" s="5">
+        <v>1</v>
+      </c>
+      <c r="D650" t="s">
+        <v>168</v>
+      </c>
+      <c r="E650" t="s">
+        <v>171</v>
+      </c>
+      <c r="F650" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="651" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A651" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C651" s="5">
+        <v>13</v>
+      </c>
+      <c r="D651" t="s">
+        <v>168</v>
+      </c>
+      <c r="E651" t="s">
+        <v>172</v>
+      </c>
+      <c r="F651" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="652" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A652" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C652" s="5">
+        <v>95</v>
+      </c>
+      <c r="D652" t="s">
+        <v>167</v>
+      </c>
+      <c r="E652" t="s">
+        <v>165</v>
+      </c>
+      <c r="F652" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="653" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A653" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B653" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C653" s="5">
+        <v>2</v>
+      </c>
+      <c r="D653" t="s">
+        <v>170</v>
+      </c>
+      <c r="E653" t="s">
+        <v>165</v>
+      </c>
+      <c r="F653" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="654" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A654" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B654" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C654" s="5">
+        <v>2</v>
+      </c>
+      <c r="D654" t="s">
+        <v>176</v>
+      </c>
+      <c r="E654" t="s">
+        <v>165</v>
+      </c>
+      <c r="F654" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A655" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C655" s="5">
+        <v>1</v>
+      </c>
+      <c r="D655" t="s">
+        <v>176</v>
+      </c>
+      <c r="E655" t="s">
+        <v>165</v>
+      </c>
+      <c r="F655" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="656" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A656" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C656" s="5">
+        <v>11</v>
+      </c>
+      <c r="D656" t="s">
+        <v>166</v>
+      </c>
+      <c r="E656" t="s">
+        <v>165</v>
+      </c>
+      <c r="F656" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="657" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A657" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C657" s="5">
+        <v>68</v>
+      </c>
+      <c r="D657" t="s">
+        <v>167</v>
+      </c>
+      <c r="E657" t="s">
+        <v>165</v>
+      </c>
+      <c r="F657" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="658" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A658" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C658" s="5">
+        <v>23</v>
+      </c>
+      <c r="D658" t="s">
+        <v>176</v>
+      </c>
+      <c r="E658" t="s">
+        <v>165</v>
+      </c>
+      <c r="F658" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="659" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A659" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C659" s="5">
+        <v>5</v>
+      </c>
+      <c r="D659" t="s">
+        <v>168</v>
+      </c>
+      <c r="E659" t="s">
+        <v>169</v>
+      </c>
+      <c r="F659" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="660" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A660" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C660" s="5">
+        <v>4</v>
+      </c>
+      <c r="D660" t="s">
+        <v>176</v>
+      </c>
+      <c r="E660" t="s">
+        <v>165</v>
+      </c>
+      <c r="F660" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="661" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A661" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C661" s="5">
+        <v>97</v>
+      </c>
+      <c r="D661" t="s">
+        <v>167</v>
+      </c>
+      <c r="E661" t="s">
+        <v>165</v>
+      </c>
+      <c r="F661" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="662" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A662" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C662" s="5">
+        <v>61</v>
+      </c>
+      <c r="D662" t="s">
+        <v>166</v>
+      </c>
+      <c r="E662" t="s">
+        <v>165</v>
+      </c>
+      <c r="F662" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="663" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A663" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C663" s="5">
+        <v>32</v>
+      </c>
+      <c r="D663" t="s">
+        <v>167</v>
+      </c>
+      <c r="E663" t="s">
+        <v>165</v>
+      </c>
+      <c r="F663" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="664" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A664" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C664" s="5">
+        <v>34</v>
+      </c>
+      <c r="D664" t="s">
+        <v>168</v>
+      </c>
+      <c r="E664" t="s">
+        <v>171</v>
+      </c>
+      <c r="F664" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="665" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A665" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C665" s="5">
+        <v>3</v>
+      </c>
+      <c r="D665" t="s">
+        <v>167</v>
+      </c>
+      <c r="E665" t="s">
+        <v>165</v>
+      </c>
+      <c r="F665" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="666" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A666" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C666" s="5">
+        <v>1</v>
+      </c>
+      <c r="D666" t="s">
+        <v>168</v>
+      </c>
+      <c r="E666" t="s">
+        <v>169</v>
+      </c>
+      <c r="F666" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="667" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A667" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C667" s="5">
+        <v>58</v>
+      </c>
+      <c r="D667" t="s">
+        <v>173</v>
+      </c>
+      <c r="E667" t="s">
+        <v>165</v>
+      </c>
+      <c r="F667" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="668" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A668" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C668" s="5">
+        <v>43</v>
+      </c>
+      <c r="D668" t="s">
+        <v>166</v>
+      </c>
+      <c r="E668" t="s">
+        <v>165</v>
+      </c>
+      <c r="F668" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="669" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A669" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C669" s="5">
+        <v>105</v>
+      </c>
+      <c r="D669" t="s">
+        <v>167</v>
+      </c>
+      <c r="E669" t="s">
+        <v>165</v>
+      </c>
+      <c r="F669" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="670" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A670" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C670" s="5">
+        <v>5</v>
+      </c>
+      <c r="D670" t="s">
+        <v>168</v>
+      </c>
+      <c r="E670" t="s">
+        <v>169</v>
+      </c>
+      <c r="F670" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="671" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A671" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C671" s="5">
+        <v>451</v>
+      </c>
+      <c r="D671" t="s">
+        <v>176</v>
+      </c>
+      <c r="E671" t="s">
+        <v>165</v>
+      </c>
+      <c r="F671" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="672" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A672" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C672" s="5">
+        <v>1</v>
+      </c>
+      <c r="D672" t="s">
+        <v>168</v>
+      </c>
+      <c r="E672" t="s">
+        <v>169</v>
+      </c>
+      <c r="F672" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="673" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A673" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C673" s="5">
+        <v>46</v>
+      </c>
+      <c r="D673" t="s">
+        <v>176</v>
+      </c>
+      <c r="E673" t="s">
+        <v>165</v>
+      </c>
+      <c r="F673" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="674" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A674" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C674" s="5">
+        <v>53</v>
+      </c>
+      <c r="D674" t="s">
+        <v>176</v>
+      </c>
+      <c r="E674" t="s">
+        <v>165</v>
+      </c>
+      <c r="F674" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A675" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C675" s="5">
+        <v>2</v>
+      </c>
+      <c r="D675" t="s">
+        <v>176</v>
+      </c>
+      <c r="E675" t="s">
+        <v>165</v>
+      </c>
+      <c r="F675" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="676" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A676" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C676" s="5">
+        <v>10</v>
+      </c>
+      <c r="D676" t="s">
+        <v>170</v>
+      </c>
+      <c r="E676" t="s">
+        <v>165</v>
+      </c>
+      <c r="F676" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="677" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A677" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C677" s="5">
+        <v>32</v>
+      </c>
+      <c r="D677" t="s">
+        <v>170</v>
+      </c>
+      <c r="E677" t="s">
+        <v>165</v>
+      </c>
+      <c r="F677" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="678" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A678" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C678" s="5">
+        <v>1</v>
+      </c>
+      <c r="D678" t="s">
+        <v>168</v>
+      </c>
+      <c r="E678" t="s">
+        <v>169</v>
+      </c>
+      <c r="F678" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="679" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A679" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C679" s="5">
+        <v>46</v>
+      </c>
+      <c r="D679" t="s">
+        <v>173</v>
+      </c>
+      <c r="E679" t="s">
+        <v>165</v>
+      </c>
+      <c r="F679" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="680" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A680" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C680" s="5">
+        <v>25</v>
+      </c>
+      <c r="D680" t="s">
+        <v>176</v>
+      </c>
+      <c r="E680" t="s">
+        <v>165</v>
+      </c>
+      <c r="F680" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="681" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A681" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B681" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C681" s="5">
+        <v>2</v>
+      </c>
+      <c r="D681" t="s">
+        <v>176</v>
+      </c>
+      <c r="E681" t="s">
+        <v>165</v>
+      </c>
+      <c r="F681" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="682" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A682" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B682" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C682" s="5">
+        <v>125</v>
+      </c>
+      <c r="D682" t="s">
+        <v>173</v>
+      </c>
+      <c r="E682" t="s">
+        <v>165</v>
+      </c>
+      <c r="F682" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="683" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A683" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B683" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C683" s="5">
+        <v>2</v>
+      </c>
+      <c r="D683" t="s">
+        <v>168</v>
+      </c>
+      <c r="E683" t="s">
+        <v>169</v>
+      </c>
+      <c r="F683" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="684" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A684" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B684" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C684" s="5">
+        <v>1</v>
+      </c>
+      <c r="D684" t="s">
+        <v>176</v>
+      </c>
+      <c r="E684" t="s">
+        <v>165</v>
+      </c>
+      <c r="F684" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="685" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A685" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C685" s="5">
+        <v>3</v>
+      </c>
+      <c r="D685" t="s">
+        <v>168</v>
+      </c>
+      <c r="E685" t="s">
+        <v>169</v>
+      </c>
+      <c r="F685" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="686" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A686" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C686" s="5">
+        <v>179</v>
+      </c>
+      <c r="D686" t="s">
+        <v>168</v>
+      </c>
+      <c r="E686" t="s">
+        <v>169</v>
+      </c>
+      <c r="F686" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="687" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A687" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C687" s="5">
+        <v>2</v>
+      </c>
+      <c r="D687" t="s">
+        <v>168</v>
+      </c>
+      <c r="E687" t="s">
+        <v>169</v>
+      </c>
+      <c r="F687" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="688" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A688" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C688" s="5">
+        <v>3</v>
+      </c>
+      <c r="D688" t="s">
+        <v>168</v>
+      </c>
+      <c r="E688" t="s">
+        <v>169</v>
+      </c>
+      <c r="F688" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="689" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A689" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B689" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C689" s="5">
+        <v>6</v>
+      </c>
+      <c r="D689" t="s">
+        <v>167</v>
+      </c>
+      <c r="E689" t="s">
+        <v>165</v>
+      </c>
+      <c r="F689" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A690" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B690" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C690" s="5">
+        <v>65</v>
+      </c>
+      <c r="D690" t="s">
+        <v>167</v>
+      </c>
+      <c r="E690" t="s">
+        <v>165</v>
+      </c>
+      <c r="F690" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A691" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C691" s="5">
+        <v>6</v>
+      </c>
+      <c r="D691" t="s">
+        <v>176</v>
+      </c>
+      <c r="E691" t="s">
+        <v>165</v>
+      </c>
+      <c r="F691" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A692" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C692" s="5">
+        <v>70</v>
+      </c>
+      <c r="D692" t="s">
+        <v>170</v>
+      </c>
+      <c r="E692" t="s">
+        <v>165</v>
+      </c>
+      <c r="F692" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A693" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C693" s="5">
+        <v>2</v>
+      </c>
+      <c r="D693" t="s">
+        <v>176</v>
+      </c>
+      <c r="E693" t="s">
+        <v>165</v>
+      </c>
+      <c r="F693" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A694" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C694" s="5">
+        <v>5</v>
+      </c>
+      <c r="D694" t="s">
+        <v>167</v>
+      </c>
+      <c r="E694" t="s">
+        <v>165</v>
+      </c>
+      <c r="F694" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A695" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C695" s="5">
+        <v>13</v>
+      </c>
+      <c r="D695" t="s">
+        <v>168</v>
+      </c>
+      <c r="E695" t="s">
+        <v>169</v>
+      </c>
+      <c r="F695" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A696" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C696" s="5">
+        <v>22</v>
+      </c>
+      <c r="D696" t="s">
+        <v>168</v>
+      </c>
+      <c r="E696" t="s">
+        <v>169</v>
+      </c>
+      <c r="F696" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A697" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C697" s="5">
+        <v>7</v>
+      </c>
+      <c r="D697" t="s">
+        <v>173</v>
+      </c>
+      <c r="E697" t="s">
+        <v>165</v>
+      </c>
+      <c r="F697" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A698" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C698" s="5">
+        <v>295</v>
+      </c>
+      <c r="D698" t="s">
+        <v>167</v>
+      </c>
+      <c r="E698" t="s">
+        <v>165</v>
+      </c>
+      <c r="F698" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A699" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C699" s="5">
+        <v>314</v>
+      </c>
+      <c r="D699" t="s">
+        <v>166</v>
+      </c>
+      <c r="E699" t="s">
+        <v>165</v>
+      </c>
+      <c r="F699" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A700" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C700" s="5">
+        <v>28</v>
+      </c>
+      <c r="D700" t="s">
+        <v>176</v>
+      </c>
+      <c r="E700" t="s">
+        <v>165</v>
+      </c>
+      <c r="F700" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A701" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C701" s="5">
+        <v>8</v>
+      </c>
+      <c r="D701" t="s">
+        <v>168</v>
+      </c>
+      <c r="E701" t="s">
+        <v>174</v>
+      </c>
+      <c r="F701" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A702" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C702" s="5">
+        <v>9</v>
+      </c>
+      <c r="D702" t="s">
+        <v>170</v>
+      </c>
+      <c r="E702" t="s">
+        <v>165</v>
+      </c>
+      <c r="F702" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="703" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A703" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C703" s="5">
+        <v>3</v>
+      </c>
+      <c r="D703" t="s">
+        <v>176</v>
+      </c>
+      <c r="E703" t="s">
+        <v>165</v>
+      </c>
+      <c r="F703" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="704" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A704" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C704" s="5">
+        <v>2</v>
+      </c>
+      <c r="D704" t="s">
+        <v>168</v>
+      </c>
+      <c r="E704" t="s">
+        <v>169</v>
+      </c>
+      <c r="F704" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="705" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A705" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C705" s="5">
+        <v>1</v>
+      </c>
+      <c r="D705" t="s">
+        <v>176</v>
+      </c>
+      <c r="E705" t="s">
+        <v>165</v>
+      </c>
+      <c r="F705" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="706" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A706" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C706" s="5">
+        <v>11</v>
+      </c>
+      <c r="D706" t="s">
+        <v>176</v>
+      </c>
+      <c r="E706" t="s">
+        <v>165</v>
+      </c>
+      <c r="F706" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="707" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A707" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C707" s="5">
+        <v>19</v>
+      </c>
+      <c r="D707" t="s">
+        <v>176</v>
+      </c>
+      <c r="E707" t="s">
+        <v>165</v>
+      </c>
+      <c r="F707" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="708" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A708" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C708" s="5">
+        <v>46</v>
+      </c>
+      <c r="D708" t="s">
+        <v>166</v>
+      </c>
+      <c r="E708" t="s">
+        <v>165</v>
+      </c>
+      <c r="F708" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="709" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A709" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C709" s="5">
+        <v>1</v>
+      </c>
+      <c r="D709" t="s">
+        <v>176</v>
+      </c>
+      <c r="E709" t="s">
+        <v>165</v>
+      </c>
+      <c r="F709" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="710" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A710" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C710" s="5">
+        <v>47</v>
+      </c>
+      <c r="D710" t="s">
+        <v>170</v>
+      </c>
+      <c r="E710" t="s">
+        <v>165</v>
+      </c>
+      <c r="F710" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="711" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A711" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C711" s="5">
+        <v>86</v>
+      </c>
+      <c r="D711" t="s">
+        <v>166</v>
+      </c>
+      <c r="E711" t="s">
+        <v>165</v>
+      </c>
+      <c r="F711" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="712" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A712" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C712" s="5">
+        <v>1</v>
+      </c>
+      <c r="D712" t="s">
+        <v>168</v>
+      </c>
+      <c r="E712" t="s">
+        <v>169</v>
+      </c>
+      <c r="F712" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="713" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A713" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C713" s="5">
+        <v>7</v>
+      </c>
+      <c r="D713" t="s">
+        <v>168</v>
+      </c>
+      <c r="E713" t="s">
+        <v>169</v>
+      </c>
+      <c r="F713" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="714" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A714" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C714" s="5">
+        <v>47</v>
+      </c>
+      <c r="D714" t="s">
+        <v>176</v>
+      </c>
+      <c r="E714" t="s">
+        <v>165</v>
+      </c>
+      <c r="F714" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="715" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A715" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C715" s="5">
+        <v>0</v>
+      </c>
+      <c r="D715" t="s">
+        <v>176</v>
+      </c>
+      <c r="E715" t="s">
+        <v>165</v>
+      </c>
+      <c r="F715" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="716" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A716" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C716" s="5">
+        <v>167</v>
+      </c>
+      <c r="D716" t="s">
+        <v>170</v>
+      </c>
+      <c r="E716" t="s">
+        <v>165</v>
+      </c>
+      <c r="F716" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="717" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A717" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C717" s="5">
+        <v>30</v>
+      </c>
+      <c r="D717" t="s">
+        <v>168</v>
+      </c>
+      <c r="E717" t="s">
+        <v>174</v>
+      </c>
+      <c r="F717" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="718" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A718" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C718" s="5">
+        <v>2</v>
+      </c>
+      <c r="D718" t="s">
+        <v>176</v>
+      </c>
+      <c r="E718" t="s">
+        <v>165</v>
+      </c>
+      <c r="F718" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A719" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C719" s="5">
+        <v>55</v>
+      </c>
+      <c r="D719" t="s">
+        <v>167</v>
+      </c>
+      <c r="E719" t="s">
+        <v>165</v>
+      </c>
+      <c r="F719" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="720" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A720" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C720" s="5">
+        <v>74</v>
+      </c>
+      <c r="D720" t="s">
+        <v>176</v>
+      </c>
+      <c r="E720" t="s">
+        <v>165</v>
+      </c>
+      <c r="F720" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="721" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A721" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C721" s="5">
+        <v>8</v>
+      </c>
+      <c r="D721" t="s">
+        <v>168</v>
+      </c>
+      <c r="E721" t="s">
+        <v>169</v>
+      </c>
+      <c r="F721" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A722" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C722" s="5">
+        <v>2</v>
+      </c>
+      <c r="D722" t="s">
+        <v>173</v>
+      </c>
+      <c r="E722" t="s">
+        <v>165</v>
+      </c>
+      <c r="F722" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="723" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A723" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C723" s="5">
+        <v>4</v>
+      </c>
+      <c r="D723" t="s">
+        <v>176</v>
+      </c>
+      <c r="E723" t="s">
+        <v>165</v>
+      </c>
+      <c r="F723" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="724" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A724" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C724" s="5">
+        <v>12</v>
+      </c>
+      <c r="D724" t="s">
+        <v>173</v>
+      </c>
+      <c r="E724" t="s">
+        <v>165</v>
+      </c>
+      <c r="F724" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="725" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A725" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B725" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C725" s="5">
+        <v>3</v>
+      </c>
+      <c r="D725" t="s">
+        <v>168</v>
+      </c>
+      <c r="E725" t="s">
+        <v>169</v>
+      </c>
+      <c r="F725" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="726" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A726" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B726" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C726" s="5">
+        <v>9</v>
+      </c>
+      <c r="D726" t="s">
+        <v>173</v>
+      </c>
+      <c r="E726" t="s">
+        <v>165</v>
+      </c>
+      <c r="F726" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="727" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A727" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B727" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C727" s="5">
+        <v>9</v>
+      </c>
+      <c r="D727" t="s">
+        <v>176</v>
+      </c>
+      <c r="E727" t="s">
+        <v>165</v>
+      </c>
+      <c r="F727" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="728" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A728" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B728" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C728" s="5">
+        <v>0</v>
+      </c>
+      <c r="D728" t="s">
+        <v>176</v>
+      </c>
+      <c r="E728" t="s">
+        <v>165</v>
+      </c>
+      <c r="F728" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="729" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A729" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B729" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C729" s="5">
+        <v>11</v>
+      </c>
+      <c r="D729" t="s">
+        <v>170</v>
+      </c>
+      <c r="E729" t="s">
+        <v>165</v>
+      </c>
+      <c r="F729" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="730" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A730" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B730" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C730" s="5">
+        <v>14</v>
+      </c>
+      <c r="D730" t="s">
+        <v>173</v>
+      </c>
+      <c r="E730" t="s">
+        <v>165</v>
+      </c>
+      <c r="F730" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="731" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A731" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C731" s="5">
+        <v>22</v>
+      </c>
+      <c r="D731" t="s">
+        <v>168</v>
+      </c>
+      <c r="E731" t="s">
+        <v>171</v>
+      </c>
+      <c r="F731" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="732" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A732" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B732" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C732" s="5">
+        <v>8</v>
+      </c>
+      <c r="D732" t="s">
+        <v>176</v>
+      </c>
+      <c r="E732" t="s">
+        <v>165</v>
+      </c>
+      <c r="F732" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A733" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C733" s="5">
+        <v>4</v>
+      </c>
+      <c r="D733" t="s">
+        <v>176</v>
+      </c>
+      <c r="E733" t="s">
+        <v>165</v>
+      </c>
+      <c r="F733" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A734" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B734" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C734" s="5">
+        <v>9</v>
+      </c>
+      <c r="D734" t="s">
+        <v>173</v>
+      </c>
+      <c r="E734" t="s">
+        <v>165</v>
+      </c>
+      <c r="F734" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A735" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B735" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C735" s="5">
+        <v>10</v>
+      </c>
+      <c r="D735" t="s">
+        <v>167</v>
+      </c>
+      <c r="E735" t="s">
+        <v>165</v>
+      </c>
+      <c r="F735" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A736" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B736" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C736" s="5">
+        <v>5</v>
+      </c>
+      <c r="D736" t="s">
+        <v>173</v>
+      </c>
+      <c r="E736" t="s">
+        <v>165</v>
+      </c>
+      <c r="F736" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A737" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B737" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C737" s="5">
+        <v>3</v>
+      </c>
+      <c r="D737" t="s">
+        <v>176</v>
+      </c>
+      <c r="E737" t="s">
+        <v>165</v>
+      </c>
+      <c r="F737" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A738" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B738" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C738" s="5">
+        <v>1</v>
+      </c>
+      <c r="D738" t="s">
+        <v>168</v>
+      </c>
+      <c r="E738" t="s">
+        <v>169</v>
+      </c>
+      <c r="F738" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A739" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B739" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C739" s="5">
+        <v>10</v>
+      </c>
+      <c r="D739" t="s">
+        <v>170</v>
+      </c>
+      <c r="E739" t="s">
+        <v>165</v>
+      </c>
+      <c r="F739" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A740" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B740" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C740" s="5">
+        <v>51</v>
+      </c>
+      <c r="D740" t="s">
+        <v>176</v>
+      </c>
+      <c r="E740" t="s">
+        <v>165</v>
+      </c>
+      <c r="F740" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A741" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B741" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C741" s="5">
+        <v>184</v>
+      </c>
+      <c r="D741" t="s">
+        <v>168</v>
+      </c>
+      <c r="E741" t="s">
+        <v>172</v>
+      </c>
+      <c r="F741" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A742" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B742" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C742" s="5">
+        <v>2</v>
+      </c>
+      <c r="D742" t="s">
+        <v>176</v>
+      </c>
+      <c r="E742" t="s">
+        <v>165</v>
+      </c>
+      <c r="F742" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A743" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B743" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C743" s="5">
+        <v>55</v>
+      </c>
+      <c r="D743" t="s">
+        <v>176</v>
+      </c>
+      <c r="E743" t="s">
+        <v>165</v>
+      </c>
+      <c r="F743" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A744" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B744" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C744" s="5">
+        <v>2</v>
+      </c>
+      <c r="D744" t="s">
+        <v>168</v>
+      </c>
+      <c r="E744" t="s">
+        <v>169</v>
+      </c>
+      <c r="F744" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A745" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B745" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C745" s="5">
+        <v>13</v>
+      </c>
+      <c r="D745" t="s">
+        <v>173</v>
+      </c>
+      <c r="E745" t="s">
+        <v>165</v>
+      </c>
+      <c r="F745" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A746" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B746" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C746" s="5">
+        <v>3</v>
+      </c>
+      <c r="D746" t="s">
+        <v>173</v>
+      </c>
+      <c r="E746" t="s">
+        <v>165</v>
+      </c>
+      <c r="F746" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A747" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B747" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C747" s="5">
+        <v>52</v>
+      </c>
+      <c r="D747" t="s">
+        <v>176</v>
+      </c>
+      <c r="E747" t="s">
+        <v>165</v>
+      </c>
+      <c r="F747" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A748" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B748" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C748" s="5">
+        <v>18</v>
+      </c>
+      <c r="D748" t="s">
+        <v>176</v>
+      </c>
+      <c r="E748" t="s">
+        <v>165</v>
+      </c>
+      <c r="F748" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A749" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B749" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C749" s="5">
+        <v>252</v>
+      </c>
+      <c r="D749" t="s">
+        <v>166</v>
+      </c>
+      <c r="E749" t="s">
+        <v>165</v>
+      </c>
+      <c r="F749" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A750" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B750" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C750" s="5">
+        <v>0</v>
+      </c>
+      <c r="D750" t="s">
+        <v>168</v>
+      </c>
+      <c r="E750" t="s">
+        <v>169</v>
+      </c>
+      <c r="F750" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A751" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B751" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C751" s="5">
+        <v>16</v>
+      </c>
+      <c r="D751" t="s">
+        <v>176</v>
+      </c>
+      <c r="E751" t="s">
+        <v>165</v>
+      </c>
+      <c r="F751" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A752" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B752" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C752" s="5">
+        <v>12</v>
+      </c>
+      <c r="D752" t="s">
+        <v>166</v>
+      </c>
+      <c r="E752" t="s">
+        <v>165</v>
+      </c>
+      <c r="F752" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A753" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C753" s="5">
+        <v>3</v>
+      </c>
+      <c r="D753" t="s">
+        <v>168</v>
+      </c>
+      <c r="E753" t="s">
+        <v>169</v>
+      </c>
+      <c r="F753" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A754" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B754" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C754" s="5">
+        <v>18</v>
+      </c>
+      <c r="D754" t="s">
+        <v>166</v>
+      </c>
+      <c r="E754" t="s">
+        <v>165</v>
+      </c>
+      <c r="F754" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A755" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B755" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C755" s="5">
+        <v>4</v>
+      </c>
+      <c r="D755" t="s">
+        <v>166</v>
+      </c>
+      <c r="E755" t="s">
+        <v>165</v>
+      </c>
+      <c r="F755" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A756" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B756" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C756" s="5">
+        <v>7</v>
+      </c>
+      <c r="D756" t="s">
+        <v>176</v>
+      </c>
+      <c r="E756" t="s">
+        <v>165</v>
+      </c>
+      <c r="F756" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A757" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B757" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C757" s="5">
+        <v>6</v>
+      </c>
+      <c r="D757" t="s">
+        <v>176</v>
+      </c>
+      <c r="E757" t="s">
+        <v>165</v>
+      </c>
+      <c r="F757" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A758" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B758" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C758" s="5">
+        <v>5</v>
+      </c>
+      <c r="D758" t="s">
+        <v>168</v>
+      </c>
+      <c r="E758" t="s">
+        <v>171</v>
+      </c>
+      <c r="F758" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A759" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B759" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C759" s="5">
+        <v>11</v>
+      </c>
+      <c r="D759" t="s">
+        <v>176</v>
+      </c>
+      <c r="E759" t="s">
+        <v>165</v>
+      </c>
+      <c r="F759" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A760" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B760" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C760" s="5">
+        <v>30</v>
+      </c>
+      <c r="D760" t="s">
+        <v>168</v>
+      </c>
+      <c r="E760" t="s">
+        <v>174</v>
+      </c>
+      <c r="F760" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A761" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B761" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C761" s="5">
+        <v>23</v>
+      </c>
+      <c r="D761" t="s">
+        <v>168</v>
+      </c>
+      <c r="E761" t="s">
+        <v>171</v>
+      </c>
+      <c r="F761" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A762" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B762" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C762" s="5">
+        <v>139</v>
+      </c>
+      <c r="D762" t="s">
+        <v>167</v>
+      </c>
+      <c r="E762" t="s">
+        <v>165</v>
+      </c>
+      <c r="F762" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A763" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B763" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C763" s="5">
+        <v>137</v>
+      </c>
+      <c r="D763" t="s">
+        <v>167</v>
+      </c>
+      <c r="E763" t="s">
+        <v>165</v>
+      </c>
+      <c r="F763" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A764" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B764" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C764" s="5">
+        <v>6</v>
+      </c>
+      <c r="D764" t="s">
+        <v>176</v>
+      </c>
+      <c r="E764" t="s">
+        <v>165</v>
+      </c>
+      <c r="F764" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A765" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B765" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C765" s="5">
+        <v>17</v>
+      </c>
+      <c r="D765" t="s">
+        <v>176</v>
+      </c>
+      <c r="E765" t="s">
+        <v>165</v>
+      </c>
+      <c r="F765" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A766" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B766" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C766" s="5">
+        <v>3</v>
+      </c>
+      <c r="D766" t="s">
+        <v>168</v>
+      </c>
+      <c r="E766" t="s">
+        <v>174</v>
+      </c>
+      <c r="F766" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A767" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B767" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C767" s="5">
+        <v>1</v>
+      </c>
+      <c r="D767" t="s">
+        <v>173</v>
+      </c>
+      <c r="E767" t="s">
+        <v>165</v>
+      </c>
+      <c r="F767" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A768" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B768" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C768" s="5">
+        <v>55</v>
+      </c>
+      <c r="D768" t="s">
+        <v>170</v>
+      </c>
+      <c r="E768" t="s">
+        <v>165</v>
+      </c>
+      <c r="F768" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A769" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B769" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C769" s="5">
+        <v>16</v>
+      </c>
+      <c r="D769" t="s">
+        <v>166</v>
+      </c>
+      <c r="E769" t="s">
+        <v>165</v>
+      </c>
+      <c r="F769" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A770" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B770" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C770" s="5">
+        <v>32</v>
+      </c>
+      <c r="D770" t="s">
+        <v>166</v>
+      </c>
+      <c r="E770" t="s">
+        <v>165</v>
+      </c>
+      <c r="F770" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A771" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C771" s="5">
+        <v>3</v>
+      </c>
+      <c r="D771" t="s">
+        <v>176</v>
+      </c>
+      <c r="E771" t="s">
+        <v>165</v>
+      </c>
+      <c r="F771" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A772" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B772" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C772" s="5">
+        <v>1</v>
+      </c>
+      <c r="D772" t="s">
+        <v>173</v>
+      </c>
+      <c r="E772" t="s">
+        <v>165</v>
+      </c>
+      <c r="F772" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A773" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B773" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C773" s="5">
+        <v>20</v>
+      </c>
+      <c r="D773" t="s">
+        <v>168</v>
+      </c>
+      <c r="E773" t="s">
+        <v>171</v>
+      </c>
+      <c r="F773" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A774" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B774" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C774" s="5">
+        <v>16</v>
+      </c>
+      <c r="D774" t="s">
+        <v>176</v>
+      </c>
+      <c r="E774" t="s">
+        <v>165</v>
+      </c>
+      <c r="F774" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A775" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B775" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C775" s="5">
+        <v>24</v>
+      </c>
+      <c r="D775" t="s">
+        <v>176</v>
+      </c>
+      <c r="E775" t="s">
+        <v>165</v>
+      </c>
+      <c r="F775" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A776" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B776" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C776" s="5">
+        <v>9</v>
+      </c>
+      <c r="D776" t="s">
+        <v>176</v>
+      </c>
+      <c r="E776" t="s">
+        <v>165</v>
+      </c>
+      <c r="F776" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A777" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B777" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C777" s="5">
+        <v>5</v>
+      </c>
+      <c r="D777" t="s">
+        <v>168</v>
+      </c>
+      <c r="E777" t="s">
+        <v>169</v>
+      </c>
+      <c r="F777" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A778" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B778" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C778" s="5">
+        <v>5</v>
+      </c>
+      <c r="D778" t="s">
+        <v>168</v>
+      </c>
+      <c r="E778" t="s">
+        <v>169</v>
+      </c>
+      <c r="F778" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A779" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B779" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C779" s="5">
+        <v>49</v>
+      </c>
+      <c r="D779" t="s">
+        <v>168</v>
+      </c>
+      <c r="E779" t="s">
+        <v>172</v>
+      </c>
+      <c r="F779" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A780" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B780" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C780" s="5">
+        <v>50</v>
+      </c>
+      <c r="D780" t="s">
+        <v>166</v>
+      </c>
+      <c r="E780" t="s">
+        <v>165</v>
+      </c>
+      <c r="F780" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A781" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B781" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C781" s="5">
+        <v>2</v>
+      </c>
+      <c r="D781" t="s">
+        <v>176</v>
+      </c>
+      <c r="E781" t="s">
+        <v>165</v>
+      </c>
+      <c r="F781" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A782" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B782" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C782" s="5">
+        <v>23</v>
+      </c>
+      <c r="D782" t="s">
+        <v>173</v>
+      </c>
+      <c r="E782" t="s">
+        <v>165</v>
+      </c>
+      <c r="F782" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A783" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B783" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C783" s="5">
+        <v>106</v>
+      </c>
+      <c r="D783" t="s">
+        <v>166</v>
+      </c>
+      <c r="E783" t="s">
+        <v>165</v>
+      </c>
+      <c r="F783" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A784" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B784" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C784" s="5">
+        <v>6</v>
+      </c>
+      <c r="D784" t="s">
+        <v>176</v>
+      </c>
+      <c r="E784" t="s">
+        <v>165</v>
+      </c>
+      <c r="F784" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A785" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B785" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C785" s="5">
+        <v>60</v>
+      </c>
+      <c r="D785" t="s">
+        <v>173</v>
+      </c>
+      <c r="E785" t="s">
+        <v>165</v>
+      </c>
+      <c r="F785" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A786" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C786" s="5">
+        <v>4</v>
+      </c>
+      <c r="D786" t="s">
+        <v>168</v>
+      </c>
+      <c r="E786" t="s">
+        <v>169</v>
+      </c>
+      <c r="F786" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A787" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B787" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C787" s="5">
+        <v>4</v>
+      </c>
+      <c r="D787" t="s">
+        <v>168</v>
+      </c>
+      <c r="E787" t="s">
+        <v>171</v>
+      </c>
+      <c r="F787" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A788" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B788" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C788" s="5">
+        <v>9</v>
+      </c>
+      <c r="D788" t="s">
+        <v>173</v>
+      </c>
+      <c r="E788" t="s">
+        <v>165</v>
+      </c>
+      <c r="F788" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A789" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B789" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C789" s="5">
+        <v>6</v>
+      </c>
+      <c r="D789" t="s">
+        <v>166</v>
+      </c>
+      <c r="E789" t="s">
+        <v>165</v>
+      </c>
+      <c r="F789" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A790" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B790" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C790" s="5">
+        <v>293</v>
+      </c>
+      <c r="D790" t="s">
+        <v>173</v>
+      </c>
+      <c r="E790" t="s">
+        <v>165</v>
+      </c>
+      <c r="F790" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A791" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B791" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C791" s="5">
+        <v>114</v>
+      </c>
+      <c r="D791" t="s">
+        <v>168</v>
+      </c>
+      <c r="E791" t="s">
+        <v>174</v>
+      </c>
+      <c r="F791" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A792" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B792" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C792" s="5">
+        <v>40</v>
+      </c>
+      <c r="D792" t="s">
+        <v>167</v>
+      </c>
+      <c r="E792" t="s">
+        <v>165</v>
+      </c>
+      <c r="F792" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A793" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C793" s="5">
+        <v>5</v>
+      </c>
+      <c r="D793" t="s">
+        <v>168</v>
+      </c>
+      <c r="E793" t="s">
+        <v>169</v>
+      </c>
+      <c r="F793" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A794" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B794" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C794" s="5">
+        <v>10</v>
+      </c>
+      <c r="D794" t="s">
+        <v>166</v>
+      </c>
+      <c r="E794" t="s">
+        <v>165</v>
+      </c>
+      <c r="F794" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A795" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B795" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C795" s="5">
+        <v>0</v>
+      </c>
+      <c r="D795" t="s">
+        <v>173</v>
+      </c>
+      <c r="E795" t="s">
+        <v>165</v>
+      </c>
+      <c r="F795" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A796" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B796" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C796" s="5">
+        <v>48</v>
+      </c>
+      <c r="D796" t="s">
+        <v>176</v>
+      </c>
+      <c r="E796" t="s">
+        <v>165</v>
+      </c>
+      <c r="F796" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A797" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C797" s="5">
+        <v>3</v>
+      </c>
+      <c r="D797" t="s">
+        <v>176</v>
+      </c>
+      <c r="E797" t="s">
+        <v>165</v>
+      </c>
+      <c r="F797" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A798" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B798" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C798" s="5">
+        <v>16</v>
+      </c>
+      <c r="D798" t="s">
+        <v>176</v>
+      </c>
+      <c r="E798" t="s">
+        <v>165</v>
+      </c>
+      <c r="F798" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A799" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B799" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C799" s="5">
+        <v>1</v>
+      </c>
+      <c r="D799" t="s">
+        <v>167</v>
+      </c>
+      <c r="E799" t="s">
+        <v>165</v>
+      </c>
+      <c r="F799" s="6">
+        <v>45925</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A800" s="4"/>
       <c r="B800" s="2"/>
       <c r="C800" s="5"/>

--- a/crm_dominus/apps/dados/limite_cancelamento.xlsx
+++ b/crm_dominus/apps/dados/limite_cancelamento.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EFB2AFB-2051-444B-8358-E0B492FA079D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925EB87A-E5FE-403A-BC28-70472A577B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3198" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="178">
   <si>
     <t>cidade</t>
   </si>
@@ -17026,806 +17026,3206 @@
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A800" s="4"/>
-      <c r="B800" s="2"/>
-      <c r="C800" s="5"/>
-    </row>
-    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A801" s="4"/>
-      <c r="B801" s="2"/>
-      <c r="C801" s="5"/>
-    </row>
-    <row r="802" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A802" s="4"/>
-      <c r="B802" s="2"/>
-      <c r="C802" s="5"/>
-    </row>
-    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A803" s="4"/>
-      <c r="B803" s="2"/>
-      <c r="C803" s="5"/>
-    </row>
-    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A804" s="4"/>
-      <c r="B804" s="2"/>
-      <c r="C804" s="5"/>
-    </row>
-    <row r="805" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A805" s="4"/>
-      <c r="B805" s="2"/>
-      <c r="C805" s="5"/>
-    </row>
-    <row r="806" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A806" s="4"/>
-      <c r="B806" s="2"/>
-      <c r="C806" s="5"/>
-    </row>
-    <row r="807" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A807" s="4"/>
-      <c r="B807" s="2"/>
-      <c r="C807" s="5"/>
-    </row>
-    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A808" s="4"/>
-      <c r="B808" s="2"/>
-      <c r="C808" s="5"/>
-    </row>
-    <row r="809" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A809" s="4"/>
-      <c r="B809" s="2"/>
-      <c r="C809" s="5"/>
-    </row>
-    <row r="810" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A810" s="4"/>
-      <c r="B810" s="2"/>
-      <c r="C810" s="5"/>
-    </row>
-    <row r="811" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A811" s="4"/>
-      <c r="B811" s="2"/>
-      <c r="C811" s="5"/>
-    </row>
-    <row r="812" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A812" s="4"/>
-      <c r="B812" s="2"/>
-      <c r="C812" s="5"/>
-    </row>
-    <row r="813" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A813" s="4"/>
-      <c r="B813" s="2"/>
-      <c r="C813" s="5"/>
-    </row>
-    <row r="814" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A814" s="4"/>
-      <c r="B814" s="2"/>
-      <c r="C814" s="5"/>
-    </row>
-    <row r="815" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A815" s="4"/>
-      <c r="B815" s="2"/>
-      <c r="C815" s="5"/>
-    </row>
-    <row r="816" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A816" s="4"/>
-      <c r="B816" s="2"/>
-      <c r="C816" s="5"/>
-    </row>
-    <row r="817" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A817" s="4"/>
-      <c r="B817" s="2"/>
-      <c r="C817" s="5"/>
-    </row>
-    <row r="818" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A818" s="4"/>
-      <c r="B818" s="2"/>
-      <c r="C818" s="5"/>
-    </row>
-    <row r="819" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A819" s="4"/>
-      <c r="B819" s="2"/>
-      <c r="C819" s="5"/>
-    </row>
-    <row r="820" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A820" s="4"/>
-      <c r="B820" s="2"/>
-      <c r="C820" s="5"/>
-    </row>
-    <row r="821" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A821" s="4"/>
-      <c r="B821" s="2"/>
-      <c r="C821" s="5"/>
-    </row>
-    <row r="822" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A822" s="4"/>
-      <c r="B822" s="2"/>
-      <c r="C822" s="5"/>
-    </row>
-    <row r="823" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A823" s="4"/>
-      <c r="B823" s="2"/>
-      <c r="C823" s="5"/>
-    </row>
-    <row r="824" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A824" s="4"/>
-      <c r="B824" s="2"/>
-      <c r="C824" s="5"/>
-    </row>
-    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A825" s="4"/>
-      <c r="B825" s="2"/>
-      <c r="C825" s="5"/>
-    </row>
-    <row r="826" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A826" s="4"/>
-      <c r="B826" s="2"/>
-      <c r="C826" s="5"/>
-    </row>
-    <row r="827" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A827" s="4"/>
-      <c r="B827" s="2"/>
-      <c r="C827" s="5"/>
-    </row>
-    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A828" s="4"/>
-      <c r="B828" s="2"/>
-      <c r="C828" s="5"/>
-    </row>
-    <row r="829" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A829" s="4"/>
-      <c r="B829" s="2"/>
-      <c r="C829" s="5"/>
-    </row>
-    <row r="830" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A830" s="4"/>
-      <c r="B830" s="2"/>
-      <c r="C830" s="5"/>
-    </row>
-    <row r="831" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A831" s="4"/>
-      <c r="B831" s="2"/>
-      <c r="C831" s="5"/>
-    </row>
-    <row r="832" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A832" s="4"/>
-      <c r="B832" s="2"/>
-      <c r="C832" s="5"/>
-    </row>
-    <row r="833" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A833" s="4"/>
-      <c r="B833" s="2"/>
-      <c r="C833" s="5"/>
-    </row>
-    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A834" s="4"/>
-      <c r="B834" s="2"/>
-      <c r="C834" s="5"/>
-    </row>
-    <row r="835" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A835" s="4"/>
-      <c r="B835" s="2"/>
-      <c r="C835" s="5"/>
-    </row>
-    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A836" s="4"/>
-      <c r="B836" s="2"/>
-      <c r="C836" s="5"/>
-    </row>
-    <row r="837" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A837" s="4"/>
-      <c r="B837" s="2"/>
-      <c r="C837" s="5"/>
-    </row>
-    <row r="838" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A838" s="4"/>
-      <c r="B838" s="2"/>
-      <c r="C838" s="5"/>
-    </row>
-    <row r="839" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A839" s="4"/>
-      <c r="B839" s="2"/>
-      <c r="C839" s="5"/>
-    </row>
-    <row r="840" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A840" s="4"/>
-      <c r="B840" s="2"/>
-      <c r="C840" s="5"/>
-    </row>
-    <row r="841" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A841" s="4"/>
-      <c r="B841" s="2"/>
-      <c r="C841" s="5"/>
-    </row>
-    <row r="842" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A842" s="4"/>
-      <c r="B842" s="2"/>
-      <c r="C842" s="5"/>
-    </row>
-    <row r="843" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A843" s="4"/>
-      <c r="B843" s="2"/>
-      <c r="C843" s="5"/>
-    </row>
-    <row r="844" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A844" s="4"/>
-      <c r="B844" s="2"/>
-      <c r="C844" s="5"/>
-    </row>
-    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A845" s="4"/>
-      <c r="B845" s="2"/>
-      <c r="C845" s="5"/>
-    </row>
-    <row r="846" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A846" s="4"/>
-      <c r="B846" s="2"/>
-      <c r="C846" s="5"/>
-    </row>
-    <row r="847" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A847" s="4"/>
-      <c r="B847" s="2"/>
-      <c r="C847" s="5"/>
-    </row>
-    <row r="848" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A848" s="4"/>
-      <c r="B848" s="2"/>
-      <c r="C848" s="5"/>
-    </row>
-    <row r="849" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A849" s="4"/>
-      <c r="B849" s="2"/>
-      <c r="C849" s="5"/>
-    </row>
-    <row r="850" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A850" s="4"/>
-      <c r="B850" s="2"/>
-      <c r="C850" s="5"/>
-    </row>
-    <row r="851" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A851" s="4"/>
-      <c r="B851" s="2"/>
-      <c r="C851" s="5"/>
-    </row>
-    <row r="852" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A852" s="4"/>
-      <c r="B852" s="2"/>
-      <c r="C852" s="5"/>
-    </row>
-    <row r="853" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A853" s="4"/>
-      <c r="B853" s="2"/>
-      <c r="C853" s="5"/>
-    </row>
-    <row r="854" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A854" s="4"/>
-      <c r="B854" s="2"/>
-      <c r="C854" s="5"/>
-    </row>
-    <row r="855" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A855" s="4"/>
-      <c r="B855" s="2"/>
-      <c r="C855" s="5"/>
-    </row>
-    <row r="856" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A856" s="4"/>
-      <c r="B856" s="2"/>
-      <c r="C856" s="5"/>
-    </row>
-    <row r="857" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A857" s="4"/>
-      <c r="B857" s="2"/>
-      <c r="C857" s="5"/>
-    </row>
-    <row r="858" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A858" s="4"/>
-      <c r="B858" s="2"/>
-      <c r="C858" s="5"/>
-    </row>
-    <row r="859" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A859" s="4"/>
-      <c r="B859" s="2"/>
-      <c r="C859" s="5"/>
-    </row>
-    <row r="860" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A860" s="4"/>
-      <c r="B860" s="2"/>
-      <c r="C860" s="5"/>
-    </row>
-    <row r="861" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A861" s="4"/>
-      <c r="B861" s="2"/>
-      <c r="C861" s="5"/>
-    </row>
-    <row r="862" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A862" s="4"/>
-      <c r="B862" s="2"/>
-      <c r="C862" s="5"/>
-    </row>
-    <row r="863" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A863" s="4"/>
-      <c r="B863" s="2"/>
-      <c r="C863" s="5"/>
-    </row>
-    <row r="864" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A864" s="4"/>
-      <c r="B864" s="2"/>
-      <c r="C864" s="5"/>
-    </row>
-    <row r="865" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A865" s="4"/>
-      <c r="B865" s="2"/>
-      <c r="C865" s="5"/>
-    </row>
-    <row r="866" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A866" s="4"/>
-      <c r="B866" s="2"/>
-      <c r="C866" s="5"/>
-    </row>
-    <row r="867" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A867" s="4"/>
-      <c r="B867" s="2"/>
-      <c r="C867" s="5"/>
-    </row>
-    <row r="868" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A868" s="4"/>
-      <c r="B868" s="2"/>
-      <c r="C868" s="5"/>
-    </row>
-    <row r="869" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A869" s="4"/>
-      <c r="B869" s="2"/>
-      <c r="C869" s="5"/>
-    </row>
-    <row r="870" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A870" s="4"/>
-      <c r="B870" s="2"/>
-      <c r="C870" s="5"/>
-    </row>
-    <row r="871" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A871" s="4"/>
-      <c r="B871" s="2"/>
-      <c r="C871" s="5"/>
-    </row>
-    <row r="872" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A872" s="4"/>
-      <c r="B872" s="2"/>
-      <c r="C872" s="5"/>
-    </row>
-    <row r="873" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A873" s="4"/>
-      <c r="B873" s="2"/>
-      <c r="C873" s="5"/>
-    </row>
-    <row r="874" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A874" s="4"/>
-      <c r="B874" s="2"/>
-      <c r="C874" s="5"/>
-    </row>
-    <row r="875" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A875" s="4"/>
-      <c r="B875" s="2"/>
-      <c r="C875" s="5"/>
-    </row>
-    <row r="876" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A876" s="4"/>
-      <c r="B876" s="2"/>
-      <c r="C876" s="5"/>
-    </row>
-    <row r="877" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A877" s="4"/>
-      <c r="B877" s="2"/>
-      <c r="C877" s="5"/>
-    </row>
-    <row r="878" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A878" s="4"/>
-      <c r="B878" s="2"/>
-      <c r="C878" s="5"/>
-    </row>
-    <row r="879" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A879" s="4"/>
-      <c r="B879" s="2"/>
-      <c r="C879" s="5"/>
-    </row>
-    <row r="880" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A880" s="4"/>
-      <c r="B880" s="2"/>
-      <c r="C880" s="5"/>
-    </row>
-    <row r="881" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A881" s="4"/>
-      <c r="B881" s="2"/>
-      <c r="C881" s="5"/>
-    </row>
-    <row r="882" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A882" s="4"/>
-      <c r="B882" s="2"/>
-      <c r="C882" s="5"/>
-    </row>
-    <row r="883" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A883" s="4"/>
-      <c r="B883" s="2"/>
-      <c r="C883" s="5"/>
-    </row>
-    <row r="884" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A884" s="4"/>
-      <c r="B884" s="2"/>
-      <c r="C884" s="5"/>
-    </row>
-    <row r="885" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A885" s="4"/>
-      <c r="B885" s="2"/>
-      <c r="C885" s="5"/>
-    </row>
-    <row r="886" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A886" s="4"/>
-      <c r="B886" s="2"/>
-      <c r="C886" s="5"/>
-    </row>
-    <row r="887" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A887" s="4"/>
-      <c r="B887" s="2"/>
-      <c r="C887" s="5"/>
-    </row>
-    <row r="888" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A888" s="4"/>
-      <c r="B888" s="2"/>
-      <c r="C888" s="5"/>
-    </row>
-    <row r="889" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A889" s="4"/>
-      <c r="B889" s="2"/>
-      <c r="C889" s="5"/>
-    </row>
-    <row r="890" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A890" s="4"/>
-      <c r="B890" s="2"/>
-      <c r="C890" s="5"/>
-    </row>
-    <row r="891" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A891" s="4"/>
-      <c r="B891" s="2"/>
-      <c r="C891" s="5"/>
-    </row>
-    <row r="892" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A892" s="4"/>
-      <c r="B892" s="2"/>
-      <c r="C892" s="5"/>
-    </row>
-    <row r="893" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A893" s="4"/>
-      <c r="B893" s="2"/>
-      <c r="C893" s="5"/>
-    </row>
-    <row r="894" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A894" s="4"/>
-      <c r="B894" s="2"/>
-      <c r="C894" s="5"/>
-    </row>
-    <row r="895" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A895" s="4"/>
-      <c r="B895" s="2"/>
-      <c r="C895" s="5"/>
-    </row>
-    <row r="896" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A896" s="4"/>
-      <c r="B896" s="2"/>
-      <c r="C896" s="5"/>
-    </row>
-    <row r="897" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A897" s="4"/>
-      <c r="B897" s="2"/>
-      <c r="C897" s="5"/>
-    </row>
-    <row r="898" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A898" s="4"/>
-      <c r="B898" s="2"/>
-      <c r="C898" s="5"/>
-    </row>
-    <row r="899" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A899" s="4"/>
-      <c r="B899" s="2"/>
-      <c r="C899" s="5"/>
-    </row>
-    <row r="900" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A900" s="4"/>
-      <c r="B900" s="2"/>
-      <c r="C900" s="5"/>
-    </row>
-    <row r="901" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A901" s="4"/>
-      <c r="B901" s="2"/>
-      <c r="C901" s="5"/>
-    </row>
-    <row r="902" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A902" s="4"/>
-      <c r="B902" s="2"/>
-      <c r="C902" s="5"/>
-    </row>
-    <row r="903" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A903" s="4"/>
-      <c r="B903" s="2"/>
-      <c r="C903" s="5"/>
-    </row>
-    <row r="904" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A904" s="4"/>
-      <c r="B904" s="2"/>
-      <c r="C904" s="5"/>
-    </row>
-    <row r="905" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A905" s="4"/>
-      <c r="B905" s="2"/>
-      <c r="C905" s="5"/>
-    </row>
-    <row r="906" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A906" s="4"/>
-      <c r="B906" s="2"/>
-      <c r="C906" s="5"/>
-    </row>
-    <row r="907" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A907" s="4"/>
-      <c r="B907" s="2"/>
-      <c r="C907" s="5"/>
-    </row>
-    <row r="908" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A908" s="4"/>
-      <c r="B908" s="2"/>
-      <c r="C908" s="5"/>
-    </row>
-    <row r="909" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A909" s="4"/>
-      <c r="B909" s="2"/>
-      <c r="C909" s="5"/>
-    </row>
-    <row r="910" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A910" s="4"/>
-      <c r="B910" s="2"/>
-      <c r="C910" s="5"/>
-    </row>
-    <row r="911" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A911" s="4"/>
-      <c r="B911" s="2"/>
-      <c r="C911" s="5"/>
-    </row>
-    <row r="912" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A912" s="4"/>
-      <c r="B912" s="2"/>
-      <c r="C912" s="5"/>
-    </row>
-    <row r="913" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A913" s="4"/>
-      <c r="B913" s="2"/>
-      <c r="C913" s="5"/>
-    </row>
-    <row r="914" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A914" s="4"/>
-      <c r="B914" s="2"/>
-      <c r="C914" s="5"/>
-    </row>
-    <row r="915" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A915" s="4"/>
-      <c r="B915" s="2"/>
-      <c r="C915" s="5"/>
-    </row>
-    <row r="916" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A916" s="4"/>
-      <c r="B916" s="2"/>
-      <c r="C916" s="5"/>
-    </row>
-    <row r="917" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A917" s="4"/>
-      <c r="B917" s="2"/>
-      <c r="C917" s="5"/>
-    </row>
-    <row r="918" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A918" s="4"/>
-      <c r="B918" s="2"/>
-      <c r="C918" s="5"/>
-    </row>
-    <row r="919" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A919" s="4"/>
-      <c r="B919" s="2"/>
-      <c r="C919" s="5"/>
-    </row>
-    <row r="920" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A920" s="4"/>
-      <c r="B920" s="2"/>
-      <c r="C920" s="5"/>
-    </row>
-    <row r="921" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A921" s="4"/>
-      <c r="B921" s="2"/>
-      <c r="C921" s="5"/>
-    </row>
-    <row r="922" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A922" s="4"/>
-      <c r="B922" s="2"/>
-      <c r="C922" s="5"/>
-    </row>
-    <row r="923" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A923" s="4"/>
-      <c r="B923" s="2"/>
-      <c r="C923" s="5"/>
-    </row>
-    <row r="924" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A924" s="4"/>
-      <c r="B924" s="2"/>
-      <c r="C924" s="5"/>
-    </row>
-    <row r="925" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A925" s="4"/>
-      <c r="B925" s="2"/>
-      <c r="C925" s="5"/>
-    </row>
-    <row r="926" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A926" s="4"/>
-      <c r="B926" s="2"/>
-      <c r="C926" s="5"/>
-    </row>
-    <row r="927" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A927" s="4"/>
-      <c r="B927" s="2"/>
-      <c r="C927" s="5"/>
-    </row>
-    <row r="928" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A928" s="4"/>
-      <c r="B928" s="2"/>
-      <c r="C928" s="5"/>
-    </row>
-    <row r="929" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A929" s="4"/>
-      <c r="B929" s="2"/>
-      <c r="C929" s="5"/>
-    </row>
-    <row r="930" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A930" s="4"/>
-      <c r="B930" s="2"/>
-      <c r="C930" s="5"/>
-    </row>
-    <row r="931" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A931" s="4"/>
-      <c r="B931" s="2"/>
-      <c r="C931" s="5"/>
-    </row>
-    <row r="932" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A932" s="4"/>
-      <c r="B932" s="2"/>
-      <c r="C932" s="5"/>
-    </row>
-    <row r="933" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A933" s="4"/>
-      <c r="B933" s="2"/>
-      <c r="C933" s="5"/>
-    </row>
-    <row r="934" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A934" s="4"/>
-      <c r="B934" s="2"/>
-      <c r="C934" s="5"/>
-    </row>
-    <row r="935" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A935" s="4"/>
-      <c r="B935" s="2"/>
-      <c r="C935" s="5"/>
-    </row>
-    <row r="936" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A936" s="4"/>
-      <c r="B936" s="2"/>
-      <c r="C936" s="5"/>
-    </row>
-    <row r="937" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A937" s="4"/>
-      <c r="B937" s="2"/>
-      <c r="C937" s="5"/>
-    </row>
-    <row r="938" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A938" s="4"/>
-      <c r="B938" s="2"/>
-      <c r="C938" s="5"/>
-    </row>
-    <row r="939" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A939" s="4"/>
-      <c r="B939" s="2"/>
-      <c r="C939" s="5"/>
-    </row>
-    <row r="940" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A940" s="4"/>
-      <c r="B940" s="2"/>
-      <c r="C940" s="5"/>
-    </row>
-    <row r="941" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A941" s="4"/>
-      <c r="B941" s="2"/>
-      <c r="C941" s="5"/>
-    </row>
-    <row r="942" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A942" s="4"/>
-      <c r="B942" s="2"/>
-      <c r="C942" s="5"/>
-    </row>
-    <row r="943" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A943" s="4"/>
-      <c r="B943" s="2"/>
-      <c r="C943" s="5"/>
-    </row>
-    <row r="944" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A944" s="4"/>
-      <c r="B944" s="2"/>
-      <c r="C944" s="5"/>
-    </row>
-    <row r="945" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A945" s="4"/>
-      <c r="B945" s="2"/>
-      <c r="C945" s="5"/>
-    </row>
-    <row r="946" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A946" s="4"/>
-      <c r="B946" s="2"/>
-      <c r="C946" s="5"/>
-    </row>
-    <row r="947" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A947" s="4"/>
-      <c r="B947" s="2"/>
-      <c r="C947" s="5"/>
-    </row>
-    <row r="948" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A948" s="4"/>
-      <c r="B948" s="2"/>
-      <c r="C948" s="5"/>
-    </row>
-    <row r="949" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A949" s="4"/>
-      <c r="B949" s="2"/>
-      <c r="C949" s="5"/>
-    </row>
-    <row r="950" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A950" s="4"/>
-      <c r="B950" s="2"/>
-      <c r="C950" s="5"/>
-    </row>
-    <row r="951" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A951" s="4"/>
-      <c r="B951" s="2"/>
-      <c r="C951" s="5"/>
-    </row>
-    <row r="952" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A952" s="4"/>
-      <c r="B952" s="2"/>
-      <c r="C952" s="5"/>
-    </row>
-    <row r="953" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A953" s="4"/>
-      <c r="B953" s="2"/>
-      <c r="C953" s="5"/>
-    </row>
-    <row r="954" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A954" s="4"/>
-      <c r="B954" s="2"/>
-      <c r="C954" s="5"/>
-    </row>
-    <row r="955" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A955" s="4"/>
-      <c r="B955" s="2"/>
-      <c r="C955" s="5"/>
-    </row>
-    <row r="956" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A956" s="4"/>
-      <c r="B956" s="2"/>
-      <c r="C956" s="5"/>
-    </row>
-    <row r="957" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A957" s="4"/>
-      <c r="B957" s="2"/>
-      <c r="C957" s="5"/>
-    </row>
-    <row r="958" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A958" s="4"/>
-      <c r="B958" s="2"/>
-      <c r="C958" s="5"/>
-    </row>
-    <row r="959" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A959" s="4"/>
-      <c r="B959" s="2"/>
-      <c r="C959" s="5"/>
-    </row>
-    <row r="960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A800" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B800" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C800" s="5">
+        <v>26</v>
+      </c>
+      <c r="D800" t="s">
+        <v>176</v>
+      </c>
+      <c r="E800" t="s">
+        <v>165</v>
+      </c>
+      <c r="F800" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A801" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B801" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C801" s="5">
+        <v>13</v>
+      </c>
+      <c r="D801" t="s">
+        <v>176</v>
+      </c>
+      <c r="E801" t="s">
+        <v>165</v>
+      </c>
+      <c r="F801" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A802" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B802" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C802" s="5">
+        <v>4</v>
+      </c>
+      <c r="D802" t="s">
+        <v>176</v>
+      </c>
+      <c r="E802" t="s">
+        <v>165</v>
+      </c>
+      <c r="F802" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A803" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B803" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C803" s="5">
+        <v>6</v>
+      </c>
+      <c r="D803" t="s">
+        <v>166</v>
+      </c>
+      <c r="E803" t="s">
+        <v>165</v>
+      </c>
+      <c r="F803" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A804" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B804" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C804" s="5">
+        <v>0</v>
+      </c>
+      <c r="D804" t="s">
+        <v>176</v>
+      </c>
+      <c r="E804" t="s">
+        <v>165</v>
+      </c>
+      <c r="F804" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A805" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B805" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C805" s="5">
+        <v>126</v>
+      </c>
+      <c r="D805" t="s">
+        <v>167</v>
+      </c>
+      <c r="E805" t="s">
+        <v>165</v>
+      </c>
+      <c r="F805" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A806" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C806" s="5">
+        <v>16</v>
+      </c>
+      <c r="D806" t="s">
+        <v>168</v>
+      </c>
+      <c r="E806" t="s">
+        <v>169</v>
+      </c>
+      <c r="F806" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A807" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B807" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C807" s="5">
+        <v>4</v>
+      </c>
+      <c r="D807" t="s">
+        <v>168</v>
+      </c>
+      <c r="E807" t="s">
+        <v>169</v>
+      </c>
+      <c r="F807" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A808" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B808" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C808" s="5">
+        <v>0</v>
+      </c>
+      <c r="D808" t="s">
+        <v>170</v>
+      </c>
+      <c r="E808" t="s">
+        <v>165</v>
+      </c>
+      <c r="F808" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A809" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B809" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C809" s="5">
+        <v>2</v>
+      </c>
+      <c r="D809" t="s">
+        <v>168</v>
+      </c>
+      <c r="E809" t="s">
+        <v>169</v>
+      </c>
+      <c r="F809" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A810" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B810" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C810" s="5">
+        <v>1</v>
+      </c>
+      <c r="D810" t="s">
+        <v>168</v>
+      </c>
+      <c r="E810" t="s">
+        <v>171</v>
+      </c>
+      <c r="F810" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A811" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B811" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C811" s="5">
+        <v>13</v>
+      </c>
+      <c r="D811" t="s">
+        <v>168</v>
+      </c>
+      <c r="E811" t="s">
+        <v>172</v>
+      </c>
+      <c r="F811" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A812" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B812" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C812" s="5">
+        <v>95</v>
+      </c>
+      <c r="D812" t="s">
+        <v>167</v>
+      </c>
+      <c r="E812" t="s">
+        <v>165</v>
+      </c>
+      <c r="F812" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A813" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B813" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C813" s="5">
+        <v>2</v>
+      </c>
+      <c r="D813" t="s">
+        <v>170</v>
+      </c>
+      <c r="E813" t="s">
+        <v>165</v>
+      </c>
+      <c r="F813" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A814" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B814" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C814" s="5">
+        <v>2</v>
+      </c>
+      <c r="D814" t="s">
+        <v>176</v>
+      </c>
+      <c r="E814" t="s">
+        <v>165</v>
+      </c>
+      <c r="F814" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A815" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B815" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C815" s="5">
+        <v>1</v>
+      </c>
+      <c r="D815" t="s">
+        <v>176</v>
+      </c>
+      <c r="E815" t="s">
+        <v>165</v>
+      </c>
+      <c r="F815" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A816" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B816" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C816" s="5">
+        <v>12</v>
+      </c>
+      <c r="D816" t="s">
+        <v>166</v>
+      </c>
+      <c r="E816" t="s">
+        <v>165</v>
+      </c>
+      <c r="F816" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A817" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B817" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C817" s="5">
+        <v>69</v>
+      </c>
+      <c r="D817" t="s">
+        <v>167</v>
+      </c>
+      <c r="E817" t="s">
+        <v>165</v>
+      </c>
+      <c r="F817" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A818" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B818" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C818" s="5">
+        <v>23</v>
+      </c>
+      <c r="D818" t="s">
+        <v>176</v>
+      </c>
+      <c r="E818" t="s">
+        <v>165</v>
+      </c>
+      <c r="F818" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A819" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B819" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C819" s="5">
+        <v>5</v>
+      </c>
+      <c r="D819" t="s">
+        <v>168</v>
+      </c>
+      <c r="E819" t="s">
+        <v>169</v>
+      </c>
+      <c r="F819" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A820" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B820" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C820" s="5">
+        <v>4</v>
+      </c>
+      <c r="D820" t="s">
+        <v>176</v>
+      </c>
+      <c r="E820" t="s">
+        <v>165</v>
+      </c>
+      <c r="F820" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A821" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B821" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C821" s="5">
+        <v>104</v>
+      </c>
+      <c r="D821" t="s">
+        <v>167</v>
+      </c>
+      <c r="E821" t="s">
+        <v>165</v>
+      </c>
+      <c r="F821" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A822" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B822" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C822" s="5">
+        <v>60</v>
+      </c>
+      <c r="D822" t="s">
+        <v>166</v>
+      </c>
+      <c r="E822" t="s">
+        <v>165</v>
+      </c>
+      <c r="F822" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A823" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C823" s="5">
+        <v>32</v>
+      </c>
+      <c r="D823" t="s">
+        <v>167</v>
+      </c>
+      <c r="E823" t="s">
+        <v>165</v>
+      </c>
+      <c r="F823" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A824" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C824" s="5">
+        <v>35</v>
+      </c>
+      <c r="D824" t="s">
+        <v>168</v>
+      </c>
+      <c r="E824" t="s">
+        <v>171</v>
+      </c>
+      <c r="F824" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A825" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B825" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C825" s="5">
+        <v>2</v>
+      </c>
+      <c r="D825" t="s">
+        <v>167</v>
+      </c>
+      <c r="E825" t="s">
+        <v>165</v>
+      </c>
+      <c r="F825" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A826" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C826" s="5">
+        <v>1</v>
+      </c>
+      <c r="D826" t="s">
+        <v>168</v>
+      </c>
+      <c r="E826" t="s">
+        <v>169</v>
+      </c>
+      <c r="F826" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A827" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C827" s="5">
+        <v>57</v>
+      </c>
+      <c r="D827" t="s">
+        <v>173</v>
+      </c>
+      <c r="E827" t="s">
+        <v>165</v>
+      </c>
+      <c r="F827" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A828" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B828" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C828" s="5">
+        <v>42</v>
+      </c>
+      <c r="D828" t="s">
+        <v>166</v>
+      </c>
+      <c r="E828" t="s">
+        <v>165</v>
+      </c>
+      <c r="F828" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A829" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C829" s="5">
+        <v>107</v>
+      </c>
+      <c r="D829" t="s">
+        <v>167</v>
+      </c>
+      <c r="E829" t="s">
+        <v>165</v>
+      </c>
+      <c r="F829" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A830" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C830" s="5">
+        <v>5</v>
+      </c>
+      <c r="D830" t="s">
+        <v>168</v>
+      </c>
+      <c r="E830" t="s">
+        <v>169</v>
+      </c>
+      <c r="F830" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A831" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C831" s="5">
+        <v>450</v>
+      </c>
+      <c r="D831" t="s">
+        <v>176</v>
+      </c>
+      <c r="E831" t="s">
+        <v>165</v>
+      </c>
+      <c r="F831" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A832" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B832" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C832" s="5">
+        <v>1</v>
+      </c>
+      <c r="D832" t="s">
+        <v>168</v>
+      </c>
+      <c r="E832" t="s">
+        <v>169</v>
+      </c>
+      <c r="F832" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A833" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B833" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C833" s="5">
+        <v>46</v>
+      </c>
+      <c r="D833" t="s">
+        <v>176</v>
+      </c>
+      <c r="E833" t="s">
+        <v>165</v>
+      </c>
+      <c r="F833" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A834" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B834" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C834" s="5">
+        <v>54</v>
+      </c>
+      <c r="D834" t="s">
+        <v>176</v>
+      </c>
+      <c r="E834" t="s">
+        <v>165</v>
+      </c>
+      <c r="F834" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A835" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B835" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C835" s="5">
+        <v>2</v>
+      </c>
+      <c r="D835" t="s">
+        <v>176</v>
+      </c>
+      <c r="E835" t="s">
+        <v>165</v>
+      </c>
+      <c r="F835" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A836" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B836" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C836" s="5">
+        <v>10</v>
+      </c>
+      <c r="D836" t="s">
+        <v>170</v>
+      </c>
+      <c r="E836" t="s">
+        <v>165</v>
+      </c>
+      <c r="F836" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A837" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B837" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C837" s="5">
+        <v>32</v>
+      </c>
+      <c r="D837" t="s">
+        <v>170</v>
+      </c>
+      <c r="E837" t="s">
+        <v>165</v>
+      </c>
+      <c r="F837" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A838" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B838" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C838" s="5">
+        <v>1</v>
+      </c>
+      <c r="D838" t="s">
+        <v>168</v>
+      </c>
+      <c r="E838" t="s">
+        <v>169</v>
+      </c>
+      <c r="F838" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A839" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B839" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C839" s="5">
+        <v>46</v>
+      </c>
+      <c r="D839" t="s">
+        <v>173</v>
+      </c>
+      <c r="E839" t="s">
+        <v>165</v>
+      </c>
+      <c r="F839" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A840" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B840" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C840" s="5">
+        <v>25</v>
+      </c>
+      <c r="D840" t="s">
+        <v>176</v>
+      </c>
+      <c r="E840" t="s">
+        <v>165</v>
+      </c>
+      <c r="F840" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A841" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B841" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C841" s="5">
+        <v>2</v>
+      </c>
+      <c r="D841" t="s">
+        <v>176</v>
+      </c>
+      <c r="E841" t="s">
+        <v>165</v>
+      </c>
+      <c r="F841" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A842" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B842" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C842" s="5">
+        <v>126</v>
+      </c>
+      <c r="D842" t="s">
+        <v>173</v>
+      </c>
+      <c r="E842" t="s">
+        <v>165</v>
+      </c>
+      <c r="F842" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A843" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B843" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C843" s="5">
+        <v>2</v>
+      </c>
+      <c r="D843" t="s">
+        <v>168</v>
+      </c>
+      <c r="E843" t="s">
+        <v>169</v>
+      </c>
+      <c r="F843" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A844" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C844" s="5">
+        <v>1</v>
+      </c>
+      <c r="D844" t="s">
+        <v>176</v>
+      </c>
+      <c r="E844" t="s">
+        <v>165</v>
+      </c>
+      <c r="F844" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A845" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C845" s="5">
+        <v>3</v>
+      </c>
+      <c r="D845" t="s">
+        <v>168</v>
+      </c>
+      <c r="E845" t="s">
+        <v>169</v>
+      </c>
+      <c r="F845" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A846" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C846" s="5">
+        <v>180</v>
+      </c>
+      <c r="D846" t="s">
+        <v>168</v>
+      </c>
+      <c r="E846" t="s">
+        <v>169</v>
+      </c>
+      <c r="F846" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A847" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C847" s="5">
+        <v>2</v>
+      </c>
+      <c r="D847" t="s">
+        <v>168</v>
+      </c>
+      <c r="E847" t="s">
+        <v>169</v>
+      </c>
+      <c r="F847" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A848" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C848" s="5">
+        <v>3</v>
+      </c>
+      <c r="D848" t="s">
+        <v>168</v>
+      </c>
+      <c r="E848" t="s">
+        <v>169</v>
+      </c>
+      <c r="F848" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A849" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C849" s="5">
+        <v>5</v>
+      </c>
+      <c r="D849" t="s">
+        <v>167</v>
+      </c>
+      <c r="E849" t="s">
+        <v>165</v>
+      </c>
+      <c r="F849" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A850" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C850" s="5">
+        <v>66</v>
+      </c>
+      <c r="D850" t="s">
+        <v>167</v>
+      </c>
+      <c r="E850" t="s">
+        <v>165</v>
+      </c>
+      <c r="F850" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A851" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C851" s="5">
+        <v>6</v>
+      </c>
+      <c r="D851" t="s">
+        <v>176</v>
+      </c>
+      <c r="E851" t="s">
+        <v>165</v>
+      </c>
+      <c r="F851" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A852" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C852" s="5">
+        <v>69</v>
+      </c>
+      <c r="D852" t="s">
+        <v>170</v>
+      </c>
+      <c r="E852" t="s">
+        <v>165</v>
+      </c>
+      <c r="F852" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A853" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C853" s="5">
+        <v>2</v>
+      </c>
+      <c r="D853" t="s">
+        <v>176</v>
+      </c>
+      <c r="E853" t="s">
+        <v>165</v>
+      </c>
+      <c r="F853" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A854" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C854" s="5">
+        <v>5</v>
+      </c>
+      <c r="D854" t="s">
+        <v>167</v>
+      </c>
+      <c r="E854" t="s">
+        <v>165</v>
+      </c>
+      <c r="F854" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A855" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C855" s="5">
+        <v>12</v>
+      </c>
+      <c r="D855" t="s">
+        <v>168</v>
+      </c>
+      <c r="E855" t="s">
+        <v>169</v>
+      </c>
+      <c r="F855" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A856" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C856" s="5">
+        <v>22</v>
+      </c>
+      <c r="D856" t="s">
+        <v>168</v>
+      </c>
+      <c r="E856" t="s">
+        <v>169</v>
+      </c>
+      <c r="F856" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A857" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C857" s="5">
+        <v>7</v>
+      </c>
+      <c r="D857" t="s">
+        <v>173</v>
+      </c>
+      <c r="E857" t="s">
+        <v>165</v>
+      </c>
+      <c r="F857" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A858" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C858" s="5">
+        <v>294</v>
+      </c>
+      <c r="D858" t="s">
+        <v>167</v>
+      </c>
+      <c r="E858" t="s">
+        <v>165</v>
+      </c>
+      <c r="F858" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A859" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C859" s="5">
+        <v>313</v>
+      </c>
+      <c r="D859" t="s">
+        <v>166</v>
+      </c>
+      <c r="E859" t="s">
+        <v>165</v>
+      </c>
+      <c r="F859" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A860" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C860" s="5">
+        <v>28</v>
+      </c>
+      <c r="D860" t="s">
+        <v>176</v>
+      </c>
+      <c r="E860" t="s">
+        <v>165</v>
+      </c>
+      <c r="F860" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A861" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C861" s="5">
+        <v>8</v>
+      </c>
+      <c r="D861" t="s">
+        <v>168</v>
+      </c>
+      <c r="E861" t="s">
+        <v>174</v>
+      </c>
+      <c r="F861" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A862" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C862" s="5">
+        <v>9</v>
+      </c>
+      <c r="D862" t="s">
+        <v>170</v>
+      </c>
+      <c r="E862" t="s">
+        <v>165</v>
+      </c>
+      <c r="F862" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A863" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C863" s="5">
+        <v>3</v>
+      </c>
+      <c r="D863" t="s">
+        <v>176</v>
+      </c>
+      <c r="E863" t="s">
+        <v>165</v>
+      </c>
+      <c r="F863" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A864" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C864" s="5">
+        <v>2</v>
+      </c>
+      <c r="D864" t="s">
+        <v>168</v>
+      </c>
+      <c r="E864" t="s">
+        <v>169</v>
+      </c>
+      <c r="F864" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A865" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C865" s="5">
+        <v>1</v>
+      </c>
+      <c r="D865" t="s">
+        <v>176</v>
+      </c>
+      <c r="E865" t="s">
+        <v>165</v>
+      </c>
+      <c r="F865" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A866" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C866" s="5">
+        <v>11</v>
+      </c>
+      <c r="D866" t="s">
+        <v>176</v>
+      </c>
+      <c r="E866" t="s">
+        <v>165</v>
+      </c>
+      <c r="F866" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A867" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C867" s="5">
+        <v>19</v>
+      </c>
+      <c r="D867" t="s">
+        <v>176</v>
+      </c>
+      <c r="E867" t="s">
+        <v>165</v>
+      </c>
+      <c r="F867" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A868" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C868" s="5">
+        <v>45</v>
+      </c>
+      <c r="D868" t="s">
+        <v>166</v>
+      </c>
+      <c r="E868" t="s">
+        <v>165</v>
+      </c>
+      <c r="F868" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A869" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B869" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C869" s="5">
+        <v>1</v>
+      </c>
+      <c r="D869" t="s">
+        <v>176</v>
+      </c>
+      <c r="E869" t="s">
+        <v>165</v>
+      </c>
+      <c r="F869" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A870" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B870" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C870" s="5">
+        <v>47</v>
+      </c>
+      <c r="D870" t="s">
+        <v>170</v>
+      </c>
+      <c r="E870" t="s">
+        <v>165</v>
+      </c>
+      <c r="F870" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A871" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B871" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C871" s="5">
+        <v>85</v>
+      </c>
+      <c r="D871" t="s">
+        <v>166</v>
+      </c>
+      <c r="E871" t="s">
+        <v>165</v>
+      </c>
+      <c r="F871" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A872" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B872" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C872" s="5">
+        <v>1</v>
+      </c>
+      <c r="D872" t="s">
+        <v>168</v>
+      </c>
+      <c r="E872" t="s">
+        <v>169</v>
+      </c>
+      <c r="F872" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A873" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B873" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C873" s="5">
+        <v>7</v>
+      </c>
+      <c r="D873" t="s">
+        <v>168</v>
+      </c>
+      <c r="E873" t="s">
+        <v>169</v>
+      </c>
+      <c r="F873" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A874" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B874" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C874" s="5">
+        <v>47</v>
+      </c>
+      <c r="D874" t="s">
+        <v>176</v>
+      </c>
+      <c r="E874" t="s">
+        <v>165</v>
+      </c>
+      <c r="F874" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A875" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B875" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C875" s="5">
+        <v>0</v>
+      </c>
+      <c r="D875" t="s">
+        <v>176</v>
+      </c>
+      <c r="E875" t="s">
+        <v>165</v>
+      </c>
+      <c r="F875" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A876" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B876" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C876" s="5">
+        <v>167</v>
+      </c>
+      <c r="D876" t="s">
+        <v>170</v>
+      </c>
+      <c r="E876" t="s">
+        <v>165</v>
+      </c>
+      <c r="F876" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A877" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B877" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C877" s="5">
+        <v>30</v>
+      </c>
+      <c r="D877" t="s">
+        <v>168</v>
+      </c>
+      <c r="E877" t="s">
+        <v>174</v>
+      </c>
+      <c r="F877" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A878" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B878" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C878" s="5">
+        <v>2</v>
+      </c>
+      <c r="D878" t="s">
+        <v>176</v>
+      </c>
+      <c r="E878" t="s">
+        <v>165</v>
+      </c>
+      <c r="F878" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A879" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B879" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C879" s="5">
+        <v>55</v>
+      </c>
+      <c r="D879" t="s">
+        <v>167</v>
+      </c>
+      <c r="E879" t="s">
+        <v>165</v>
+      </c>
+      <c r="F879" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A880" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B880" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C880" s="5">
+        <v>74</v>
+      </c>
+      <c r="D880" t="s">
+        <v>176</v>
+      </c>
+      <c r="E880" t="s">
+        <v>165</v>
+      </c>
+      <c r="F880" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A881" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B881" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C881" s="5">
+        <v>8</v>
+      </c>
+      <c r="D881" t="s">
+        <v>168</v>
+      </c>
+      <c r="E881" t="s">
+        <v>169</v>
+      </c>
+      <c r="F881" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A882" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B882" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C882" s="5">
+        <v>2</v>
+      </c>
+      <c r="D882" t="s">
+        <v>173</v>
+      </c>
+      <c r="E882" t="s">
+        <v>165</v>
+      </c>
+      <c r="F882" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A883" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B883" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C883" s="5">
+        <v>4</v>
+      </c>
+      <c r="D883" t="s">
+        <v>176</v>
+      </c>
+      <c r="E883" t="s">
+        <v>165</v>
+      </c>
+      <c r="F883" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A884" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B884" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C884" s="5">
+        <v>12</v>
+      </c>
+      <c r="D884" t="s">
+        <v>173</v>
+      </c>
+      <c r="E884" t="s">
+        <v>165</v>
+      </c>
+      <c r="F884" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A885" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B885" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C885" s="5">
+        <v>3</v>
+      </c>
+      <c r="D885" t="s">
+        <v>168</v>
+      </c>
+      <c r="E885" t="s">
+        <v>169</v>
+      </c>
+      <c r="F885" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A886" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B886" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C886" s="5">
+        <v>9</v>
+      </c>
+      <c r="D886" t="s">
+        <v>173</v>
+      </c>
+      <c r="E886" t="s">
+        <v>165</v>
+      </c>
+      <c r="F886" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A887" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B887" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C887" s="5">
+        <v>9</v>
+      </c>
+      <c r="D887" t="s">
+        <v>176</v>
+      </c>
+      <c r="E887" t="s">
+        <v>165</v>
+      </c>
+      <c r="F887" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A888" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B888" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C888" s="5">
+        <v>0</v>
+      </c>
+      <c r="D888" t="s">
+        <v>176</v>
+      </c>
+      <c r="E888" t="s">
+        <v>165</v>
+      </c>
+      <c r="F888" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A889" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B889" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C889" s="5">
+        <v>13</v>
+      </c>
+      <c r="D889" t="s">
+        <v>170</v>
+      </c>
+      <c r="E889" t="s">
+        <v>165</v>
+      </c>
+      <c r="F889" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A890" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B890" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C890" s="5">
+        <v>14</v>
+      </c>
+      <c r="D890" t="s">
+        <v>173</v>
+      </c>
+      <c r="E890" t="s">
+        <v>165</v>
+      </c>
+      <c r="F890" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A891" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B891" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C891" s="5">
+        <v>22</v>
+      </c>
+      <c r="D891" t="s">
+        <v>168</v>
+      </c>
+      <c r="E891" t="s">
+        <v>171</v>
+      </c>
+      <c r="F891" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A892" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C892" s="5">
+        <v>8</v>
+      </c>
+      <c r="D892" t="s">
+        <v>176</v>
+      </c>
+      <c r="E892" t="s">
+        <v>165</v>
+      </c>
+      <c r="F892" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A893" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C893" s="5">
+        <v>4</v>
+      </c>
+      <c r="D893" t="s">
+        <v>176</v>
+      </c>
+      <c r="E893" t="s">
+        <v>165</v>
+      </c>
+      <c r="F893" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A894" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C894" s="5">
+        <v>9</v>
+      </c>
+      <c r="D894" t="s">
+        <v>173</v>
+      </c>
+      <c r="E894" t="s">
+        <v>165</v>
+      </c>
+      <c r="F894" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A895" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C895" s="5">
+        <v>10</v>
+      </c>
+      <c r="D895" t="s">
+        <v>167</v>
+      </c>
+      <c r="E895" t="s">
+        <v>165</v>
+      </c>
+      <c r="F895" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A896" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C896" s="5">
+        <v>5</v>
+      </c>
+      <c r="D896" t="s">
+        <v>173</v>
+      </c>
+      <c r="E896" t="s">
+        <v>165</v>
+      </c>
+      <c r="F896" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A897" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C897" s="5">
+        <v>3</v>
+      </c>
+      <c r="D897" t="s">
+        <v>176</v>
+      </c>
+      <c r="E897" t="s">
+        <v>165</v>
+      </c>
+      <c r="F897" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A898" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C898" s="5">
+        <v>1</v>
+      </c>
+      <c r="D898" t="s">
+        <v>168</v>
+      </c>
+      <c r="E898" t="s">
+        <v>169</v>
+      </c>
+      <c r="F898" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A899" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C899" s="5">
+        <v>9</v>
+      </c>
+      <c r="D899" t="s">
+        <v>170</v>
+      </c>
+      <c r="E899" t="s">
+        <v>165</v>
+      </c>
+      <c r="F899" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A900" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C900" s="5">
+        <v>50</v>
+      </c>
+      <c r="D900" t="s">
+        <v>176</v>
+      </c>
+      <c r="E900" t="s">
+        <v>165</v>
+      </c>
+      <c r="F900" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A901" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C901" s="5">
+        <v>184</v>
+      </c>
+      <c r="D901" t="s">
+        <v>168</v>
+      </c>
+      <c r="E901" t="s">
+        <v>172</v>
+      </c>
+      <c r="F901" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A902" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C902" s="5">
+        <v>2</v>
+      </c>
+      <c r="D902" t="s">
+        <v>176</v>
+      </c>
+      <c r="E902" t="s">
+        <v>165</v>
+      </c>
+      <c r="F902" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A903" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C903" s="5">
+        <v>55</v>
+      </c>
+      <c r="D903" t="s">
+        <v>176</v>
+      </c>
+      <c r="E903" t="s">
+        <v>165</v>
+      </c>
+      <c r="F903" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A904" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C904" s="5">
+        <v>2</v>
+      </c>
+      <c r="D904" t="s">
+        <v>168</v>
+      </c>
+      <c r="E904" t="s">
+        <v>169</v>
+      </c>
+      <c r="F904" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A905" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C905" s="5">
+        <v>12</v>
+      </c>
+      <c r="D905" t="s">
+        <v>173</v>
+      </c>
+      <c r="E905" t="s">
+        <v>165</v>
+      </c>
+      <c r="F905" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A906" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C906" s="5">
+        <v>3</v>
+      </c>
+      <c r="D906" t="s">
+        <v>173</v>
+      </c>
+      <c r="E906" t="s">
+        <v>165</v>
+      </c>
+      <c r="F906" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A907" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C907" s="5">
+        <v>52</v>
+      </c>
+      <c r="D907" t="s">
+        <v>176</v>
+      </c>
+      <c r="E907" t="s">
+        <v>165</v>
+      </c>
+      <c r="F907" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A908" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C908" s="5">
+        <v>17</v>
+      </c>
+      <c r="D908" t="s">
+        <v>176</v>
+      </c>
+      <c r="E908" t="s">
+        <v>165</v>
+      </c>
+      <c r="F908" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A909" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C909" s="5">
+        <v>251</v>
+      </c>
+      <c r="D909" t="s">
+        <v>166</v>
+      </c>
+      <c r="E909" t="s">
+        <v>165</v>
+      </c>
+      <c r="F909" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A910" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C910" s="5">
+        <v>0</v>
+      </c>
+      <c r="D910" t="s">
+        <v>168</v>
+      </c>
+      <c r="E910" t="s">
+        <v>169</v>
+      </c>
+      <c r="F910" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A911" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C911" s="5">
+        <v>16</v>
+      </c>
+      <c r="D911" t="s">
+        <v>176</v>
+      </c>
+      <c r="E911" t="s">
+        <v>165</v>
+      </c>
+      <c r="F911" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A912" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C912" s="5">
+        <v>12</v>
+      </c>
+      <c r="D912" t="s">
+        <v>166</v>
+      </c>
+      <c r="E912" t="s">
+        <v>165</v>
+      </c>
+      <c r="F912" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="913" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A913" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C913" s="5">
+        <v>3</v>
+      </c>
+      <c r="D913" t="s">
+        <v>168</v>
+      </c>
+      <c r="E913" t="s">
+        <v>169</v>
+      </c>
+      <c r="F913" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A914" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C914" s="5">
+        <v>19</v>
+      </c>
+      <c r="D914" t="s">
+        <v>166</v>
+      </c>
+      <c r="E914" t="s">
+        <v>165</v>
+      </c>
+      <c r="F914" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A915" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C915" s="5">
+        <v>4</v>
+      </c>
+      <c r="D915" t="s">
+        <v>166</v>
+      </c>
+      <c r="E915" t="s">
+        <v>165</v>
+      </c>
+      <c r="F915" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A916" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C916" s="5">
+        <v>7</v>
+      </c>
+      <c r="D916" t="s">
+        <v>176</v>
+      </c>
+      <c r="E916" t="s">
+        <v>165</v>
+      </c>
+      <c r="F916" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A917" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C917" s="5">
+        <v>6</v>
+      </c>
+      <c r="D917" t="s">
+        <v>176</v>
+      </c>
+      <c r="E917" t="s">
+        <v>165</v>
+      </c>
+      <c r="F917" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A918" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C918" s="5">
+        <v>5</v>
+      </c>
+      <c r="D918" t="s">
+        <v>168</v>
+      </c>
+      <c r="E918" t="s">
+        <v>171</v>
+      </c>
+      <c r="F918" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="919" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A919" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C919" s="5">
+        <v>11</v>
+      </c>
+      <c r="D919" t="s">
+        <v>176</v>
+      </c>
+      <c r="E919" t="s">
+        <v>165</v>
+      </c>
+      <c r="F919" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="920" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A920" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C920" s="5">
+        <v>29</v>
+      </c>
+      <c r="D920" t="s">
+        <v>168</v>
+      </c>
+      <c r="E920" t="s">
+        <v>174</v>
+      </c>
+      <c r="F920" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="921" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A921" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C921" s="5">
+        <v>23</v>
+      </c>
+      <c r="D921" t="s">
+        <v>168</v>
+      </c>
+      <c r="E921" t="s">
+        <v>171</v>
+      </c>
+      <c r="F921" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="922" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A922" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C922" s="5">
+        <v>140</v>
+      </c>
+      <c r="D922" t="s">
+        <v>167</v>
+      </c>
+      <c r="E922" t="s">
+        <v>165</v>
+      </c>
+      <c r="F922" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="923" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A923" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C923" s="5">
+        <v>137</v>
+      </c>
+      <c r="D923" t="s">
+        <v>167</v>
+      </c>
+      <c r="E923" t="s">
+        <v>165</v>
+      </c>
+      <c r="F923" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="924" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A924" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C924" s="5">
+        <v>6</v>
+      </c>
+      <c r="D924" t="s">
+        <v>176</v>
+      </c>
+      <c r="E924" t="s">
+        <v>165</v>
+      </c>
+      <c r="F924" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="925" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A925" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C925" s="5">
+        <v>17</v>
+      </c>
+      <c r="D925" t="s">
+        <v>176</v>
+      </c>
+      <c r="E925" t="s">
+        <v>165</v>
+      </c>
+      <c r="F925" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="926" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A926" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C926" s="5">
+        <v>3</v>
+      </c>
+      <c r="D926" t="s">
+        <v>168</v>
+      </c>
+      <c r="E926" t="s">
+        <v>174</v>
+      </c>
+      <c r="F926" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="927" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A927" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C927" s="5">
+        <v>1</v>
+      </c>
+      <c r="D927" t="s">
+        <v>173</v>
+      </c>
+      <c r="E927" t="s">
+        <v>165</v>
+      </c>
+      <c r="F927" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="928" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A928" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C928" s="5">
+        <v>54</v>
+      </c>
+      <c r="D928" t="s">
+        <v>170</v>
+      </c>
+      <c r="E928" t="s">
+        <v>165</v>
+      </c>
+      <c r="F928" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="929" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A929" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C929" s="5">
+        <v>16</v>
+      </c>
+      <c r="D929" t="s">
+        <v>166</v>
+      </c>
+      <c r="E929" t="s">
+        <v>165</v>
+      </c>
+      <c r="F929" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="930" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A930" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C930" s="5">
+        <v>32</v>
+      </c>
+      <c r="D930" t="s">
+        <v>166</v>
+      </c>
+      <c r="E930" t="s">
+        <v>165</v>
+      </c>
+      <c r="F930" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="931" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A931" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C931" s="5">
+        <v>3</v>
+      </c>
+      <c r="D931" t="s">
+        <v>176</v>
+      </c>
+      <c r="E931" t="s">
+        <v>165</v>
+      </c>
+      <c r="F931" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="932" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A932" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C932" s="5">
+        <v>1</v>
+      </c>
+      <c r="D932" t="s">
+        <v>173</v>
+      </c>
+      <c r="E932" t="s">
+        <v>165</v>
+      </c>
+      <c r="F932" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="933" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A933" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B933" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C933" s="5">
+        <v>20</v>
+      </c>
+      <c r="D933" t="s">
+        <v>168</v>
+      </c>
+      <c r="E933" t="s">
+        <v>171</v>
+      </c>
+      <c r="F933" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="934" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A934" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C934" s="5">
+        <v>16</v>
+      </c>
+      <c r="D934" t="s">
+        <v>176</v>
+      </c>
+      <c r="E934" t="s">
+        <v>165</v>
+      </c>
+      <c r="F934" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="935" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A935" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C935" s="5">
+        <v>24</v>
+      </c>
+      <c r="D935" t="s">
+        <v>176</v>
+      </c>
+      <c r="E935" t="s">
+        <v>165</v>
+      </c>
+      <c r="F935" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="936" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A936" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C936" s="5">
+        <v>9</v>
+      </c>
+      <c r="D936" t="s">
+        <v>176</v>
+      </c>
+      <c r="E936" t="s">
+        <v>165</v>
+      </c>
+      <c r="F936" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="937" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A937" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C937" s="5">
+        <v>5</v>
+      </c>
+      <c r="D937" t="s">
+        <v>168</v>
+      </c>
+      <c r="E937" t="s">
+        <v>169</v>
+      </c>
+      <c r="F937" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="938" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A938" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C938" s="5">
+        <v>5</v>
+      </c>
+      <c r="D938" t="s">
+        <v>168</v>
+      </c>
+      <c r="E938" t="s">
+        <v>169</v>
+      </c>
+      <c r="F938" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="939" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A939" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C939" s="5">
+        <v>48</v>
+      </c>
+      <c r="D939" t="s">
+        <v>168</v>
+      </c>
+      <c r="E939" t="s">
+        <v>172</v>
+      </c>
+      <c r="F939" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="940" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A940" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C940" s="5">
+        <v>50</v>
+      </c>
+      <c r="D940" t="s">
+        <v>166</v>
+      </c>
+      <c r="E940" t="s">
+        <v>165</v>
+      </c>
+      <c r="F940" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="941" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A941" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C941" s="5">
+        <v>2</v>
+      </c>
+      <c r="D941" t="s">
+        <v>176</v>
+      </c>
+      <c r="E941" t="s">
+        <v>165</v>
+      </c>
+      <c r="F941" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="942" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A942" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C942" s="5">
+        <v>23</v>
+      </c>
+      <c r="D942" t="s">
+        <v>173</v>
+      </c>
+      <c r="E942" t="s">
+        <v>165</v>
+      </c>
+      <c r="F942" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="943" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A943" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C943" s="5">
+        <v>98</v>
+      </c>
+      <c r="D943" t="s">
+        <v>166</v>
+      </c>
+      <c r="E943" t="s">
+        <v>165</v>
+      </c>
+      <c r="F943" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="944" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A944" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C944" s="5">
+        <v>7</v>
+      </c>
+      <c r="D944" t="s">
+        <v>176</v>
+      </c>
+      <c r="E944" t="s">
+        <v>165</v>
+      </c>
+      <c r="F944" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="945" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A945" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B945" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C945" s="5">
+        <v>58</v>
+      </c>
+      <c r="D945" t="s">
+        <v>173</v>
+      </c>
+      <c r="E945" t="s">
+        <v>165</v>
+      </c>
+      <c r="F945" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="946" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A946" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C946" s="5">
+        <v>4</v>
+      </c>
+      <c r="D946" t="s">
+        <v>168</v>
+      </c>
+      <c r="E946" t="s">
+        <v>169</v>
+      </c>
+      <c r="F946" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="947" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A947" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C947" s="5">
+        <v>5</v>
+      </c>
+      <c r="D947" t="s">
+        <v>168</v>
+      </c>
+      <c r="E947" t="s">
+        <v>171</v>
+      </c>
+      <c r="F947" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="948" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A948" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C948" s="5">
+        <v>9</v>
+      </c>
+      <c r="D948" t="s">
+        <v>173</v>
+      </c>
+      <c r="E948" t="s">
+        <v>165</v>
+      </c>
+      <c r="F948" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="949" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A949" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B949" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C949" s="5">
+        <v>6</v>
+      </c>
+      <c r="D949" t="s">
+        <v>166</v>
+      </c>
+      <c r="E949" t="s">
+        <v>165</v>
+      </c>
+      <c r="F949" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="950" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A950" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B950" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C950" s="5">
+        <v>295</v>
+      </c>
+      <c r="D950" t="s">
+        <v>173</v>
+      </c>
+      <c r="E950" t="s">
+        <v>165</v>
+      </c>
+      <c r="F950" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="951" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A951" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B951" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C951" s="5">
+        <v>114</v>
+      </c>
+      <c r="D951" t="s">
+        <v>168</v>
+      </c>
+      <c r="E951" t="s">
+        <v>174</v>
+      </c>
+      <c r="F951" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="952" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A952" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B952" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C952" s="5">
+        <v>40</v>
+      </c>
+      <c r="D952" t="s">
+        <v>167</v>
+      </c>
+      <c r="E952" t="s">
+        <v>165</v>
+      </c>
+      <c r="F952" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="953" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A953" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B953" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C953" s="5">
+        <v>5</v>
+      </c>
+      <c r="D953" t="s">
+        <v>168</v>
+      </c>
+      <c r="E953" t="s">
+        <v>169</v>
+      </c>
+      <c r="F953" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="954" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A954" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B954" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C954" s="5">
+        <v>10</v>
+      </c>
+      <c r="D954" t="s">
+        <v>166</v>
+      </c>
+      <c r="E954" t="s">
+        <v>165</v>
+      </c>
+      <c r="F954" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="955" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A955" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C955" s="5">
+        <v>0</v>
+      </c>
+      <c r="D955" t="s">
+        <v>173</v>
+      </c>
+      <c r="E955" t="s">
+        <v>165</v>
+      </c>
+      <c r="F955" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="956" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A956" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C956" s="5">
+        <v>48</v>
+      </c>
+      <c r="D956" t="s">
+        <v>176</v>
+      </c>
+      <c r="E956" t="s">
+        <v>165</v>
+      </c>
+      <c r="F956" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="957" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A957" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B957" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C957" s="5">
+        <v>3</v>
+      </c>
+      <c r="D957" t="s">
+        <v>176</v>
+      </c>
+      <c r="E957" t="s">
+        <v>165</v>
+      </c>
+      <c r="F957" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="958" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A958" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C958" s="5">
+        <v>16</v>
+      </c>
+      <c r="D958" t="s">
+        <v>176</v>
+      </c>
+      <c r="E958" t="s">
+        <v>165</v>
+      </c>
+      <c r="F958" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="959" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A959" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C959" s="5">
+        <v>2</v>
+      </c>
+      <c r="D959" t="s">
+        <v>167</v>
+      </c>
+      <c r="E959" t="s">
+        <v>165</v>
+      </c>
+      <c r="F959" s="6">
+        <v>45955</v>
+      </c>
+    </row>
+    <row r="960" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A960" s="4"/>
       <c r="B960" s="2"/>
       <c r="C960" s="5"/>
